--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E28794-5E3C-470A-9170-BEAAE4771B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A237ABE-4100-40A4-A557-6B3CF6E31E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 19-12-2025'!$A$1:$BF$161</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 29-01-2026'!$A$1:$BF$161</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A237ABE-4100-40A4-A557-6B3CF6E31E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55B0078-451D-42F2-AA6E-7604B3E9058D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 29-01-2026'!$A$1:$BF$161</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 02-02-2026'!$A$1:$BF$161</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -3352,7 +3352,7 @@
         <v>62</v>
       </c>
       <c r="AH104" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="BA104" t="s">
         <v>62</v>
@@ -3372,7 +3372,7 @@
         <v>62</v>
       </c>
       <c r="AH105" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="BA105" t="s">
         <v>62</v>
@@ -3409,7 +3409,7 @@
         <v>62</v>
       </c>
       <c r="AH107" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="BA107" t="s">
         <v>62</v>
@@ -4400,7 +4400,7 @@
         <v>61</v>
       </c>
       <c r="AH151" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AV151" t="s">
         <v>61</v>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FED3A54-EA1E-4AD7-9DBC-C0269C922420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A31D686-70E0-45B4-9BAD-7FDD40F44F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 20-02-2026'!$A$1:$BG$161</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 04-03-2026'!$A$1:$BG$161</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="234">
   <si>
     <t>Standard</t>
   </si>
@@ -1427,6 +1427,9 @@
       <c r="AO9" t="s">
         <v>62</v>
       </c>
+      <c r="AQ9" t="s">
+        <v>62</v>
+      </c>
       <c r="AT9" t="s">
         <v>62</v>
       </c>
@@ -1474,6 +1477,9 @@
       <c r="AO10" t="s">
         <v>62</v>
       </c>
+      <c r="AQ10" t="s">
+        <v>62</v>
+      </c>
       <c r="AT10" t="s">
         <v>62</v>
       </c>
@@ -1608,6 +1614,9 @@
       <c r="AO17" t="s">
         <v>62</v>
       </c>
+      <c r="AQ17" t="s">
+        <v>62</v>
+      </c>
       <c r="AT17" t="s">
         <v>62</v>
       </c>
@@ -2177,7 +2186,7 @@
         <v>62</v>
       </c>
       <c r="AQ49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AY49" t="s">
         <v>63</v>
@@ -2282,7 +2291,7 @@
         <v>62</v>
       </c>
       <c r="AQ52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AT52" t="s">
         <v>62</v>
@@ -2332,7 +2341,7 @@
         <v>62</v>
       </c>
       <c r="AQ53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AT53" t="s">
         <v>62</v>
@@ -2540,7 +2549,7 @@
         <v>62</v>
       </c>
       <c r="AQ64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AT64" t="s">
         <v>62</v>
@@ -2970,6 +2979,9 @@
       <c r="AO86" t="s">
         <v>62</v>
       </c>
+      <c r="AQ86" t="s">
+        <v>62</v>
+      </c>
       <c r="AS86" t="s">
         <v>62</v>
       </c>
@@ -3032,6 +3044,9 @@
       <c r="AO87" t="s">
         <v>62</v>
       </c>
+      <c r="AQ87" t="s">
+        <v>62</v>
+      </c>
       <c r="AS87" t="s">
         <v>62</v>
       </c>
@@ -3097,6 +3112,9 @@
       <c r="AO88" t="s">
         <v>62</v>
       </c>
+      <c r="AQ88" t="s">
+        <v>62</v>
+      </c>
       <c r="AS88" t="s">
         <v>62</v>
       </c>
@@ -3291,6 +3309,9 @@
       <c r="AO98" t="s">
         <v>62</v>
       </c>
+      <c r="AQ98" t="s">
+        <v>62</v>
+      </c>
       <c r="AV98" t="s">
         <v>62</v>
       </c>
@@ -3976,7 +3997,7 @@
         <v>62</v>
       </c>
       <c r="AQ134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AY134" t="s">
         <v>63</v>
@@ -4093,7 +4114,7 @@
         <v>62</v>
       </c>
       <c r="AQ137" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AT137" t="s">
         <v>62</v>
@@ -4167,7 +4188,7 @@
         <v>62</v>
       </c>
       <c r="AQ138" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AT138" t="s">
         <v>62</v>
@@ -4235,7 +4256,7 @@
         <v>62</v>
       </c>
       <c r="AQ139" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AT139" t="s">
         <v>62</v>
@@ -4434,7 +4455,7 @@
         <v>62</v>
       </c>
       <c r="AQ150" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AY150" t="s">
         <v>63</v>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A31D686-70E0-45B4-9BAD-7FDD40F44F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0011DAB5-DCF0-44A8-8329-7AEB1004490E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 04-03-2026'!$A$1:$BG$161</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 06-03-2026'!$A$1:$BG$161</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0011DAB5-DCF0-44A8-8329-7AEB1004490E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B5F295-6238-46A5-AF8A-F60EEA94375D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="234">
   <si>
     <t>Standard</t>
   </si>
@@ -1309,6 +1309,9 @@
       <c r="AH4" t="s">
         <v>62</v>
       </c>
+      <c r="AN4" t="s">
+        <v>62</v>
+      </c>
       <c r="AO4" t="s">
         <v>62</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B5F295-6238-46A5-AF8A-F60EEA94375D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D330B5-6A70-4042-B2D9-A9D2E16528DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D330B5-6A70-4042-B2D9-A9D2E16528DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DD139B-D835-4583-8C79-9125CBC630FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 06-03-2026'!$A$1:$BG$161</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 09-03-2026'!$A$1:$BG$163</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="235">
   <si>
     <t>Standard</t>
   </si>
@@ -715,6 +715,9 @@
   </si>
   <si>
     <t>XDIS05 (XD0533L)</t>
+  </si>
+  <si>
+    <t>XDIS07 (XD0734L)</t>
   </si>
   <si>
     <t>XREF01 (XH0130R)</t>
@@ -1068,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG161"/>
+  <dimension ref="A1:BG163"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:59" x14ac:dyDescent="0.3">
@@ -3161,6 +3164,9 @@
       <c r="U90" t="s">
         <v>62</v>
       </c>
+      <c r="AA90" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="91" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
@@ -3195,6 +3201,9 @@
       <c r="Z92" t="s">
         <v>62</v>
       </c>
+      <c r="AA92" t="s">
+        <v>63</v>
+      </c>
       <c r="AB92" t="s">
         <v>114</v>
       </c>
@@ -3212,6 +3221,9 @@
       <c r="U93" t="s">
         <v>62</v>
       </c>
+      <c r="AA93" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="94" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
@@ -3229,6 +3241,9 @@
       <c r="Z94" t="s">
         <v>62</v>
       </c>
+      <c r="AA94" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="95" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
@@ -3243,6 +3258,9 @@
       <c r="U95" t="s">
         <v>62</v>
       </c>
+      <c r="AA95" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="96" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -4295,6 +4313,9 @@
       <c r="W141" t="s">
         <v>62</v>
       </c>
+      <c r="AA141" t="s">
+        <v>63</v>
+      </c>
       <c r="AB141" t="s">
         <v>114</v>
       </c>
@@ -4326,47 +4347,50 @@
       <c r="C143" t="s">
         <v>195</v>
       </c>
+      <c r="AA143" t="s">
+        <v>63</v>
+      </c>
       <c r="AB143" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="144" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>229</v>
+        <v>160</v>
       </c>
       <c r="C144" t="s">
         <v>195</v>
       </c>
-      <c r="W144" t="s">
-        <v>62</v>
+      <c r="AA144" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="145" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="B145" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="C145" t="s">
         <v>195</v>
       </c>
-      <c r="M145" t="s">
-        <v>62</v>
-      </c>
       <c r="W145" t="s">
         <v>62</v>
+      </c>
+      <c r="AA145" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="146" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C146" t="s">
         <v>195</v>
@@ -4375,46 +4399,49 @@
         <v>62</v>
       </c>
       <c r="W146" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB146" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="147" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B147" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="C147" t="s">
         <v>195</v>
       </c>
-      <c r="U147" t="s">
-        <v>62</v>
+      <c r="AA147" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="148" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C148" t="s">
         <v>195</v>
       </c>
-      <c r="Z148" t="s">
+      <c r="M148" t="s">
+        <v>62</v>
+      </c>
+      <c r="W148" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB148" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="149" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B149" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C149" t="s">
         <v>195</v>
@@ -4425,131 +4452,125 @@
     </row>
     <row r="150" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B150" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C150" t="s">
         <v>195</v>
       </c>
-      <c r="H150" t="s">
-        <v>62</v>
-      </c>
-      <c r="O150" t="s">
-        <v>62</v>
-      </c>
-      <c r="W150" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA150" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB150" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC150" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF150" t="s">
-        <v>62</v>
-      </c>
-      <c r="AO150" t="s">
-        <v>62</v>
-      </c>
-      <c r="AQ150" t="s">
-        <v>62</v>
-      </c>
-      <c r="AY150" t="s">
-        <v>63</v>
+      <c r="Z150" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="151" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B151" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C151" t="s">
         <v>195</v>
       </c>
-      <c r="E151" t="s">
-        <v>62</v>
-      </c>
-      <c r="F151" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG151" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI151" t="s">
-        <v>62</v>
-      </c>
-      <c r="AW151" t="s">
-        <v>62</v>
-      </c>
-      <c r="AX151" t="s">
-        <v>62</v>
-      </c>
-      <c r="BB151" t="s">
+      <c r="U151" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="152" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B152" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="C152" t="s">
         <v>195</v>
       </c>
-      <c r="AT152" t="s">
-        <v>62</v>
+      <c r="H152" t="s">
+        <v>62</v>
+      </c>
+      <c r="O152" t="s">
+        <v>62</v>
+      </c>
+      <c r="W152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA152" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AQ152" t="s">
+        <v>62</v>
+      </c>
+      <c r="AY152" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="153" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B153" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C153" t="s">
         <v>195</v>
       </c>
-      <c r="M153" t="s">
-        <v>62</v>
-      </c>
-      <c r="W153" t="s">
-        <v>62</v>
-      </c>
-      <c r="AT153" t="s">
-        <v>75</v>
+      <c r="E153" t="s">
+        <v>62</v>
+      </c>
+      <c r="F153" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG153" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI153" t="s">
+        <v>62</v>
+      </c>
+      <c r="AW153" t="s">
+        <v>62</v>
+      </c>
+      <c r="AX153" t="s">
+        <v>62</v>
+      </c>
+      <c r="BB153" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="154" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B154" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="C154" t="s">
         <v>195</v>
       </c>
-      <c r="M154" t="s">
-        <v>63</v>
+      <c r="AT154" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="155" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B155" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C155" t="s">
         <v>195</v>
@@ -4557,70 +4578,64 @@
       <c r="M155" t="s">
         <v>62</v>
       </c>
+      <c r="W155" t="s">
+        <v>62</v>
+      </c>
       <c r="AT155" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="156" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B156" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C156" t="s">
         <v>195</v>
       </c>
-      <c r="T156" t="s">
-        <v>62</v>
-      </c>
-      <c r="U156" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z156" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK156" t="s">
-        <v>62</v>
-      </c>
-      <c r="BB156" t="s">
-        <v>62</v>
+      <c r="M156" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="157" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B157" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C157" t="s">
         <v>195</v>
       </c>
-      <c r="T157" t="s">
-        <v>62</v>
-      </c>
-      <c r="U157" t="s">
-        <v>62</v>
-      </c>
-      <c r="BB157" t="s">
-        <v>63</v>
+      <c r="M157" t="s">
+        <v>62</v>
+      </c>
+      <c r="AT157" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="158" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B158" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="C158" t="s">
         <v>195</v>
       </c>
-      <c r="M158" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB158" t="s">
+      <c r="T158" t="s">
+        <v>62</v>
+      </c>
+      <c r="U158" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z158" t="s">
+        <v>62</v>
+      </c>
+      <c r="AK158" t="s">
         <v>62</v>
       </c>
       <c r="BB158" t="s">
@@ -4629,70 +4644,110 @@
     </row>
     <row r="159" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B159" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C159" t="s">
         <v>195</v>
       </c>
-      <c r="AJ159" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK159" t="s">
-        <v>62</v>
-      </c>
-      <c r="AW159" t="s">
-        <v>62</v>
-      </c>
-      <c r="AX159" t="s">
+      <c r="T159" t="s">
+        <v>62</v>
+      </c>
+      <c r="U159" t="s">
         <v>62</v>
       </c>
       <c r="BB159" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="160" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>191</v>
+      </c>
+      <c r="B160" t="s">
         <v>232</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
+        <v>195</v>
+      </c>
+      <c r="M160" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB160" t="s">
+        <v>62</v>
+      </c>
+      <c r="BB160" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="161" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>191</v>
+      </c>
+      <c r="B161" t="s">
+        <v>192</v>
+      </c>
+      <c r="C161" t="s">
+        <v>195</v>
+      </c>
+      <c r="AJ161" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK161" t="s">
+        <v>62</v>
+      </c>
+      <c r="AW161" t="s">
+        <v>62</v>
+      </c>
+      <c r="AX161" t="s">
+        <v>62</v>
+      </c>
+      <c r="BB161" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="162" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>233</v>
       </c>
-      <c r="C160" t="s">
-        <v>195</v>
-      </c>
-      <c r="AK160" t="s">
-        <v>62</v>
-      </c>
-      <c r="AW160" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="161" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+      <c r="B162" t="s">
+        <v>234</v>
+      </c>
+      <c r="C162" t="s">
+        <v>195</v>
+      </c>
+      <c r="AK162" t="s">
+        <v>62</v>
+      </c>
+      <c r="AW162" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="163" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>193</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B163" t="s">
         <v>194</v>
       </c>
-      <c r="C161" t="s">
-        <v>195</v>
-      </c>
-      <c r="U161" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z161" t="s">
-        <v>62</v>
-      </c>
-      <c r="AJ161" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK161" t="s">
-        <v>62</v>
-      </c>
-      <c r="AW161" t="s">
+      <c r="C163" t="s">
+        <v>195</v>
+      </c>
+      <c r="U163" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z163" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ163" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK163" t="s">
+        <v>62</v>
+      </c>
+      <c r="AW163" t="s">
         <v>62</v>
       </c>
     </row>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF5E846-6306-426A-A64C-631D67F70F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FC5878-7007-46FC-BEB2-A4E0EC67CBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 09-03-2026'!$A$1:$BH$163</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 11-03-2026'!$A$1:$BH$163</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FC5878-7007-46FC-BEB2-A4E0EC67CBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D766F944-2AF3-4B7E-ABDC-89E5AA9E237E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="236">
   <si>
     <t>Standard</t>
   </si>
@@ -82,7 +82,7 @@
     <t>DiaProfil (ZiteLab)</t>
   </si>
   <si>
-    <t>Digital Svangrejournal (PLSP A/S)</t>
+    <t>Digital Svangrejournal (PLSP)</t>
   </si>
   <si>
     <t>DNHF (CGI)</t>
@@ -157,7 +157,7 @@
     <t>Planner4You (Software-fabric)</t>
   </si>
   <si>
-    <t>PLSP integrationsplatform (PLSP A/S)</t>
+    <t>PLSP integrationsplatform (PLSP)</t>
   </si>
   <si>
     <t>Practio (Practio)</t>
@@ -332,8 +332,7 @@
     <t>Pregnancy Referral Form</t>
   </si>
   <si>
-    <t>PRF-DK (3.0_x000D_
-3.0)</t>
+    <t>PRF-DK (3.0)</t>
   </si>
   <si>
     <t>Pregnancy visit summary Document</t>
@@ -2592,6 +2591,9 @@
       <c r="D65" t="s">
         <v>64</v>
       </c>
+      <c r="T65" t="s">
+        <v>63</v>
+      </c>
       <c r="Y65" t="s">
         <v>63</v>
       </c>
@@ -4558,6 +4560,9 @@
       </c>
       <c r="F153" t="s">
         <v>64</v>
+      </c>
+      <c r="T153" t="s">
+        <v>63</v>
       </c>
       <c r="AH153" t="s">
         <v>64</v>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D766F944-2AF3-4B7E-ABDC-89E5AA9E237E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6F942A-B2FE-4E37-AFED-9A7C5ECD15AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 11-03-2026'!$A$1:$BH$163</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 20-03-2026'!$A$1:$BH$163</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6F942A-B2FE-4E37-AFED-9A7C5ECD15AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CCE9EE-212D-43F5-8379-03C9723413F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 20-03-2026'!$A$1:$BH$163</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 25-03-2026'!$A$1:$BH$163</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="236">
   <si>
     <t>Standard</t>
   </si>
@@ -1643,6 +1643,9 @@
       <c r="BB17" t="s">
         <v>64</v>
       </c>
+      <c r="BC17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="18" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -3020,6 +3023,9 @@
       <c r="AW86" t="s">
         <v>64</v>
       </c>
+      <c r="BC86" t="s">
+        <v>63</v>
+      </c>
       <c r="BG86" t="s">
         <v>63</v>
       </c>
@@ -3088,6 +3094,9 @@
       <c r="BB87" t="s">
         <v>64</v>
       </c>
+      <c r="BC87" t="s">
+        <v>63</v>
+      </c>
       <c r="BG87" t="s">
         <v>63</v>
       </c>
@@ -3152,6 +3161,9 @@
       </c>
       <c r="AW88" t="s">
         <v>64</v>
+      </c>
+      <c r="BC88" t="s">
+        <v>63</v>
       </c>
       <c r="BG88" t="s">
         <v>63</v>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CCE9EE-212D-43F5-8379-03C9723413F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE612BB-6694-4B75-9739-EAEB00D09C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 25-03-2026'!$A$1:$BH$163</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 08-04-2026'!$A$1:$BH$163</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE612BB-6694-4B75-9739-EAEB00D09C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617093D2-AA81-47B9-8333-F96E1B3C34AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 08-04-2026'!$A$1:$BH$163</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 10-04-2026'!$A$1:$BH$167</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="240">
   <si>
     <t>Standard</t>
   </si>
@@ -267,6 +267,19 @@
   </si>
   <si>
     <t>CTL03 (C0330Q)</t>
+  </si>
+  <si>
+    <t>Den Dynamiske Blanket</t>
+  </si>
+  <si>
+    <t>DDB (1.1)</t>
+  </si>
+  <si>
+    <t>Den Gode Blanketservice</t>
+  </si>
+  <si>
+    <t>DGB (0.91_x000D_
+0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>
@@ -1073,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH163"/>
+  <dimension ref="A1:BH167"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:60" x14ac:dyDescent="0.3">
@@ -1491,6 +1504,9 @@
       <c r="AF10" t="s">
         <v>64</v>
       </c>
+      <c r="AO10" t="s">
+        <v>64</v>
+      </c>
       <c r="AP10" t="s">
         <v>64</v>
       </c>
@@ -1517,7 +1533,7 @@
       <c r="C11" t="s">
         <v>62</v>
       </c>
-      <c r="V11" t="s">
+      <c r="AO11" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1531,16 +1547,16 @@
       <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="AW12" t="s">
+      <c r="AO12" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
@@ -1551,21 +1567,21 @@
     </row>
     <row r="14" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
         <v>62</v>
       </c>
-      <c r="V14" t="s">
+      <c r="AW14" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>89</v>
@@ -1601,50 +1617,8 @@
       <c r="C17" t="s">
         <v>62</v>
       </c>
-      <c r="U17" t="s">
-        <v>64</v>
-      </c>
       <c r="V17" t="s">
         <v>64</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW17" t="s">
-        <v>64</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:60" x14ac:dyDescent="0.3">
@@ -1657,8 +1631,8 @@
       <c r="C18" t="s">
         <v>62</v>
       </c>
-      <c r="Y18" t="s">
-        <v>63</v>
+      <c r="V18" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:60" x14ac:dyDescent="0.3">
@@ -1671,50 +1645,92 @@
       <c r="C19" t="s">
         <v>62</v>
       </c>
-      <c r="D19" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>64</v>
-      </c>
-      <c r="BH19" t="s">
-        <v>64</v>
+      <c r="U19" t="s">
+        <v>64</v>
+      </c>
+      <c r="V19" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
       </c>
-      <c r="BF20" t="s">
-        <v>64</v>
+      <c r="Y20" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
         <v>62</v>
       </c>
-      <c r="T21" t="s">
-        <v>63</v>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>64</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
         <v>102</v>
@@ -1722,8 +1738,8 @@
       <c r="C22" t="s">
         <v>62</v>
       </c>
-      <c r="T22" t="s">
-        <v>63</v>
+      <c r="BF22" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:60" x14ac:dyDescent="0.3">
@@ -1736,11 +1752,8 @@
       <c r="C23" t="s">
         <v>62</v>
       </c>
-      <c r="W23" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>64</v>
+      <c r="T23" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:60" x14ac:dyDescent="0.3">
@@ -1767,11 +1780,11 @@
       <c r="C25" t="s">
         <v>62</v>
       </c>
-      <c r="D25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>63</v>
+      <c r="W25" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:60" x14ac:dyDescent="0.3">
@@ -1784,89 +1797,80 @@
       <c r="C26" t="s">
         <v>62</v>
       </c>
-      <c r="D26" t="s">
-        <v>76</v>
-      </c>
-      <c r="S26" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM26" t="s">
-        <v>76</v>
-      </c>
-      <c r="BB26" t="s">
-        <v>64</v>
-      </c>
-      <c r="BH26" t="s">
-        <v>64</v>
+      <c r="T26" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
         <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
-      </c>
-      <c r="S27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AH27" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM27" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
         <v>62</v>
       </c>
-      <c r="V28" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC28" t="s">
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="S28" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>76</v>
+      </c>
+      <c r="BB28" t="s">
+        <v>64</v>
+      </c>
+      <c r="BH28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
         <v>62</v>
       </c>
-      <c r="U29" t="s">
-        <v>64</v>
-      </c>
-      <c r="V29" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>115</v>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="S29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:60" x14ac:dyDescent="0.3">
@@ -1882,6 +1886,9 @@
       <c r="V30" t="s">
         <v>64</v>
       </c>
+      <c r="AC30" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="31" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1903,35 +1910,29 @@
         <v>64</v>
       </c>
       <c r="AC31" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
         <v>62</v>
       </c>
-      <c r="U32" t="s">
-        <v>64</v>
-      </c>
       <c r="V32" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC32" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
         <v>62</v>
@@ -1940,20 +1941,29 @@
         <v>64</v>
       </c>
       <c r="V33" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC33" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
         <v>62</v>
       </c>
       <c r="U34" t="s">
+        <v>64</v>
+      </c>
+      <c r="V34" t="s">
         <v>64</v>
       </c>
       <c r="AC34" t="s">
@@ -1962,7 +1972,7 @@
     </row>
     <row r="35" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
         <v>125</v>
@@ -1973,35 +1983,41 @@
       <c r="U35" t="s">
         <v>64</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="V35" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
         <v>62</v>
       </c>
       <c r="U36" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC36" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
         <v>62</v>
       </c>
       <c r="U37" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC37" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2010,21 +2026,18 @@
         <v>128</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
         <v>62</v>
       </c>
       <c r="U38" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC38" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B39" t="s">
         <v>131</v>
@@ -2035,16 +2048,13 @@
       <c r="U39" t="s">
         <v>64</v>
       </c>
-      <c r="AC39" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="40" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
         <v>62</v>
@@ -2053,100 +2063,94 @@
         <v>64</v>
       </c>
       <c r="AC40" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
         <v>62</v>
       </c>
-      <c r="O41" t="s">
+      <c r="U41" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC41" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s">
         <v>62</v>
       </c>
-      <c r="AA42" t="s">
-        <v>64</v>
+      <c r="U42" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
         <v>62</v>
       </c>
-      <c r="AQ43" t="s">
-        <v>64</v>
-      </c>
-      <c r="AV43" t="s">
-        <v>64</v>
-      </c>
-      <c r="BG43" t="s">
-        <v>63</v>
+      <c r="O43" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
         <v>62</v>
       </c>
-      <c r="O44" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>76</v>
-      </c>
-      <c r="BG44" t="s">
-        <v>63</v>
-      </c>
-      <c r="BH44" t="s">
+      <c r="AA44" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
         <v>62</v>
       </c>
-      <c r="G45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT45" t="s">
-        <v>64</v>
+      <c r="AQ45" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV45" t="s">
+        <v>64</v>
+      </c>
+      <c r="BG45" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
         <v>142</v>
@@ -2154,41 +2158,53 @@
       <c r="C46" t="s">
         <v>62</v>
       </c>
-      <c r="J46" t="s">
+      <c r="O46" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>76</v>
+      </c>
+      <c r="BG46" t="s">
+        <v>63</v>
+      </c>
+      <c r="BH46" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C47" t="s">
         <v>62</v>
       </c>
-      <c r="J47" t="s">
+      <c r="G47" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT47" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
         <v>62</v>
       </c>
-      <c r="BE48" t="s">
+      <c r="J48" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B49" t="s">
         <v>147</v>
@@ -2196,86 +2212,59 @@
       <c r="C49" t="s">
         <v>62</v>
       </c>
-      <c r="L49" t="s">
-        <v>63</v>
-      </c>
-      <c r="U49" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD49" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP49" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR49" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ49" t="s">
-        <v>63</v>
-      </c>
-      <c r="BG49" t="s">
-        <v>63</v>
+      <c r="J49" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
         <v>62</v>
       </c>
-      <c r="P50" t="s">
-        <v>64</v>
-      </c>
-      <c r="R50" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>63</v>
+      <c r="BE50" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
         <v>62</v>
       </c>
-      <c r="H51" t="s">
-        <v>64</v>
-      </c>
-      <c r="N51" t="s">
-        <v>64</v>
-      </c>
-      <c r="X51" t="s">
+      <c r="L51" t="s">
+        <v>63</v>
+      </c>
+      <c r="U51" t="s">
         <v>64</v>
       </c>
       <c r="AD51" t="s">
         <v>64</v>
       </c>
-      <c r="AG51" t="s">
-        <v>64</v>
-      </c>
       <c r="AP51" t="s">
         <v>64</v>
       </c>
-      <c r="AU51" t="s">
+      <c r="AR51" t="s">
         <v>64</v>
       </c>
       <c r="AZ51" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG51" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
         <v>152</v>
@@ -2283,43 +2272,13 @@
       <c r="C52" t="s">
         <v>62</v>
       </c>
-      <c r="H52" t="s">
-        <v>64</v>
-      </c>
-      <c r="N52" t="s">
-        <v>64</v>
-      </c>
       <c r="P52" t="s">
         <v>64</v>
       </c>
-      <c r="U52" t="s">
-        <v>64</v>
-      </c>
-      <c r="V52" t="s">
-        <v>64</v>
-      </c>
-      <c r="X52" t="s">
+      <c r="R52" t="s">
         <v>64</v>
       </c>
       <c r="AB52" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD52" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG52" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP52" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR52" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU52" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ52" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2339,21 +2298,9 @@
       <c r="N53" t="s">
         <v>64</v>
       </c>
-      <c r="P53" t="s">
-        <v>64</v>
-      </c>
-      <c r="U53" t="s">
-        <v>64</v>
-      </c>
-      <c r="V53" t="s">
-        <v>64</v>
-      </c>
       <c r="X53" t="s">
         <v>64</v>
       </c>
-      <c r="AB53" t="s">
-        <v>63</v>
-      </c>
       <c r="AD53" t="s">
         <v>64</v>
       </c>
@@ -2361,9 +2308,6 @@
         <v>64</v>
       </c>
       <c r="AP53" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR53" t="s">
         <v>64</v>
       </c>
       <c r="AU53" t="s">
@@ -2383,8 +2327,44 @@
       <c r="C54" t="s">
         <v>62</v>
       </c>
+      <c r="H54" t="s">
+        <v>64</v>
+      </c>
+      <c r="N54" t="s">
+        <v>64</v>
+      </c>
+      <c r="P54" t="s">
+        <v>64</v>
+      </c>
+      <c r="U54" t="s">
+        <v>64</v>
+      </c>
+      <c r="V54" t="s">
+        <v>64</v>
+      </c>
       <c r="X54" t="s">
         <v>64</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG54" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP54" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR54" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ54" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:59" x14ac:dyDescent="0.3">
@@ -2397,41 +2377,77 @@
       <c r="C55" t="s">
         <v>62</v>
       </c>
+      <c r="H55" t="s">
+        <v>64</v>
+      </c>
       <c r="N55" t="s">
         <v>64</v>
+      </c>
+      <c r="P55" t="s">
+        <v>64</v>
+      </c>
+      <c r="U55" t="s">
+        <v>64</v>
+      </c>
+      <c r="V55" t="s">
+        <v>64</v>
+      </c>
+      <c r="X55" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP55" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU55" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ55" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C56" t="s">
         <v>62</v>
       </c>
-      <c r="R56" t="s">
+      <c r="X56" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
         <v>62</v>
       </c>
-      <c r="X57" t="s">
+      <c r="N57" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B58" t="s">
         <v>163</v>
@@ -2439,16 +2455,7 @@
       <c r="C58" t="s">
         <v>62</v>
       </c>
-      <c r="E58" t="s">
-        <v>64</v>
-      </c>
-      <c r="F58" t="s">
-        <v>64</v>
-      </c>
-      <c r="I58" t="s">
-        <v>64</v>
-      </c>
-      <c r="M58" t="s">
+      <c r="R58" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2462,7 +2469,7 @@
       <c r="C59" t="s">
         <v>62</v>
       </c>
-      <c r="N59" t="s">
+      <c r="X59" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2476,7 +2483,16 @@
       <c r="C60" t="s">
         <v>62</v>
       </c>
-      <c r="X60" t="s">
+      <c r="E60" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" t="s">
+        <v>64</v>
+      </c>
+      <c r="I60" t="s">
+        <v>64</v>
+      </c>
+      <c r="M60" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2490,30 +2506,30 @@
       <c r="C61" t="s">
         <v>62</v>
       </c>
-      <c r="V61" t="s">
+      <c r="N61" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C62" t="s">
         <v>62</v>
       </c>
-      <c r="AA62" t="s">
+      <c r="X62" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B63" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
         <v>62</v>
@@ -2524,7 +2540,7 @@
     </row>
     <row r="64" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B64" t="s">
         <v>174</v>
@@ -2532,53 +2548,8 @@
       <c r="C64" t="s">
         <v>62</v>
       </c>
-      <c r="H64" t="s">
-        <v>64</v>
-      </c>
-      <c r="K64" t="s">
-        <v>64</v>
-      </c>
-      <c r="N64" t="s">
-        <v>64</v>
-      </c>
-      <c r="P64" t="s">
-        <v>64</v>
-      </c>
-      <c r="R64" t="s">
-        <v>64</v>
-      </c>
-      <c r="X64" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB64" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC64" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD64" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG64" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM64" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP64" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR64" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU64" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ64" t="s">
-        <v>63</v>
+      <c r="AA64" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:60" x14ac:dyDescent="0.3">
@@ -2591,22 +2562,7 @@
       <c r="C65" t="s">
         <v>62</v>
       </c>
-      <c r="D65" t="s">
-        <v>64</v>
-      </c>
-      <c r="T65" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH65" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF65" t="s">
-        <v>64</v>
-      </c>
-      <c r="BH65" t="s">
+      <c r="V65" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2620,8 +2576,53 @@
       <c r="C66" t="s">
         <v>62</v>
       </c>
+      <c r="H66" t="s">
+        <v>64</v>
+      </c>
+      <c r="K66" t="s">
+        <v>64</v>
+      </c>
+      <c r="N66" t="s">
+        <v>64</v>
+      </c>
+      <c r="P66" t="s">
+        <v>64</v>
+      </c>
+      <c r="R66" t="s">
+        <v>64</v>
+      </c>
       <c r="X66" t="s">
         <v>64</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM66" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP66" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR66" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU66" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ66" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:60" x14ac:dyDescent="0.3">
@@ -2634,10 +2635,22 @@
       <c r="C67" t="s">
         <v>62</v>
       </c>
-      <c r="N67" t="s">
-        <v>64</v>
-      </c>
-      <c r="X67" t="s">
+      <c r="D67" t="s">
+        <v>64</v>
+      </c>
+      <c r="T67" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>64</v>
+      </c>
+      <c r="BF67" t="s">
+        <v>64</v>
+      </c>
+      <c r="BH67" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2668,19 +2681,19 @@
       <c r="N69" t="s">
         <v>64</v>
       </c>
+      <c r="X69" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="70" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C70" t="s">
         <v>62</v>
-      </c>
-      <c r="N70" t="s">
-        <v>64</v>
       </c>
       <c r="X70" t="s">
         <v>64</v>
@@ -2688,27 +2701,21 @@
     </row>
     <row r="71" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B71" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C71" t="s">
         <v>62</v>
       </c>
-      <c r="U71" t="s">
-        <v>64</v>
-      </c>
-      <c r="V71" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA71" t="s">
+      <c r="N71" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B72" t="s">
         <v>189</v>
@@ -2716,10 +2723,10 @@
       <c r="C72" t="s">
         <v>62</v>
       </c>
-      <c r="U72" t="s">
-        <v>64</v>
-      </c>
-      <c r="V72" t="s">
+      <c r="N72" t="s">
+        <v>64</v>
+      </c>
+      <c r="X72" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2733,8 +2740,14 @@
       <c r="C73" t="s">
         <v>62</v>
       </c>
-      <c r="O73" t="s">
-        <v>63</v>
+      <c r="U73" t="s">
+        <v>64</v>
+      </c>
+      <c r="V73" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:60" x14ac:dyDescent="0.3">
@@ -2747,8 +2760,11 @@
       <c r="C74" t="s">
         <v>62</v>
       </c>
-      <c r="Z74" t="s">
-        <v>76</v>
+      <c r="U74" t="s">
+        <v>64</v>
+      </c>
+      <c r="V74" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:60" x14ac:dyDescent="0.3">
@@ -2762,201 +2778,192 @@
         <v>62</v>
       </c>
       <c r="O75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="B76" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
-      </c>
-      <c r="L76" t="s">
-        <v>63</v>
-      </c>
-      <c r="V76" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD76" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="B77" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>196</v>
-      </c>
-      <c r="M77" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK77" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL77" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS77" t="s">
-        <v>63</v>
-      </c>
-      <c r="AX77" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY77" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC77" t="s">
+        <v>62</v>
+      </c>
+      <c r="O77" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C78" t="s">
-        <v>196</v>
-      </c>
-      <c r="U78" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="L78" t="s">
+        <v>63</v>
       </c>
       <c r="V78" t="s">
         <v>64</v>
       </c>
-      <c r="AP78" t="s">
-        <v>64</v>
+      <c r="AD78" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
-      </c>
-      <c r="U79" t="s">
+        <v>200</v>
+      </c>
+      <c r="M79" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK79" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS79" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX79" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY79" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC79" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C80" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="U80" t="s">
+        <v>64</v>
       </c>
       <c r="V80" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO80" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP80" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B81" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C81" t="s">
-        <v>196</v>
-      </c>
-      <c r="L81" t="s">
-        <v>63</v>
-      </c>
-      <c r="V81" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD81" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="U81" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C82" t="s">
-        <v>196</v>
-      </c>
-      <c r="W82" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS82" t="s">
+        <v>200</v>
+      </c>
+      <c r="V82" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="B83" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="C83" t="s">
-        <v>196</v>
-      </c>
-      <c r="AX83" t="s">
-        <v>63</v>
-      </c>
-      <c r="BC83" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="L83" t="s">
+        <v>63</v>
+      </c>
+      <c r="V83" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="B84" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>196</v>
-      </c>
-      <c r="AY84" t="s">
+        <v>200</v>
+      </c>
+      <c r="W84" t="s">
         <v>76</v>
       </c>
-      <c r="BC84" t="s">
+      <c r="AS84" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" t="s">
-        <v>196</v>
-      </c>
-      <c r="AK85" t="s">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="AX85" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BC85" t="s">
         <v>64</v>
@@ -2964,152 +2971,53 @@
     </row>
     <row r="86" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B86" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
-      </c>
-      <c r="G86" t="s">
-        <v>64</v>
-      </c>
-      <c r="J86" t="s">
+        <v>200</v>
+      </c>
+      <c r="AY86" t="s">
         <v>76</v>
       </c>
-      <c r="O86" t="s">
-        <v>64</v>
-      </c>
-      <c r="U86" t="s">
-        <v>64</v>
-      </c>
-      <c r="V86" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB86" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU86" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW86" t="s">
-        <v>64</v>
-      </c>
       <c r="BC86" t="s">
-        <v>63</v>
-      </c>
-      <c r="BG86" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="87" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="C87" t="s">
-        <v>196</v>
-      </c>
-      <c r="G87" t="s">
-        <v>64</v>
-      </c>
-      <c r="J87" t="s">
-        <v>76</v>
-      </c>
-      <c r="O87" t="s">
-        <v>64</v>
-      </c>
-      <c r="U87" t="s">
-        <v>64</v>
-      </c>
-      <c r="V87" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB87" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU87" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW87" t="s">
-        <v>64</v>
-      </c>
-      <c r="BB87" t="s">
+        <v>200</v>
+      </c>
+      <c r="AK87" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX87" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY87" t="s">
         <v>64</v>
       </c>
       <c r="BC87" t="s">
-        <v>63</v>
-      </c>
-      <c r="BG87" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="C88" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G88" t="s">
         <v>64</v>
@@ -3171,49 +3079,154 @@
     </row>
     <row r="89" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B89" t="s">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="C89" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="G89" t="s">
+        <v>64</v>
+      </c>
+      <c r="J89" t="s">
+        <v>76</v>
+      </c>
+      <c r="O89" t="s">
+        <v>64</v>
+      </c>
+      <c r="U89" t="s">
+        <v>64</v>
       </c>
       <c r="V89" t="s">
         <v>64</v>
       </c>
+      <c r="Z89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>63</v>
+      </c>
       <c r="AC89" t="s">
         <v>64</v>
+      </c>
+      <c r="AF89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU89" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW89" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB89" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC89" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG89" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="90" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="G90" t="s">
+        <v>64</v>
+      </c>
+      <c r="J90" t="s">
+        <v>76</v>
+      </c>
+      <c r="O90" t="s">
+        <v>64</v>
+      </c>
+      <c r="U90" t="s">
+        <v>64</v>
       </c>
       <c r="V90" t="s">
         <v>64</v>
       </c>
+      <c r="Z90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>64</v>
+      </c>
       <c r="AB90" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AT90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU90" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW90" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC90" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG90" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="91" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC91" t="s">
+        <v>200</v>
+      </c>
+      <c r="AO91" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3222,58 +3235,43 @@
         <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>196</v>
-      </c>
-      <c r="V92" t="s">
-        <v>64</v>
-      </c>
-      <c r="X92" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA92" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB92" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC92" t="s">
-        <v>115</v>
+        <v>200</v>
+      </c>
+      <c r="AO92" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="93" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>205</v>
+        <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C93" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="V93" t="s">
         <v>64</v>
       </c>
-      <c r="AB93" t="s">
-        <v>63</v>
+      <c r="AC93" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
-        <v>208</v>
+        <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="V94" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA94" t="s">
         <v>64</v>
       </c>
       <c r="AB94" t="s">
@@ -3282,147 +3280,126 @@
     </row>
     <row r="95" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B95" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
-      </c>
-      <c r="V95" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB95" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B96" t="s">
         <v>89</v>
       </c>
       <c r="C96" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="V96" t="s">
         <v>64</v>
       </c>
+      <c r="X96" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA96" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB96" t="s">
+        <v>63</v>
+      </c>
       <c r="AC96" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="V97" t="s">
         <v>64</v>
+      </c>
+      <c r="AB97" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>92</v>
+        <v>211</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="C98" t="s">
-        <v>196</v>
-      </c>
-      <c r="H98" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="V98" t="s">
         <v>64</v>
       </c>
-      <c r="X98" t="s">
-        <v>64</v>
-      </c>
       <c r="AA98" t="s">
         <v>64</v>
       </c>
       <c r="AB98" t="s">
         <v>63</v>
-      </c>
-      <c r="AC98" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF98" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO98" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP98" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR98" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW98" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="99" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B99" t="s">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="C99" t="s">
-        <v>196</v>
-      </c>
-      <c r="AL99" t="s">
-        <v>63</v>
-      </c>
-      <c r="BC99" t="s">
-        <v>64</v>
-      </c>
-      <c r="BD99" t="s">
-        <v>76</v>
+        <v>200</v>
+      </c>
+      <c r="V99" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB99" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>196</v>
-      </c>
-      <c r="E100" t="s">
-        <v>64</v>
-      </c>
-      <c r="F100" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC100" t="s">
+        <v>200</v>
+      </c>
+      <c r="V100" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC100" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>210</v>
+        <v>94</v>
       </c>
       <c r="B101" t="s">
-        <v>211</v>
+        <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>196</v>
-      </c>
-      <c r="BC101" t="s">
+        <v>200</v>
+      </c>
+      <c r="V101" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3434,104 +3411,125 @@
         <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>196</v>
-      </c>
-      <c r="AL102" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM102" t="s">
-        <v>76</v>
-      </c>
-      <c r="BC102" t="s">
+        <v>200</v>
+      </c>
+      <c r="H102" t="s">
+        <v>64</v>
+      </c>
+      <c r="V102" t="s">
+        <v>64</v>
+      </c>
+      <c r="X102" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA102" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB102" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF102" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO102" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP102" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR102" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW102" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>213</v>
       </c>
       <c r="C103" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="AL103" t="s">
+        <v>63</v>
       </c>
       <c r="BC103" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="BD103" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="104" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>98</v>
+      </c>
+      <c r="B104" t="s">
         <v>99</v>
       </c>
-      <c r="B104" t="s">
-        <v>100</v>
-      </c>
       <c r="C104" t="s">
-        <v>196</v>
-      </c>
-      <c r="T104" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ104" t="s">
+        <v>200</v>
+      </c>
+      <c r="E104" t="s">
+        <v>64</v>
+      </c>
+      <c r="F104" t="s">
         <v>64</v>
       </c>
       <c r="BC104" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>101</v>
+        <v>214</v>
       </c>
       <c r="B105" t="s">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="C105" t="s">
-        <v>196</v>
-      </c>
-      <c r="T105" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ105" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="BC105" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C106" t="s">
-        <v>196</v>
-      </c>
-      <c r="W106" t="s">
+        <v>200</v>
+      </c>
+      <c r="AL106" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM106" t="s">
         <v>76</v>
       </c>
-      <c r="AS106" t="s">
+      <c r="BC106" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="107" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>196</v>
-      </c>
-      <c r="T107" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ107" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="BC107" t="s">
         <v>63</v>
@@ -3539,49 +3537,58 @@
     </row>
     <row r="108" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="C108" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="T108" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ108" t="s">
+        <v>64</v>
       </c>
       <c r="BC108" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C109" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="T109" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ109" t="s">
+        <v>64</v>
       </c>
       <c r="BC109" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="110" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>196</v>
-      </c>
-      <c r="AL110" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM110" t="s">
+        <v>200</v>
+      </c>
+      <c r="W110" t="s">
         <v>76</v>
       </c>
-      <c r="BC110" t="s">
+      <c r="AS110" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3590,56 +3597,44 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C111" t="s">
-        <v>196</v>
-      </c>
-      <c r="AH111" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM111" t="s">
+        <v>200</v>
+      </c>
+      <c r="T111" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ111" t="s">
         <v>64</v>
       </c>
       <c r="BC111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="112" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="C112" t="s">
-        <v>196</v>
-      </c>
-      <c r="AW112" t="s">
+        <v>200</v>
+      </c>
+      <c r="BC112" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="113" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>111</v>
+      </c>
+      <c r="B113" t="s">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
-        <v>114</v>
-      </c>
       <c r="C113" t="s">
-        <v>196</v>
-      </c>
-      <c r="U113" t="s">
-        <v>64</v>
-      </c>
-      <c r="V113" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL113" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU113" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="BC113" t="s">
         <v>64</v>
@@ -3647,25 +3642,19 @@
     </row>
     <row r="114" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C114" t="s">
-        <v>196</v>
-      </c>
-      <c r="U114" t="s">
-        <v>64</v>
-      </c>
-      <c r="V114" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC114" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY114" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="AL114" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM114" t="s">
+        <v>76</v>
       </c>
       <c r="BC114" t="s">
         <v>64</v>
@@ -3673,21 +3662,18 @@
     </row>
     <row r="115" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C115" t="s">
-        <v>196</v>
-      </c>
-      <c r="U115" t="s">
-        <v>64</v>
-      </c>
-      <c r="V115" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC115" t="s">
+        <v>200</v>
+      </c>
+      <c r="AH115" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM115" t="s">
         <v>64</v>
       </c>
       <c r="BC115" t="s">
@@ -3696,44 +3682,38 @@
     </row>
     <row r="116" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C116" t="s">
-        <v>196</v>
-      </c>
-      <c r="U116" t="s">
-        <v>64</v>
-      </c>
-      <c r="V116" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA116" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL116" t="s">
+        <v>200</v>
+      </c>
+      <c r="AW116" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="117" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C117" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U117" t="s">
         <v>64</v>
       </c>
-      <c r="AC117" t="s">
+      <c r="V117" t="s">
         <v>64</v>
       </c>
       <c r="AL117" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU117" t="s">
         <v>64</v>
       </c>
       <c r="BC117" t="s">
@@ -3742,19 +3722,25 @@
     </row>
     <row r="118" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B118" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U118" t="s">
         <v>64</v>
       </c>
+      <c r="V118" t="s">
+        <v>64</v>
+      </c>
       <c r="AC118" t="s">
         <v>64</v>
+      </c>
+      <c r="AY118" t="s">
+        <v>63</v>
       </c>
       <c r="BC118" t="s">
         <v>64</v>
@@ -3762,32 +3748,44 @@
     </row>
     <row r="119" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
+        <v>123</v>
+      </c>
+      <c r="B119" t="s">
         <v>124</v>
       </c>
-      <c r="B119" t="s">
-        <v>126</v>
-      </c>
       <c r="C119" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U119" t="s">
         <v>64</v>
       </c>
+      <c r="V119" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC119" t="s">
+        <v>64</v>
+      </c>
       <c r="BC119" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="120" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C120" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U120" t="s">
+        <v>64</v>
+      </c>
+      <c r="V120" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA120" t="s">
         <v>64</v>
       </c>
       <c r="AL120" t="s">
@@ -3796,13 +3794,13 @@
     </row>
     <row r="121" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U121" t="s">
         <v>64</v>
@@ -3819,13 +3817,13 @@
     </row>
     <row r="122" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C122" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U122" t="s">
         <v>64</v>
@@ -3839,405 +3837,291 @@
     </row>
     <row r="123" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" t="s">
         <v>130</v>
       </c>
-      <c r="B123" t="s">
-        <v>132</v>
-      </c>
       <c r="C123" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U123" t="s">
         <v>64</v>
       </c>
-      <c r="AC123" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL123" t="s">
-        <v>64</v>
-      </c>
       <c r="BC123" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
     </row>
     <row r="124" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C124" t="s">
-        <v>196</v>
-      </c>
-      <c r="AV124" t="s">
+        <v>200</v>
+      </c>
+      <c r="U124" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL124" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="125" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C125" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="U125" t="s">
+        <v>64</v>
       </c>
       <c r="AC125" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL125" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC125" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="126" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B126" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C126" t="s">
-        <v>196</v>
-      </c>
-      <c r="O126" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>64</v>
-      </c>
-      <c r="V126" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA126" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK126" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY126" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="U126" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC126" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC126" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="127" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="C127" t="s">
-        <v>196</v>
-      </c>
-      <c r="AX127" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY127" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="U127" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC127" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL127" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC127" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="128" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="B128" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
       <c r="C128" t="s">
-        <v>196</v>
-      </c>
-      <c r="V128" t="s">
+        <v>200</v>
+      </c>
+      <c r="AV128" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="129" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="B129" t="s">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="C129" t="s">
-        <v>196</v>
-      </c>
-      <c r="AK129" t="s">
-        <v>76</v>
-      </c>
-      <c r="AY129" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="AC129" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="130" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="B130" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="C130" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="O130" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>64</v>
       </c>
       <c r="V130" t="s">
         <v>64</v>
       </c>
       <c r="AA130" t="s">
         <v>64</v>
+      </c>
+      <c r="AK130" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY130" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="131" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B131" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C131" t="s">
-        <v>196</v>
-      </c>
-      <c r="V131" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA131" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK131" t="s">
-        <v>76</v>
+        <v>200</v>
+      </c>
+      <c r="AX131" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY131" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="132" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B132" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C132" t="s">
-        <v>196</v>
-      </c>
-      <c r="AK132" t="s">
-        <v>76</v>
+        <v>200</v>
+      </c>
+      <c r="V132" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="133" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B133" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C133" t="s">
-        <v>196</v>
-      </c>
-      <c r="AX133" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="AK133" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY133" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="134" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>224</v>
       </c>
       <c r="C134" t="s">
-        <v>196</v>
-      </c>
-      <c r="L134" t="s">
-        <v>63</v>
-      </c>
-      <c r="U134" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD134" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM134" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP134" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR134" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ134" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="V134" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA134" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="135" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c r="B135" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="C135" t="s">
-        <v>196</v>
-      </c>
-      <c r="P135" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB135" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="V135" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA135" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK135" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="136" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>149</v>
+        <v>226</v>
       </c>
       <c r="B136" t="s">
-        <v>150</v>
+        <v>227</v>
       </c>
       <c r="C136" t="s">
-        <v>196</v>
-      </c>
-      <c r="H136" t="s">
-        <v>64</v>
-      </c>
-      <c r="N136" t="s">
-        <v>64</v>
-      </c>
-      <c r="X136" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD136" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG136" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP136" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ136" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="AK136" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="137" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B137" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C137" t="s">
-        <v>196</v>
-      </c>
-      <c r="E137" t="s">
-        <v>64</v>
-      </c>
-      <c r="F137" t="s">
-        <v>64</v>
-      </c>
-      <c r="H137" t="s">
-        <v>64</v>
-      </c>
-      <c r="I137" t="s">
-        <v>64</v>
-      </c>
-      <c r="K137" t="s">
-        <v>64</v>
-      </c>
-      <c r="M137" t="s">
-        <v>64</v>
-      </c>
-      <c r="N137" t="s">
-        <v>64</v>
-      </c>
-      <c r="P137" t="s">
-        <v>64</v>
-      </c>
-      <c r="R137" t="s">
-        <v>64</v>
-      </c>
-      <c r="U137" t="s">
-        <v>64</v>
-      </c>
-      <c r="V137" t="s">
-        <v>64</v>
-      </c>
-      <c r="X137" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB137" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD137" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG137" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM137" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP137" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR137" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU137" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ137" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="AX137" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="138" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>150</v>
+      </c>
+      <c r="B138" t="s">
         <v>151</v>
       </c>
-      <c r="B138" t="s">
-        <v>152</v>
-      </c>
       <c r="C138" t="s">
-        <v>196</v>
-      </c>
-      <c r="E138" t="s">
-        <v>64</v>
-      </c>
-      <c r="F138" t="s">
-        <v>64</v>
-      </c>
-      <c r="H138" t="s">
-        <v>64</v>
-      </c>
-      <c r="I138" t="s">
-        <v>64</v>
-      </c>
-      <c r="K138" t="s">
-        <v>64</v>
-      </c>
-      <c r="M138" t="s">
-        <v>64</v>
-      </c>
-      <c r="N138" t="s">
-        <v>64</v>
-      </c>
-      <c r="P138" t="s">
-        <v>64</v>
-      </c>
-      <c r="R138" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="L138" t="s">
+        <v>63</v>
       </c>
       <c r="U138" t="s">
         <v>64</v>
       </c>
-      <c r="V138" t="s">
-        <v>64</v>
-      </c>
-      <c r="X138" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z138" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB138" t="s">
-        <v>63</v>
-      </c>
       <c r="AD138" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG138" t="s">
         <v>64</v>
       </c>
       <c r="AM138" t="s">
@@ -4249,104 +4133,101 @@
       <c r="AR138" t="s">
         <v>64</v>
       </c>
-      <c r="AU138" t="s">
-        <v>64</v>
-      </c>
       <c r="AZ138" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="139" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B139" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C139" t="s">
-        <v>196</v>
-      </c>
-      <c r="E139" t="s">
-        <v>64</v>
-      </c>
-      <c r="F139" t="s">
-        <v>64</v>
-      </c>
-      <c r="H139" t="s">
-        <v>64</v>
-      </c>
-      <c r="I139" t="s">
-        <v>64</v>
-      </c>
-      <c r="M139" t="s">
-        <v>64</v>
-      </c>
-      <c r="N139" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="P139" t="s">
         <v>64</v>
       </c>
-      <c r="R139" t="s">
-        <v>64</v>
-      </c>
-      <c r="U139" t="s">
-        <v>64</v>
-      </c>
-      <c r="V139" t="s">
-        <v>64</v>
-      </c>
-      <c r="X139" t="s">
-        <v>64</v>
-      </c>
       <c r="AB139" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD139" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG139" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM139" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP139" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR139" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU139" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ139" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="140" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B140" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="C140" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC140" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="H140" t="s">
+        <v>64</v>
+      </c>
+      <c r="N140" t="s">
+        <v>64</v>
+      </c>
+      <c r="X140" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD140" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG140" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP140" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ140" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="141" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>155</v>
+        <v>230</v>
       </c>
       <c r="B141" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="C141" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="E141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F141" t="s">
+        <v>64</v>
+      </c>
+      <c r="H141" t="s">
+        <v>64</v>
+      </c>
+      <c r="I141" t="s">
+        <v>64</v>
+      </c>
+      <c r="K141" t="s">
+        <v>64</v>
+      </c>
+      <c r="M141" t="s">
+        <v>64</v>
+      </c>
+      <c r="N141" t="s">
+        <v>64</v>
+      </c>
+      <c r="P141" t="s">
+        <v>64</v>
+      </c>
+      <c r="R141" t="s">
+        <v>64</v>
+      </c>
+      <c r="U141" t="s">
+        <v>64</v>
+      </c>
+      <c r="V141" t="s">
+        <v>64</v>
       </c>
       <c r="X141" t="s">
         <v>64</v>
@@ -4354,25 +4235,100 @@
       <c r="AB141" t="s">
         <v>63</v>
       </c>
-      <c r="AC141" t="s">
-        <v>115</v>
+      <c r="AD141" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG141" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM141" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP141" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR141" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU141" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ141" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="142" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B142" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C142" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="E142" t="s">
+        <v>64</v>
+      </c>
+      <c r="F142" t="s">
+        <v>64</v>
+      </c>
+      <c r="H142" t="s">
+        <v>64</v>
+      </c>
+      <c r="I142" t="s">
+        <v>64</v>
+      </c>
+      <c r="K142" t="s">
+        <v>64</v>
+      </c>
+      <c r="M142" t="s">
+        <v>64</v>
       </c>
       <c r="N142" t="s">
         <v>64</v>
       </c>
-      <c r="AC142" t="s">
-        <v>64</v>
+      <c r="P142" t="s">
+        <v>64</v>
+      </c>
+      <c r="R142" t="s">
+        <v>64</v>
+      </c>
+      <c r="U142" t="s">
+        <v>64</v>
+      </c>
+      <c r="V142" t="s">
+        <v>64</v>
+      </c>
+      <c r="X142" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB142" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD142" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG142" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM142" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP142" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR142" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU142" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ142" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="143" spans="1:52" x14ac:dyDescent="0.3">
@@ -4380,112 +4336,166 @@
         <v>157</v>
       </c>
       <c r="B143" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C143" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="E143" t="s">
+        <v>64</v>
+      </c>
+      <c r="F143" t="s">
+        <v>64</v>
+      </c>
+      <c r="H143" t="s">
+        <v>64</v>
+      </c>
+      <c r="I143" t="s">
+        <v>64</v>
+      </c>
+      <c r="M143" t="s">
+        <v>64</v>
+      </c>
+      <c r="N143" t="s">
+        <v>64</v>
+      </c>
+      <c r="P143" t="s">
+        <v>64</v>
+      </c>
+      <c r="R143" t="s">
+        <v>64</v>
+      </c>
+      <c r="U143" t="s">
+        <v>64</v>
+      </c>
+      <c r="V143" t="s">
+        <v>64</v>
+      </c>
+      <c r="X143" t="s">
+        <v>64</v>
       </c>
       <c r="AB143" t="s">
         <v>63</v>
       </c>
-      <c r="AC143" t="s">
-        <v>115</v>
+      <c r="AD143" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG143" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM143" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP143" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR143" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU143" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ143" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="144" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="C144" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB144" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="AC144" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="145" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="B145" t="s">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="C145" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="X145" t="s">
         <v>64</v>
       </c>
       <c r="AB145" t="s">
         <v>63</v>
+      </c>
+      <c r="AC145" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="146" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B146" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C146" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N146" t="s">
         <v>64</v>
       </c>
-      <c r="X146" t="s">
+      <c r="AC146" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="147" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B147" t="s">
-        <v>231</v>
+        <v>163</v>
       </c>
       <c r="C147" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AB147" t="s">
         <v>63</v>
+      </c>
+      <c r="AC147" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="148" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B148" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C148" t="s">
-        <v>196</v>
-      </c>
-      <c r="N148" t="s">
-        <v>64</v>
-      </c>
-      <c r="X148" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC148" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="AB148" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="149" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="B149" t="s">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C149" t="s">
-        <v>196</v>
-      </c>
-      <c r="V149" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="X149" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB149" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="150" spans="1:55" x14ac:dyDescent="0.3">
@@ -4493,302 +4503,367 @@
         <v>168</v>
       </c>
       <c r="B150" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C150" t="s">
-        <v>196</v>
-      </c>
-      <c r="AA150" t="s">
+        <v>200</v>
+      </c>
+      <c r="N150" t="s">
+        <v>64</v>
+      </c>
+      <c r="X150" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="151" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="C151" t="s">
-        <v>196</v>
-      </c>
-      <c r="V151" t="s">
-        <v>64</v>
+        <v>200</v>
+      </c>
+      <c r="AB151" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="152" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B152" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C152" t="s">
-        <v>196</v>
-      </c>
-      <c r="H152" t="s">
-        <v>64</v>
-      </c>
-      <c r="P152" t="s">
+        <v>200</v>
+      </c>
+      <c r="N152" t="s">
         <v>64</v>
       </c>
       <c r="X152" t="s">
         <v>64</v>
       </c>
-      <c r="AB152" t="s">
-        <v>63</v>
-      </c>
       <c r="AC152" t="s">
         <v>64</v>
-      </c>
-      <c r="AD152" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG152" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP152" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR152" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ152" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="153" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B153" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C153" t="s">
-        <v>196</v>
-      </c>
-      <c r="E153" t="s">
-        <v>64</v>
-      </c>
-      <c r="F153" t="s">
-        <v>64</v>
-      </c>
-      <c r="T153" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH153" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ153" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX153" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY153" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC153" t="s">
+        <v>200</v>
+      </c>
+      <c r="V153" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="154" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B154" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="C154" t="s">
-        <v>196</v>
-      </c>
-      <c r="AU154" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA154" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="155" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C155" t="s">
-        <v>196</v>
-      </c>
-      <c r="N155" t="s">
-        <v>64</v>
-      </c>
-      <c r="X155" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU155" t="s">
-        <v>76</v>
+        <v>200</v>
+      </c>
+      <c r="V155" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="156" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B156" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C156" t="s">
-        <v>196</v>
-      </c>
-      <c r="N156" t="s">
+        <v>200</v>
+      </c>
+      <c r="H156" t="s">
+        <v>64</v>
+      </c>
+      <c r="P156" t="s">
+        <v>64</v>
+      </c>
+      <c r="X156" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB156" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC156" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD156" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG156" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP156" t="s">
+        <v>64</v>
+      </c>
+      <c r="AR156" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ156" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="157" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B157" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>196</v>
-      </c>
-      <c r="N157" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU157" t="s">
+        <v>200</v>
+      </c>
+      <c r="E157" t="s">
+        <v>64</v>
+      </c>
+      <c r="F157" t="s">
+        <v>64</v>
+      </c>
+      <c r="T157" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH157" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ157" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX157" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY157" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC157" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="158" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B158" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="C158" t="s">
-        <v>196</v>
-      </c>
-      <c r="U158" t="s">
-        <v>64</v>
-      </c>
-      <c r="V158" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA158" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL158" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC158" t="s">
+        <v>200</v>
+      </c>
+      <c r="AU158" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="159" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C159" t="s">
-        <v>196</v>
-      </c>
-      <c r="U159" t="s">
-        <v>64</v>
-      </c>
-      <c r="V159" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC159" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="N159" t="s">
+        <v>64</v>
+      </c>
+      <c r="X159" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU159" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="160" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B160" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="C160" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N160" t="s">
         <v>63</v>
-      </c>
-      <c r="AC160" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC160" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="161" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B161" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C161" t="s">
-        <v>196</v>
-      </c>
-      <c r="AK161" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL161" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX161" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY161" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC161" t="s">
+        <v>200</v>
+      </c>
+      <c r="N161" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU161" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="162" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="B162" t="s">
-        <v>235</v>
+        <v>191</v>
       </c>
       <c r="C162" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="U162" t="s">
+        <v>64</v>
+      </c>
+      <c r="V162" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA162" t="s">
+        <v>64</v>
       </c>
       <c r="AL162" t="s">
         <v>64</v>
       </c>
-      <c r="AX162" t="s">
+      <c r="BC162" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="163" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C163" t="s">
+        <v>200</v>
+      </c>
+      <c r="U163" t="s">
+        <v>64</v>
+      </c>
+      <c r="V163" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC163" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="164" spans="1:55" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>196</v>
       </c>
-      <c r="V163" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA163" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK163" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL163" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX163" t="s">
+      <c r="B164" t="s">
+        <v>237</v>
+      </c>
+      <c r="C164" t="s">
+        <v>200</v>
+      </c>
+      <c r="N164" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC164" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC164" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="165" spans="1:55" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>196</v>
+      </c>
+      <c r="B165" t="s">
+        <v>197</v>
+      </c>
+      <c r="C165" t="s">
+        <v>200</v>
+      </c>
+      <c r="AK165" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL165" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX165" t="s">
+        <v>64</v>
+      </c>
+      <c r="AY165" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC165" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="166" spans="1:55" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>238</v>
+      </c>
+      <c r="B166" t="s">
+        <v>239</v>
+      </c>
+      <c r="C166" t="s">
+        <v>200</v>
+      </c>
+      <c r="AL166" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX166" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="167" spans="1:55" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>198</v>
+      </c>
+      <c r="B167" t="s">
+        <v>199</v>
+      </c>
+      <c r="C167" t="s">
+        <v>200</v>
+      </c>
+      <c r="V167" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA167" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK167" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL167" t="s">
+        <v>64</v>
+      </c>
+      <c r="AX167" t="s">
         <v>64</v>
       </c>
     </row>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617093D2-AA81-47B9-8333-F96E1B3C34AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCE874B-3F41-45F5-AFFA-4ED0FCAAAB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
@@ -278,8 +278,7 @@
     <t>Den Gode Blanketservice</t>
   </si>
   <si>
-    <t>DGB (0.91_x000D_
-0.91)</t>
+    <t>DGB (0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCE874B-3F41-45F5-AFFA-4ED0FCAAAB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FE8305-A165-4011-8FA1-85619198234D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 10-04-2026'!$A$1:$BH$167</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 14-04-2026'!$A$1:$BH$167</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C845BEC0-ACD0-4AE7-9DAF-36066004ED58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE099FA-7C48-433C-B35A-0F147D9A1F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 24-04-2026'!$A$1:$BK$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 27-04-2026'!$A$1:$BK$168</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="245">
   <si>
     <t>Standard</t>
   </si>
@@ -250,11 +250,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
-  </si>
-  <si>
-    <t>CareCommunication (5.0_x000D_
-5.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Care Measurement Report</t>
@@ -1104,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BK170"/>
+  <dimension ref="A1:BK168"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.3">
@@ -1394,68 +1390,110 @@
       <c r="C6" t="s">
         <v>65</v>
       </c>
+      <c r="L6" t="s">
+        <v>66</v>
+      </c>
       <c r="V6" t="s">
         <v>67</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
         <v>65</v>
       </c>
-      <c r="L7" t="s">
-        <v>66</v>
-      </c>
-      <c r="V7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>66</v>
+      <c r="W7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" t="s">
         <v>78</v>
       </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>67</v>
+      <c r="O8" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U8" t="s">
+        <v>67</v>
+      </c>
+      <c r="V8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>67</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>67</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>67</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
         <v>65</v>
       </c>
-      <c r="G9" t="s">
-        <v>67</v>
-      </c>
       <c r="J9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="U9" t="s">
         <v>67</v>
@@ -1475,9 +1513,6 @@
       <c r="AG9" t="s">
         <v>67</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>67</v>
-      </c>
       <c r="AQ9" t="s">
         <v>67</v>
       </c>
@@ -1490,72 +1525,33 @@
       <c r="AW9" t="s">
         <v>67</v>
       </c>
+      <c r="AY9" t="s">
+        <v>67</v>
+      </c>
       <c r="BC9" t="s">
         <v>67</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>67</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
         <v>65</v>
       </c>
-      <c r="J10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U10" t="s">
-        <v>67</v>
-      </c>
-      <c r="V10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>67</v>
-      </c>
       <c r="AQ10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AY10" t="s">
-        <v>67</v>
-      </c>
-      <c r="BC10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
         <v>65</v>
@@ -1566,35 +1562,35 @@
     </row>
     <row r="12" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>65</v>
       </c>
-      <c r="AQ12" t="s">
+      <c r="V12" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
         <v>65</v>
       </c>
-      <c r="V13" t="s">
+      <c r="AY13" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
         <v>91</v>
@@ -1602,16 +1598,16 @@
       <c r="C14" t="s">
         <v>65</v>
       </c>
-      <c r="AY14" t="s">
+      <c r="V14" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
         <v>65</v>
@@ -1622,10 +1618,10 @@
     </row>
     <row r="16" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
         <v>65</v>
@@ -1636,10 +1632,10 @@
     </row>
     <row r="17" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
         <v>65</v>
@@ -1650,91 +1646,100 @@
     </row>
     <row r="18" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
         <v>65</v>
       </c>
+      <c r="U18" t="s">
+        <v>67</v>
+      </c>
       <c r="V18" t="s">
         <v>67</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>67</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE18" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
         <v>65</v>
       </c>
-      <c r="U19" t="s">
-        <v>67</v>
-      </c>
-      <c r="V19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>67</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>67</v>
-      </c>
-      <c r="BD19" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE19" t="s">
+      <c r="Z19" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
         <v>65</v>
       </c>
-      <c r="Z20" t="s">
-        <v>66</v>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
         <v>104</v>
@@ -1742,39 +1747,30 @@
       <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="D21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>67</v>
-      </c>
-      <c r="BK21" t="s">
+      <c r="BH21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
         <v>65</v>
       </c>
-      <c r="BH22" t="s">
-        <v>67</v>
+      <c r="T22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
         <v>65</v>
@@ -1785,69 +1781,84 @@
     </row>
     <row r="24" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
       </c>
-      <c r="T24" t="s">
-        <v>66</v>
+      <c r="W24" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="W25" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU25" t="s">
-        <v>67</v>
+      <c r="T25" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
       </c>
-      <c r="T26" t="s">
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI26" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
         <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>66</v>
+        <v>78</v>
+      </c>
+      <c r="S27" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>78</v>
+      </c>
+      <c r="BD27" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK27" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B28" t="s">
         <v>117</v>
@@ -1856,53 +1867,41 @@
         <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="S28" t="s">
         <v>67</v>
       </c>
-      <c r="AF28" t="s">
-        <v>79</v>
+      <c r="AI28" t="s">
+        <v>67</v>
       </c>
       <c r="AN28" t="s">
-        <v>79</v>
-      </c>
-      <c r="BD28" t="s">
-        <v>67</v>
-      </c>
-      <c r="BK28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO28" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
         <v>65</v>
       </c>
-      <c r="D29" t="s">
-        <v>67</v>
-      </c>
-      <c r="S29" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>67</v>
-      </c>
-      <c r="AO29" t="s">
+      <c r="V29" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD29" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
         <v>120</v>
@@ -1910,39 +1909,36 @@
       <c r="C30" t="s">
         <v>65</v>
       </c>
+      <c r="U30" t="s">
+        <v>67</v>
+      </c>
       <c r="V30" t="s">
         <v>67</v>
       </c>
+      <c r="AB30" t="s">
+        <v>67</v>
+      </c>
       <c r="AD30" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
         <v>65</v>
       </c>
-      <c r="U31" t="s">
-        <v>67</v>
-      </c>
       <c r="V31" t="s">
         <v>67</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
         <v>124</v>
@@ -1950,16 +1946,25 @@
       <c r="C32" t="s">
         <v>65</v>
       </c>
+      <c r="U32" t="s">
+        <v>67</v>
+      </c>
       <c r="V32" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD32" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
         <v>65</v>
@@ -1968,9 +1973,6 @@
         <v>67</v>
       </c>
       <c r="V33" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB33" t="s">
         <v>67</v>
       </c>
       <c r="AD33" t="s">
@@ -1979,7 +1981,7 @@
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
         <v>127</v>
@@ -1993,16 +1995,13 @@
       <c r="V34" t="s">
         <v>67</v>
       </c>
-      <c r="AD34" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="35" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
         <v>65</v>
@@ -2010,16 +2009,16 @@
       <c r="U35" t="s">
         <v>67</v>
       </c>
-      <c r="V35" t="s">
+      <c r="AD35" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
         <v>65</v>
@@ -2033,7 +2032,7 @@
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
         <v>132</v>
@@ -2044,13 +2043,10 @@
       <c r="U37" t="s">
         <v>67</v>
       </c>
-      <c r="AD37" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s">
         <v>133</v>
@@ -2064,24 +2060,27 @@
     </row>
     <row r="39" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C39" t="s">
         <v>65</v>
       </c>
       <c r="U39" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD39" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
         <v>65</v>
@@ -2095,7 +2094,7 @@
     </row>
     <row r="41" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B41" t="s">
         <v>138</v>
@@ -2107,29 +2106,26 @@
         <v>67</v>
       </c>
       <c r="AD41" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
         <v>65</v>
       </c>
-      <c r="U42" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>122</v>
+      <c r="O42" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B43" t="s">
         <v>141</v>
@@ -2137,27 +2133,33 @@
       <c r="C43" t="s">
         <v>65</v>
       </c>
-      <c r="O43" t="s">
+      <c r="AB43" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C44" t="s">
         <v>65</v>
       </c>
-      <c r="AB44" t="s">
-        <v>67</v>
+      <c r="AS44" t="s">
+        <v>67</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>67</v>
+      </c>
+      <c r="BI44" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
         <v>144</v>
@@ -2165,59 +2167,53 @@
       <c r="C45" t="s">
         <v>65</v>
       </c>
-      <c r="AS45" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX45" t="s">
-        <v>67</v>
+      <c r="O45" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>78</v>
       </c>
       <c r="BI45" t="s">
         <v>66</v>
+      </c>
+      <c r="BK45" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s">
         <v>65</v>
       </c>
-      <c r="O46" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA46" t="s">
-        <v>79</v>
-      </c>
-      <c r="BI46" t="s">
-        <v>66</v>
-      </c>
-      <c r="BK46" t="s">
+      <c r="G46" t="s">
+        <v>67</v>
+      </c>
+      <c r="AV46" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
         <v>65</v>
       </c>
-      <c r="G47" t="s">
-        <v>67</v>
-      </c>
-      <c r="AV47" t="s">
+      <c r="J47" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B48" t="s">
         <v>149</v>
@@ -2231,55 +2227,73 @@
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C49" t="s">
         <v>65</v>
       </c>
-      <c r="J49" t="s">
-        <v>67</v>
+      <c r="BG49" t="s">
+        <v>67</v>
+      </c>
+      <c r="BJ49" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
         <v>65</v>
       </c>
-      <c r="BG50" t="s">
-        <v>67</v>
-      </c>
-      <c r="BJ50" t="s">
+      <c r="X50" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP50" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B51" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
         <v>65</v>
       </c>
-      <c r="X51" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP51" t="s">
+      <c r="L51" t="s">
+        <v>66</v>
+      </c>
+      <c r="U51" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB51" t="s">
+        <v>66</v>
+      </c>
+      <c r="BI51" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B52" t="s">
         <v>156</v>
@@ -2287,54 +2301,57 @@
       <c r="C52" t="s">
         <v>65</v>
       </c>
-      <c r="L52" t="s">
-        <v>66</v>
-      </c>
-      <c r="U52" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE52" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR52" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT52" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB52" t="s">
-        <v>66</v>
-      </c>
-      <c r="BI52" t="s">
+      <c r="P52" t="s">
+        <v>67</v>
+      </c>
+      <c r="R52" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC52" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s">
         <v>65</v>
       </c>
-      <c r="P53" t="s">
-        <v>67</v>
-      </c>
-      <c r="R53" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC53" t="s">
+      <c r="H53" t="s">
+        <v>67</v>
+      </c>
+      <c r="N53" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR53" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW53" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB53" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B54" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
         <v>65</v>
@@ -2345,9 +2362,21 @@
       <c r="N54" t="s">
         <v>67</v>
       </c>
+      <c r="P54" t="s">
+        <v>67</v>
+      </c>
+      <c r="U54" t="s">
+        <v>67</v>
+      </c>
+      <c r="V54" t="s">
+        <v>67</v>
+      </c>
       <c r="Y54" t="s">
         <v>67</v>
       </c>
+      <c r="AC54" t="s">
+        <v>66</v>
+      </c>
       <c r="AE54" t="s">
         <v>67</v>
       </c>
@@ -2355,6 +2384,9 @@
         <v>67</v>
       </c>
       <c r="AR54" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT54" t="s">
         <v>67</v>
       </c>
       <c r="AW54" t="s">
@@ -2366,10 +2398,10 @@
     </row>
     <row r="55" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
         <v>65</v>
@@ -2416,71 +2448,35 @@
     </row>
     <row r="56" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C56" t="s">
         <v>65</v>
       </c>
-      <c r="H56" t="s">
-        <v>67</v>
-      </c>
-      <c r="N56" t="s">
-        <v>67</v>
-      </c>
-      <c r="P56" t="s">
-        <v>67</v>
-      </c>
-      <c r="U56" t="s">
-        <v>67</v>
-      </c>
-      <c r="V56" t="s">
-        <v>67</v>
-      </c>
       <c r="Y56" t="s">
         <v>67</v>
-      </c>
-      <c r="AC56" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE56" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH56" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR56" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT56" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW56" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB56" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
         <v>65</v>
       </c>
-      <c r="Y57" t="s">
+      <c r="N57" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B58" t="s">
         <v>167</v>
@@ -2488,92 +2484,92 @@
       <c r="C58" t="s">
         <v>65</v>
       </c>
-      <c r="N58" t="s">
+      <c r="R58" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C59" t="s">
         <v>65</v>
       </c>
-      <c r="R59" t="s">
+      <c r="Y59" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B60" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C60" t="s">
         <v>65</v>
       </c>
-      <c r="Y60" t="s">
+      <c r="E60" t="s">
+        <v>67</v>
+      </c>
+      <c r="F60" t="s">
+        <v>67</v>
+      </c>
+      <c r="I60" t="s">
+        <v>67</v>
+      </c>
+      <c r="M60" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
         <v>65</v>
       </c>
-      <c r="E61" t="s">
-        <v>67</v>
-      </c>
-      <c r="F61" t="s">
-        <v>67</v>
-      </c>
-      <c r="I61" t="s">
-        <v>67</v>
-      </c>
-      <c r="M61" t="s">
+      <c r="N61" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C62" t="s">
         <v>65</v>
       </c>
-      <c r="N62" t="s">
+      <c r="Y62" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B63" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C63" t="s">
         <v>65</v>
       </c>
-      <c r="Y63" t="s">
+      <c r="V63" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B64" t="s">
         <v>178</v>
@@ -2581,100 +2577,115 @@
       <c r="C64" t="s">
         <v>65</v>
       </c>
-      <c r="V64" t="s">
+      <c r="AB64" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B65" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C65" t="s">
         <v>65</v>
       </c>
-      <c r="AB65" t="s">
+      <c r="V65" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C66" t="s">
         <v>65</v>
       </c>
-      <c r="V66" t="s">
-        <v>67</v>
+      <c r="H66" t="s">
+        <v>67</v>
+      </c>
+      <c r="K66" t="s">
+        <v>67</v>
+      </c>
+      <c r="N66" t="s">
+        <v>67</v>
+      </c>
+      <c r="P66" t="s">
+        <v>67</v>
+      </c>
+      <c r="R66" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE66" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR66" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT66" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW66" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB66" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B67" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C67" t="s">
         <v>65</v>
       </c>
-      <c r="H67" t="s">
-        <v>67</v>
-      </c>
-      <c r="K67" t="s">
-        <v>67</v>
-      </c>
-      <c r="N67" t="s">
-        <v>67</v>
-      </c>
-      <c r="P67" t="s">
-        <v>67</v>
-      </c>
-      <c r="R67" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD67" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE67" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH67" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN67" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR67" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT67" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW67" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB67" t="s">
-        <v>66</v>
+      <c r="D67" t="s">
+        <v>67</v>
+      </c>
+      <c r="T67" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>67</v>
+      </c>
+      <c r="BH67" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK67" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
         <v>185</v>
@@ -2682,51 +2693,39 @@
       <c r="C68" t="s">
         <v>65</v>
       </c>
-      <c r="D68" t="s">
-        <v>67</v>
-      </c>
-      <c r="T68" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI68" t="s">
-        <v>67</v>
-      </c>
-      <c r="BH68" t="s">
-        <v>67</v>
-      </c>
-      <c r="BK68" t="s">
-        <v>67</v>
+      <c r="X68" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP68" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C69" t="s">
         <v>65</v>
       </c>
-      <c r="X69" t="s">
-        <v>66</v>
-      </c>
-      <c r="AP69" t="s">
-        <v>66</v>
+      <c r="Y69" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B70" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C70" t="s">
         <v>65</v>
+      </c>
+      <c r="N70" t="s">
+        <v>67</v>
       </c>
       <c r="Y70" t="s">
         <v>67</v>
@@ -2734,16 +2733,13 @@
     </row>
     <row r="71" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B71" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C71" t="s">
         <v>65</v>
-      </c>
-      <c r="N71" t="s">
-        <v>67</v>
       </c>
       <c r="Y71" t="s">
         <v>67</v>
@@ -2751,21 +2747,21 @@
     </row>
     <row r="72" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C72" t="s">
         <v>65</v>
       </c>
-      <c r="Y72" t="s">
+      <c r="N72" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B73" t="s">
         <v>194</v>
@@ -2776,30 +2772,36 @@
       <c r="N73" t="s">
         <v>67</v>
       </c>
+      <c r="Y73" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="74" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C74" t="s">
         <v>65</v>
       </c>
-      <c r="N74" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y74" t="s">
+      <c r="U74" t="s">
+        <v>67</v>
+      </c>
+      <c r="V74" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB74" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C75" t="s">
         <v>65</v>
@@ -2808,225 +2810,231 @@
         <v>67</v>
       </c>
       <c r="V75" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB75" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C76" t="s">
         <v>65</v>
       </c>
-      <c r="U76" t="s">
-        <v>67</v>
-      </c>
-      <c r="V76" t="s">
-        <v>67</v>
+      <c r="O76" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C77" t="s">
         <v>65</v>
       </c>
-      <c r="O77" t="s">
-        <v>66</v>
+      <c r="AA77" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C78" t="s">
         <v>65</v>
       </c>
-      <c r="AA78" t="s">
-        <v>79</v>
+      <c r="O78" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>65</v>
-      </c>
-      <c r="O79" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="L79" t="s">
+        <v>66</v>
+      </c>
+      <c r="V79" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE79" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C80" t="s">
-        <v>206</v>
-      </c>
-      <c r="L80" t="s">
-        <v>66</v>
-      </c>
-      <c r="V80" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE80" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="M80" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM80" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU80" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ80" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA80" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE80" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C81" t="s">
-        <v>206</v>
-      </c>
-      <c r="M81" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>66</v>
-      </c>
-      <c r="AL81" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM81" t="s">
-        <v>66</v>
-      </c>
-      <c r="AU81" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ81" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA81" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE81" t="s">
+        <v>205</v>
+      </c>
+      <c r="U81" t="s">
+        <v>67</v>
+      </c>
+      <c r="V81" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ81" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR81" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C82" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U82" t="s">
-        <v>67</v>
-      </c>
-      <c r="V82" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ82" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR82" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B83" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
-      </c>
-      <c r="U83" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="L83" t="s">
+        <v>66</v>
+      </c>
+      <c r="V83" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE83" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C84" t="s">
-        <v>206</v>
-      </c>
-      <c r="V84" t="s">
+        <v>205</v>
+      </c>
+      <c r="W84" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU84" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="B85" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="C85" t="s">
-        <v>206</v>
-      </c>
-      <c r="L85" t="s">
-        <v>66</v>
-      </c>
-      <c r="V85" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE85" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="AZ85" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE85" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="B86" t="s">
+        <v>209</v>
+      </c>
+      <c r="C86" t="s">
+        <v>205</v>
+      </c>
+      <c r="BA86" t="s">
         <v>78</v>
       </c>
-      <c r="C86" t="s">
-        <v>206</v>
-      </c>
-      <c r="W86" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU86" t="s">
+      <c r="BE86" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B87" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C87" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>66</v>
       </c>
       <c r="AZ87" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA87" t="s">
         <v>67</v>
       </c>
       <c r="BE87" t="s">
@@ -3035,59 +3043,164 @@
     </row>
     <row r="88" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B88" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C88" t="s">
-        <v>206</v>
-      </c>
-      <c r="BA88" t="s">
-        <v>79</v>
+        <v>205</v>
+      </c>
+      <c r="G88" t="s">
+        <v>67</v>
+      </c>
+      <c r="J88" t="s">
+        <v>78</v>
+      </c>
+      <c r="O88" t="s">
+        <v>67</v>
+      </c>
+      <c r="U88" t="s">
+        <v>67</v>
+      </c>
+      <c r="V88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AV88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW88" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY88" t="s">
+        <v>67</v>
       </c>
       <c r="BE88" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="BI88" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ88" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL89" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ89" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA89" t="s">
+        <v>205</v>
+      </c>
+      <c r="G89" t="s">
+        <v>67</v>
+      </c>
+      <c r="J89" t="s">
+        <v>78</v>
+      </c>
+      <c r="O89" t="s">
+        <v>67</v>
+      </c>
+      <c r="U89" t="s">
+        <v>67</v>
+      </c>
+      <c r="V89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AV89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW89" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY89" t="s">
+        <v>67</v>
+      </c>
+      <c r="BD89" t="s">
         <v>67</v>
       </c>
       <c r="BE89" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="BI89" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ89" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>212</v>
+        <v>81</v>
       </c>
       <c r="B90" t="s">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G90" t="s">
         <v>67</v>
       </c>
       <c r="J90" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O90" t="s">
         <v>67</v>
@@ -3146,189 +3259,75 @@
     </row>
     <row r="91" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B91" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>206</v>
-      </c>
-      <c r="G91" t="s">
-        <v>67</v>
-      </c>
-      <c r="J91" t="s">
-        <v>79</v>
-      </c>
-      <c r="O91" t="s">
-        <v>67</v>
-      </c>
-      <c r="U91" t="s">
-        <v>67</v>
-      </c>
-      <c r="V91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC91" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ91" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="AQ91" t="s">
         <v>67</v>
-      </c>
-      <c r="AR91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AV91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW91" t="s">
-        <v>67</v>
-      </c>
-      <c r="AY91" t="s">
-        <v>67</v>
-      </c>
-      <c r="BD91" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE91" t="s">
-        <v>66</v>
-      </c>
-      <c r="BI91" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ91" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>206</v>
-      </c>
-      <c r="G92" t="s">
-        <v>67</v>
-      </c>
-      <c r="J92" t="s">
-        <v>79</v>
-      </c>
-      <c r="O92" t="s">
-        <v>67</v>
-      </c>
-      <c r="U92" t="s">
-        <v>67</v>
-      </c>
-      <c r="V92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC92" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ92" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="AQ92" t="s">
         <v>67</v>
-      </c>
-      <c r="AR92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AV92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW92" t="s">
-        <v>67</v>
-      </c>
-      <c r="AY92" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE92" t="s">
-        <v>66</v>
-      </c>
-      <c r="BI92" t="s">
-        <v>66</v>
-      </c>
-      <c r="BJ92" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B93" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="C93" t="s">
-        <v>206</v>
-      </c>
-      <c r="AQ93" t="s">
+        <v>205</v>
+      </c>
+      <c r="V93" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD93" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B94" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C94" t="s">
-        <v>206</v>
-      </c>
-      <c r="AQ94" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="V94" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B95" t="s">
-        <v>214</v>
+        <v>90</v>
       </c>
       <c r="C95" t="s">
-        <v>206</v>
-      </c>
-      <c r="V95" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="AD95" t="s">
         <v>67</v>
@@ -3336,70 +3335,76 @@
     </row>
     <row r="96" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B96" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C96" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V96" t="s">
         <v>67</v>
       </c>
+      <c r="Y96" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB96" t="s">
+        <v>67</v>
+      </c>
       <c r="AC96" t="s">
         <v>66</v>
+      </c>
+      <c r="AD96" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="97" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>90</v>
+        <v>214</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>215</v>
       </c>
       <c r="C97" t="s">
-        <v>206</v>
-      </c>
-      <c r="AD97" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="V97" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="C98" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V98" t="s">
         <v>67</v>
       </c>
-      <c r="Y98" t="s">
-        <v>67</v>
-      </c>
       <c r="AB98" t="s">
         <v>67</v>
       </c>
       <c r="AC98" t="s">
         <v>66</v>
-      </c>
-      <c r="AD98" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="99" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>93</v>
       </c>
       <c r="C99" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V99" t="s">
         <v>67</v>
@@ -3410,151 +3415,148 @@
     </row>
     <row r="100" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="B100" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="C100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V100" t="s">
         <v>67</v>
       </c>
-      <c r="AB100" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC100" t="s">
-        <v>66</v>
+      <c r="AD100" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="101" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B101" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C101" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V101" t="s">
         <v>67</v>
-      </c>
-      <c r="AC101" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="102" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C102" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="H102" t="s">
+        <v>67</v>
       </c>
       <c r="V102" t="s">
         <v>67</v>
       </c>
+      <c r="Y102" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB102" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>66</v>
+      </c>
       <c r="AD102" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG102" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ102" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR102" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT102" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY102" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="103" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="C103" t="s">
-        <v>206</v>
-      </c>
-      <c r="V103" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="AM103" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE103" t="s">
+        <v>67</v>
+      </c>
+      <c r="BF103" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="104" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C104" t="s">
-        <v>206</v>
-      </c>
-      <c r="H104" t="s">
-        <v>67</v>
-      </c>
-      <c r="V104" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y104" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB104" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC104" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD104" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG104" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ104" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR104" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT104" t="s">
-        <v>67</v>
-      </c>
-      <c r="AY104" t="s">
+        <v>205</v>
+      </c>
+      <c r="E104" t="s">
+        <v>67</v>
+      </c>
+      <c r="F104" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE104" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>101</v>
+        <v>219</v>
       </c>
       <c r="B105" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C105" t="s">
-        <v>206</v>
-      </c>
-      <c r="AM105" t="s">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="BE105" t="s">
         <v>67</v>
-      </c>
-      <c r="BF105" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C106" t="s">
-        <v>206</v>
-      </c>
-      <c r="E106" t="s">
-        <v>67</v>
-      </c>
-      <c r="F106" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="AM106" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>78</v>
       </c>
       <c r="BE106" t="s">
         <v>67</v>
@@ -3562,47 +3564,53 @@
     </row>
     <row r="107" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="C107" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BE107" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>206</v>
-      </c>
-      <c r="AM108" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN108" t="s">
-        <v>79</v>
+        <v>205</v>
+      </c>
+      <c r="T108" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK108" t="s">
+        <v>67</v>
       </c>
       <c r="BE108" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C109" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="T109" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK109" t="s">
+        <v>67</v>
       </c>
       <c r="BE109" t="s">
         <v>66</v>
@@ -3610,33 +3618,30 @@
     </row>
     <row r="110" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C110" t="s">
-        <v>206</v>
-      </c>
-      <c r="T110" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK110" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE110" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="W110" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU110" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T111" t="s">
         <v>66</v>
@@ -3650,50 +3655,47 @@
     </row>
     <row r="112" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
       <c r="C112" t="s">
-        <v>206</v>
-      </c>
-      <c r="W112" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU112" t="s">
+        <v>205</v>
+      </c>
+      <c r="BE112" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="113" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C113" t="s">
-        <v>206</v>
-      </c>
-      <c r="T113" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK113" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="BE113" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>222</v>
+        <v>116</v>
       </c>
       <c r="C114" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="AM114" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN114" t="s">
+        <v>78</v>
       </c>
       <c r="BE114" t="s">
         <v>67</v>
@@ -3701,13 +3703,19 @@
     </row>
     <row r="115" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C115" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="AI115" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN115" t="s">
+        <v>67</v>
       </c>
       <c r="BE115" t="s">
         <v>67</v>
@@ -3715,38 +3723,38 @@
     </row>
     <row r="116" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B116" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C116" t="s">
-        <v>206</v>
-      </c>
-      <c r="AM116" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN116" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE116" t="s">
+        <v>205</v>
+      </c>
+      <c r="AY116" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="117" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C117" t="s">
-        <v>206</v>
-      </c>
-      <c r="AI117" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN117" t="s">
+        <v>205</v>
+      </c>
+      <c r="U117" t="s">
+        <v>67</v>
+      </c>
+      <c r="V117" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM117" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW117" t="s">
         <v>67</v>
       </c>
       <c r="BE117" t="s">
@@ -3755,27 +3763,39 @@
     </row>
     <row r="118" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C118" t="s">
-        <v>206</v>
-      </c>
-      <c r="AY118" t="s">
+        <v>205</v>
+      </c>
+      <c r="U118" t="s">
+        <v>67</v>
+      </c>
+      <c r="V118" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD118" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA118" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE118" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C119" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U119" t="s">
         <v>67</v>
@@ -3783,10 +3803,7 @@
       <c r="V119" t="s">
         <v>67</v>
       </c>
-      <c r="AM119" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW119" t="s">
+      <c r="AD119" t="s">
         <v>67</v>
       </c>
       <c r="BE119" t="s">
@@ -3795,13 +3812,13 @@
     </row>
     <row r="120" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C120" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U120" t="s">
         <v>67</v>
@@ -3809,33 +3826,30 @@
       <c r="V120" t="s">
         <v>67</v>
       </c>
-      <c r="AD120" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA120" t="s">
-        <v>66</v>
-      </c>
-      <c r="BE120" t="s">
+      <c r="AB120" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM120" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C121" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U121" t="s">
         <v>67</v>
       </c>
-      <c r="V121" t="s">
-        <v>67</v>
-      </c>
       <c r="AD121" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM121" t="s">
         <v>67</v>
       </c>
       <c r="BE121" t="s">
@@ -3844,605 +3858,611 @@
     </row>
     <row r="122" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C122" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U122" t="s">
         <v>67</v>
       </c>
-      <c r="V122" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB122" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM122" t="s">
+      <c r="AD122" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE122" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C123" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U123" t="s">
         <v>67</v>
       </c>
-      <c r="AD123" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM123" t="s">
-        <v>67</v>
-      </c>
       <c r="BE123" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="124" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C124" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U124" t="s">
         <v>67</v>
       </c>
-      <c r="AD124" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE124" t="s">
+      <c r="AM124" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="125" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B125" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C125" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U125" t="s">
         <v>67</v>
       </c>
+      <c r="AD125" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM125" t="s">
+        <v>67</v>
+      </c>
       <c r="BE125" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C126" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U126" t="s">
         <v>67</v>
       </c>
-      <c r="AM126" t="s">
+      <c r="AD126" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE126" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="127" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C127" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U127" t="s">
         <v>67</v>
       </c>
       <c r="AD127" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="AM127" t="s">
         <v>67</v>
       </c>
       <c r="BE127" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B128" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C128" t="s">
-        <v>206</v>
-      </c>
-      <c r="U128" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD128" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE128" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="129" spans="1:57" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="AX128" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="129" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B129" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C129" t="s">
-        <v>206</v>
-      </c>
-      <c r="U129" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="AD129" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM129" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE129" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="130" spans="1:57" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="130" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C130" t="s">
-        <v>206</v>
-      </c>
-      <c r="AX130" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="131" spans="1:57" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="O130" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>67</v>
+      </c>
+      <c r="V130" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB130" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL130" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA130" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="131" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>222</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>223</v>
       </c>
       <c r="C131" t="s">
-        <v>206</v>
-      </c>
-      <c r="AD131" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="132" spans="1:57" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="AZ131" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA131" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="132" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="C132" t="s">
-        <v>206</v>
-      </c>
-      <c r="O132" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="V132" t="s">
         <v>67</v>
       </c>
-      <c r="AB132" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL132" t="s">
-        <v>79</v>
-      </c>
-      <c r="BA132" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="133" spans="1:57" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B133" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C133" t="s">
-        <v>206</v>
-      </c>
-      <c r="AZ133" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="AL133" t="s">
+        <v>78</v>
       </c>
       <c r="BA133" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="134" spans="1:57" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="134" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B134" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C134" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V134" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="135" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="AB134" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="135" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B135" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C135" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="V135" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB135" t="s">
+        <v>67</v>
       </c>
       <c r="AL135" t="s">
-        <v>79</v>
-      </c>
-      <c r="BA135" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="136" spans="1:57" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="136" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B136" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C136" t="s">
-        <v>206</v>
-      </c>
-      <c r="V136" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB136" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="137" spans="1:57" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="AL136" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B137" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C137" t="s">
-        <v>206</v>
-      </c>
-      <c r="V137" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB137" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL137" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="138" spans="1:57" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="AZ137" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="138" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>233</v>
+        <v>155</v>
       </c>
       <c r="C138" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL138" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="139" spans="1:57" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="L138" t="s">
+        <v>66</v>
+      </c>
+      <c r="U138" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE138" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN138" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR138" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT138" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB138" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="139" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="B139" t="s">
+        <v>156</v>
+      </c>
+      <c r="C139" t="s">
+        <v>205</v>
+      </c>
+      <c r="P139" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC139" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="140" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>157</v>
+      </c>
+      <c r="B140" t="s">
+        <v>158</v>
+      </c>
+      <c r="C140" t="s">
+        <v>205</v>
+      </c>
+      <c r="H140" t="s">
+        <v>67</v>
+      </c>
+      <c r="N140" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE140" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH140" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR140" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB140" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="141" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>235</v>
       </c>
-      <c r="C139" t="s">
-        <v>206</v>
-      </c>
-      <c r="AZ139" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="140" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>155</v>
-      </c>
-      <c r="B140" t="s">
-        <v>156</v>
-      </c>
-      <c r="C140" t="s">
-        <v>206</v>
-      </c>
-      <c r="L140" t="s">
-        <v>66</v>
-      </c>
-      <c r="U140" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE140" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN140" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR140" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT140" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB140" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="141" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>155</v>
-      </c>
       <c r="B141" t="s">
-        <v>157</v>
+        <v>236</v>
       </c>
       <c r="C141" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="E141" t="s">
+        <v>67</v>
+      </c>
+      <c r="F141" t="s">
+        <v>67</v>
+      </c>
+      <c r="H141" t="s">
+        <v>67</v>
+      </c>
+      <c r="I141" t="s">
+        <v>67</v>
+      </c>
+      <c r="K141" t="s">
+        <v>67</v>
+      </c>
+      <c r="M141" t="s">
+        <v>67</v>
+      </c>
+      <c r="N141" t="s">
+        <v>67</v>
       </c>
       <c r="P141" t="s">
         <v>67</v>
       </c>
+      <c r="R141" t="s">
+        <v>67</v>
+      </c>
+      <c r="U141" t="s">
+        <v>67</v>
+      </c>
+      <c r="V141" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>67</v>
+      </c>
       <c r="AC141" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="142" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="AE141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN141" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW141" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB141" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="142" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C142" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="E142" t="s">
+        <v>67</v>
+      </c>
+      <c r="F142" t="s">
+        <v>67</v>
       </c>
       <c r="H142" t="s">
         <v>67</v>
       </c>
+      <c r="I142" t="s">
+        <v>67</v>
+      </c>
+      <c r="K142" t="s">
+        <v>67</v>
+      </c>
+      <c r="M142" t="s">
+        <v>67</v>
+      </c>
       <c r="N142" t="s">
         <v>67</v>
       </c>
+      <c r="P142" t="s">
+        <v>67</v>
+      </c>
+      <c r="R142" t="s">
+        <v>67</v>
+      </c>
+      <c r="U142" t="s">
+        <v>67</v>
+      </c>
+      <c r="V142" t="s">
+        <v>67</v>
+      </c>
       <c r="Y142" t="s">
         <v>67</v>
       </c>
+      <c r="AA142" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC142" t="s">
+        <v>66</v>
+      </c>
       <c r="AE142" t="s">
         <v>67</v>
       </c>
       <c r="AH142" t="s">
         <v>67</v>
       </c>
+      <c r="AN142" t="s">
+        <v>78</v>
+      </c>
       <c r="AR142" t="s">
         <v>67</v>
       </c>
+      <c r="AT142" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW142" t="s">
+        <v>67</v>
+      </c>
       <c r="BB142" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>236</v>
+        <v>161</v>
       </c>
       <c r="B143" t="s">
+        <v>162</v>
+      </c>
+      <c r="C143" t="s">
+        <v>205</v>
+      </c>
+      <c r="E143" t="s">
+        <v>67</v>
+      </c>
+      <c r="F143" t="s">
+        <v>67</v>
+      </c>
+      <c r="H143" t="s">
+        <v>67</v>
+      </c>
+      <c r="I143" t="s">
+        <v>67</v>
+      </c>
+      <c r="M143" t="s">
+        <v>67</v>
+      </c>
+      <c r="N143" t="s">
+        <v>67</v>
+      </c>
+      <c r="P143" t="s">
+        <v>67</v>
+      </c>
+      <c r="R143" t="s">
+        <v>67</v>
+      </c>
+      <c r="U143" t="s">
+        <v>67</v>
+      </c>
+      <c r="V143" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC143" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE143" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH143" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN143" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR143" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT143" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW143" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB143" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="144" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>163</v>
+      </c>
+      <c r="B144" t="s">
         <v>237</v>
       </c>
-      <c r="C143" t="s">
-        <v>206</v>
-      </c>
-      <c r="E143" t="s">
-        <v>67</v>
-      </c>
-      <c r="F143" t="s">
-        <v>67</v>
-      </c>
-      <c r="H143" t="s">
-        <v>67</v>
-      </c>
-      <c r="I143" t="s">
-        <v>67</v>
-      </c>
-      <c r="K143" t="s">
-        <v>67</v>
-      </c>
-      <c r="M143" t="s">
-        <v>67</v>
-      </c>
-      <c r="N143" t="s">
-        <v>67</v>
-      </c>
-      <c r="P143" t="s">
-        <v>67</v>
-      </c>
-      <c r="R143" t="s">
-        <v>67</v>
-      </c>
-      <c r="U143" t="s">
-        <v>67</v>
-      </c>
-      <c r="V143" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y143" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC143" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE143" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH143" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN143" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR143" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT143" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW143" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB143" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="144" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>160</v>
-      </c>
-      <c r="B144" t="s">
-        <v>161</v>
-      </c>
       <c r="C144" t="s">
-        <v>206</v>
-      </c>
-      <c r="E144" t="s">
-        <v>67</v>
-      </c>
-      <c r="F144" t="s">
-        <v>67</v>
-      </c>
-      <c r="H144" t="s">
-        <v>67</v>
-      </c>
-      <c r="I144" t="s">
-        <v>67</v>
-      </c>
-      <c r="K144" t="s">
-        <v>67</v>
-      </c>
-      <c r="M144" t="s">
-        <v>67</v>
-      </c>
-      <c r="N144" t="s">
-        <v>67</v>
-      </c>
-      <c r="P144" t="s">
-        <v>67</v>
-      </c>
-      <c r="R144" t="s">
-        <v>67</v>
-      </c>
-      <c r="U144" t="s">
-        <v>67</v>
-      </c>
-      <c r="V144" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y144" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA144" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC144" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE144" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH144" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN144" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR144" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT144" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW144" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB144" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="AD144" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="145" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C145" t="s">
-        <v>206</v>
-      </c>
-      <c r="E145" t="s">
-        <v>67</v>
-      </c>
-      <c r="F145" t="s">
-        <v>67</v>
-      </c>
-      <c r="H145" t="s">
-        <v>67</v>
-      </c>
-      <c r="I145" t="s">
-        <v>67</v>
-      </c>
-      <c r="M145" t="s">
-        <v>67</v>
-      </c>
-      <c r="N145" t="s">
-        <v>67</v>
-      </c>
-      <c r="P145" t="s">
-        <v>67</v>
-      </c>
-      <c r="R145" t="s">
-        <v>67</v>
-      </c>
-      <c r="U145" t="s">
-        <v>67</v>
-      </c>
-      <c r="V145" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="Y145" t="s">
         <v>67</v>
@@ -4450,37 +4470,22 @@
       <c r="AC145" t="s">
         <v>66</v>
       </c>
-      <c r="AE145" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH145" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN145" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR145" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT145" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW145" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB145" t="s">
-        <v>66</v>
+      <c r="AD145" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="146" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B146" t="s">
-        <v>238</v>
+        <v>166</v>
       </c>
       <c r="C146" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="N146" t="s">
+        <v>67</v>
       </c>
       <c r="AD146" t="s">
         <v>67</v>
@@ -4488,84 +4493,78 @@
     </row>
     <row r="147" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B147" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C147" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y147" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="AC147" t="s">
         <v>66</v>
       </c>
       <c r="AD147" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="148" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B148" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C148" t="s">
-        <v>206</v>
-      </c>
-      <c r="N148" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD148" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="AC148" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="149" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="B149" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="C149" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>67</v>
       </c>
       <c r="AC149" t="s">
         <v>66</v>
-      </c>
-      <c r="AD149" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="150" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B150" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC150" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="N150" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="151" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="B151" t="s">
         <v>240</v>
       </c>
       <c r="C151" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y151" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="AC151" t="s">
         <v>66</v>
@@ -4573,64 +4572,61 @@
     </row>
     <row r="152" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B152" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N152" t="s">
         <v>67</v>
       </c>
       <c r="Y152" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD152" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B153" t="s">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="C153" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC153" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="V153" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="154" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B154" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C154" t="s">
-        <v>206</v>
-      </c>
-      <c r="N154" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y154" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD154" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB154" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="155" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B155" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C155" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V155" t="s">
         <v>67</v>
@@ -4638,207 +4634,219 @@
     </row>
     <row r="156" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B156" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C156" t="s">
-        <v>206</v>
-      </c>
-      <c r="AB156" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="H156" t="s">
+        <v>67</v>
+      </c>
+      <c r="P156" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y156" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC156" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD156" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE156" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH156" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR156" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT156" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB156" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="157" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B157" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C157" t="s">
-        <v>206</v>
-      </c>
-      <c r="V157" t="s">
+        <v>205</v>
+      </c>
+      <c r="E157" t="s">
+        <v>67</v>
+      </c>
+      <c r="F157" t="s">
+        <v>67</v>
+      </c>
+      <c r="T157" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI157" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK157" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ157" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA157" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE157" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="158" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B158" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C158" t="s">
-        <v>206</v>
-      </c>
-      <c r="H158" t="s">
-        <v>67</v>
-      </c>
-      <c r="P158" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y158" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC158" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD158" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE158" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH158" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR158" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT158" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB158" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="AZ158" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="159" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B159" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="C159" t="s">
-        <v>206</v>
-      </c>
-      <c r="E159" t="s">
-        <v>67</v>
-      </c>
-      <c r="F159" t="s">
-        <v>67</v>
-      </c>
-      <c r="T159" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI159" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK159" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ159" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA159" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE159" t="s">
+        <v>205</v>
+      </c>
+      <c r="AW159" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B160" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C160" t="s">
-        <v>206</v>
-      </c>
-      <c r="AZ160" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="N160" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y160" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW160" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="161" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B161" t="s">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="C161" t="s">
-        <v>206</v>
-      </c>
-      <c r="AW161" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="N161" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="162" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B162" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C162" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N162" t="s">
         <v>67</v>
       </c>
-      <c r="Y162" t="s">
-        <v>67</v>
-      </c>
       <c r="AW162" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="163" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B163" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C163" t="s">
-        <v>206</v>
-      </c>
-      <c r="N163" t="s">
-        <v>66</v>
+        <v>205</v>
+      </c>
+      <c r="U163" t="s">
+        <v>67</v>
+      </c>
+      <c r="V163" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB163" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM163" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE163" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="164" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B164" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C164" t="s">
-        <v>206</v>
-      </c>
-      <c r="N164" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW164" t="s">
-        <v>67</v>
+        <v>205</v>
+      </c>
+      <c r="U164" t="s">
+        <v>67</v>
+      </c>
+      <c r="V164" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE164" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="165" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B165" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="C165" t="s">
-        <v>206</v>
-      </c>
-      <c r="U165" t="s">
-        <v>67</v>
-      </c>
-      <c r="V165" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB165" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM165" t="s">
+        <v>205</v>
+      </c>
+      <c r="N165" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD165" t="s">
         <v>67</v>
       </c>
       <c r="BE165" t="s">
@@ -4847,53 +4855,62 @@
     </row>
     <row r="166" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B166" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C166" t="s">
-        <v>206</v>
-      </c>
-      <c r="U166" t="s">
-        <v>67</v>
-      </c>
-      <c r="V166" t="s">
+        <v>205</v>
+      </c>
+      <c r="AL166" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM166" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ166" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA166" t="s">
         <v>67</v>
       </c>
       <c r="BE166" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="167" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="B167" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C167" t="s">
-        <v>206</v>
-      </c>
-      <c r="N167" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD167" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE167" t="s">
+        <v>205</v>
+      </c>
+      <c r="AM167" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ167" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="168" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B168" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C168" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="V168" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB168" t="s">
+        <v>67</v>
       </c>
       <c r="AL168" t="s">
         <v>66</v>
@@ -4902,55 +4919,6 @@
         <v>67</v>
       </c>
       <c r="AZ168" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA168" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE168" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="169" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>244</v>
-      </c>
-      <c r="B169" t="s">
-        <v>245</v>
-      </c>
-      <c r="C169" t="s">
-        <v>206</v>
-      </c>
-      <c r="AM169" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ169" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="170" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>204</v>
-      </c>
-      <c r="B170" t="s">
-        <v>205</v>
-      </c>
-      <c r="C170" t="s">
-        <v>206</v>
-      </c>
-      <c r="V170" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB170" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL170" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM170" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ170" t="s">
         <v>67</v>
       </c>
     </row>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE099FA-7C48-433C-B35A-0F147D9A1F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC42F0A0-9FD4-4252-A504-409F862D6AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 27-04-2026'!$A$1:$BK$168</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 06-05-2026'!$A$1:$BK$168</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -3593,7 +3593,7 @@
         <v>67</v>
       </c>
       <c r="BE108" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:58" x14ac:dyDescent="0.3">
@@ -3613,7 +3613,7 @@
         <v>67</v>
       </c>
       <c r="BE109" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="1:58" x14ac:dyDescent="0.3">
@@ -3650,7 +3650,7 @@
         <v>67</v>
       </c>
       <c r="BE111" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:58" x14ac:dyDescent="0.3">

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC42F0A0-9FD4-4252-A504-409F862D6AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25949F24-F037-46C3-AF61-EB75B7DE25B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 06-05-2026'!$A$1:$BK$168</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 01-06-2026'!$A$1:$BK$169</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="246">
   <si>
     <t>Standard</t>
   </si>
@@ -723,6 +723,9 @@
   </si>
   <si>
     <t>RPT07 (R0730G)</t>
+  </si>
+  <si>
+    <t>Shared EKG Recording (2.0)</t>
   </si>
   <si>
     <t>Sundhedsjournal</t>
@@ -1100,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BK168"/>
+  <dimension ref="A1:BK169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.3">
@@ -3990,7 +3993,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="129" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>142</v>
       </c>
@@ -4004,7 +4007,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="130" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4033,7 +4036,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>222</v>
       </c>
@@ -4050,7 +4053,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="132" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>224</v>
       </c>
@@ -4064,7 +4067,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="133" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>226</v>
       </c>
@@ -4081,7 +4084,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>228</v>
       </c>
@@ -4098,7 +4101,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="135" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>228</v>
       </c>
@@ -4118,7 +4121,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="136" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>231</v>
       </c>
@@ -4132,178 +4135,121 @@
         <v>78</v>
       </c>
     </row>
-    <row r="137" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>152</v>
+      </c>
+      <c r="B137" t="s">
         <v>233</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
+        <v>205</v>
+      </c>
+      <c r="BE137" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="138" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>234</v>
       </c>
-      <c r="C137" t="s">
-        <v>205</v>
-      </c>
-      <c r="AZ137" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="138" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>154</v>
-      </c>
       <c r="B138" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="C138" t="s">
         <v>205</v>
       </c>
-      <c r="L138" t="s">
-        <v>66</v>
-      </c>
-      <c r="U138" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE138" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN138" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR138" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT138" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB138" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="139" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="AZ138" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="139" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>154</v>
       </c>
       <c r="B139" t="s">
+        <v>155</v>
+      </c>
+      <c r="C139" t="s">
+        <v>205</v>
+      </c>
+      <c r="L139" t="s">
+        <v>66</v>
+      </c>
+      <c r="U139" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE139" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN139" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR139" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT139" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB139" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="140" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>154</v>
+      </c>
+      <c r="B140" t="s">
         <v>156</v>
       </c>
-      <c r="C139" t="s">
-        <v>205</v>
-      </c>
-      <c r="P139" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC139" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="140" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="C140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P140" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC140" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="141" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>157</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B141" t="s">
         <v>158</v>
       </c>
-      <c r="C140" t="s">
-        <v>205</v>
-      </c>
-      <c r="H140" t="s">
-        <v>67</v>
-      </c>
-      <c r="N140" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y140" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE140" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH140" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR140" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB140" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="141" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>235</v>
-      </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
+        <v>205</v>
+      </c>
+      <c r="H141" t="s">
+        <v>67</v>
+      </c>
+      <c r="N141" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR141" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB141" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="142" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>236</v>
       </c>
-      <c r="C141" t="s">
-        <v>205</v>
-      </c>
-      <c r="E141" t="s">
-        <v>67</v>
-      </c>
-      <c r="F141" t="s">
-        <v>67</v>
-      </c>
-      <c r="H141" t="s">
-        <v>67</v>
-      </c>
-      <c r="I141" t="s">
-        <v>67</v>
-      </c>
-      <c r="K141" t="s">
-        <v>67</v>
-      </c>
-      <c r="M141" t="s">
-        <v>67</v>
-      </c>
-      <c r="N141" t="s">
-        <v>67</v>
-      </c>
-      <c r="P141" t="s">
-        <v>67</v>
-      </c>
-      <c r="R141" t="s">
-        <v>67</v>
-      </c>
-      <c r="U141" t="s">
-        <v>67</v>
-      </c>
-      <c r="V141" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC141" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN141" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW141" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB141" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="142" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>159</v>
-      </c>
       <c r="B142" t="s">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="C142" t="s">
         <v>205</v>
@@ -4342,9 +4288,6 @@
         <v>67</v>
       </c>
       <c r="Y142" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA142" t="s">
         <v>67</v>
       </c>
       <c r="AC142" t="s">
@@ -4372,12 +4315,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C143" t="s">
         <v>205</v>
@@ -4394,6 +4337,9 @@
       <c r="I143" t="s">
         <v>67</v>
       </c>
+      <c r="K143" t="s">
+        <v>67</v>
+      </c>
       <c r="M143" t="s">
         <v>67</v>
       </c>
@@ -4413,6 +4359,9 @@
         <v>67</v>
       </c>
       <c r="Y143" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA143" t="s">
         <v>67</v>
       </c>
       <c r="AC143" t="s">
@@ -4440,18 +4389,72 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>237</v>
+        <v>162</v>
       </c>
       <c r="C144" t="s">
         <v>205</v>
       </c>
-      <c r="AD144" t="s">
-        <v>67</v>
+      <c r="E144" t="s">
+        <v>67</v>
+      </c>
+      <c r="F144" t="s">
+        <v>67</v>
+      </c>
+      <c r="H144" t="s">
+        <v>67</v>
+      </c>
+      <c r="I144" t="s">
+        <v>67</v>
+      </c>
+      <c r="M144" t="s">
+        <v>67</v>
+      </c>
+      <c r="N144" t="s">
+        <v>67</v>
+      </c>
+      <c r="P144" t="s">
+        <v>67</v>
+      </c>
+      <c r="R144" t="s">
+        <v>67</v>
+      </c>
+      <c r="U144" t="s">
+        <v>67</v>
+      </c>
+      <c r="V144" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC144" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE144" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH144" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN144" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR144" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT144" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW144" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB144" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="145" spans="1:57" x14ac:dyDescent="0.3">
@@ -4459,36 +4462,33 @@
         <v>163</v>
       </c>
       <c r="B145" t="s">
-        <v>164</v>
+        <v>238</v>
       </c>
       <c r="C145" t="s">
         <v>205</v>
       </c>
-      <c r="Y145" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC145" t="s">
-        <v>66</v>
-      </c>
       <c r="AD145" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="146" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C146" t="s">
         <v>205</v>
       </c>
-      <c r="N146" t="s">
-        <v>67</v>
+      <c r="Y146" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC146" t="s">
+        <v>66</v>
       </c>
       <c r="AD146" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147" spans="1:57" x14ac:dyDescent="0.3">
@@ -4496,44 +4496,44 @@
         <v>165</v>
       </c>
       <c r="B147" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C147" t="s">
         <v>205</v>
       </c>
-      <c r="AC147" t="s">
-        <v>66</v>
+      <c r="N147" t="s">
+        <v>67</v>
       </c>
       <c r="AD147" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="148" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C148" t="s">
         <v>205</v>
       </c>
       <c r="AC148" t="s">
         <v>66</v>
+      </c>
+      <c r="AD148" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="149" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="B149" t="s">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="C149" t="s">
         <v>205</v>
-      </c>
-      <c r="Y149" t="s">
-        <v>67</v>
       </c>
       <c r="AC149" t="s">
         <v>66</v>
@@ -4541,19 +4541,19 @@
     </row>
     <row r="150" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="B150" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="C150" t="s">
         <v>205</v>
       </c>
-      <c r="N150" t="s">
-        <v>67</v>
-      </c>
       <c r="Y150" t="s">
         <v>67</v>
+      </c>
+      <c r="AC150" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="151" spans="1:57" x14ac:dyDescent="0.3">
@@ -4561,46 +4561,49 @@
         <v>172</v>
       </c>
       <c r="B151" t="s">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="C151" t="s">
         <v>205</v>
       </c>
-      <c r="AC151" t="s">
-        <v>66</v>
+      <c r="N151" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="152" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B152" t="s">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="C152" t="s">
         <v>205</v>
       </c>
-      <c r="N152" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y152" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD152" t="s">
-        <v>67</v>
+      <c r="AC152" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="153" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B153" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C153" t="s">
         <v>205</v>
       </c>
-      <c r="V153" t="s">
+      <c r="N153" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD153" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4609,103 +4612,82 @@
         <v>176</v>
       </c>
       <c r="B154" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C154" t="s">
         <v>205</v>
       </c>
-      <c r="AB154" t="s">
+      <c r="V154" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="155" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C155" t="s">
         <v>205</v>
       </c>
-      <c r="V155" t="s">
+      <c r="AB155" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="156" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B156" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C156" t="s">
         <v>205</v>
       </c>
-      <c r="H156" t="s">
-        <v>67</v>
-      </c>
-      <c r="P156" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y156" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC156" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD156" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE156" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH156" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR156" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT156" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB156" t="s">
-        <v>66</v>
+      <c r="V156" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="157" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B157" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C157" t="s">
         <v>205</v>
       </c>
-      <c r="E157" t="s">
-        <v>67</v>
-      </c>
-      <c r="F157" t="s">
-        <v>67</v>
-      </c>
-      <c r="T157" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI157" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK157" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ157" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA157" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE157" t="s">
-        <v>67</v>
+      <c r="H157" t="s">
+        <v>67</v>
+      </c>
+      <c r="P157" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y157" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC157" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD157" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE157" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH157" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR157" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT157" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB157" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="158" spans="1:57" x14ac:dyDescent="0.3">
@@ -4713,27 +4695,51 @@
         <v>183</v>
       </c>
       <c r="B158" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C158" t="s">
         <v>205</v>
       </c>
+      <c r="E158" t="s">
+        <v>67</v>
+      </c>
+      <c r="F158" t="s">
+        <v>67</v>
+      </c>
+      <c r="T158" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI158" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK158" t="s">
+        <v>67</v>
+      </c>
       <c r="AZ158" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA158" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE158" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="159" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="C159" t="s">
         <v>205</v>
       </c>
-      <c r="AW159" t="s">
-        <v>67</v>
+      <c r="AZ159" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE159" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="160" spans="1:57" x14ac:dyDescent="0.3">
@@ -4741,33 +4747,33 @@
         <v>188</v>
       </c>
       <c r="B160" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="C160" t="s">
         <v>205</v>
       </c>
-      <c r="N160" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y160" t="s">
-        <v>67</v>
-      </c>
       <c r="AW160" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="161" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B161" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C161" t="s">
         <v>205</v>
       </c>
       <c r="N161" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="Y161" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW161" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="162" spans="1:57" x14ac:dyDescent="0.3">
@@ -4775,50 +4781,38 @@
         <v>192</v>
       </c>
       <c r="B162" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C162" t="s">
         <v>205</v>
       </c>
       <c r="N162" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW162" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="163" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C163" t="s">
         <v>205</v>
       </c>
-      <c r="U163" t="s">
-        <v>67</v>
-      </c>
-      <c r="V163" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB163" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM163" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE163" t="s">
+      <c r="N163" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW163" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="164" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B164" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C164" t="s">
         <v>205</v>
@@ -4829,28 +4823,34 @@
       <c r="V164" t="s">
         <v>67</v>
       </c>
+      <c r="AB164" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM164" t="s">
+        <v>67</v>
+      </c>
       <c r="BE164" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="165" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B165" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="C165" t="s">
         <v>205</v>
       </c>
-      <c r="N165" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD165" t="s">
+      <c r="U165" t="s">
+        <v>67</v>
+      </c>
+      <c r="V165" t="s">
         <v>67</v>
       </c>
       <c r="BE165" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="166" spans="1:57" x14ac:dyDescent="0.3">
@@ -4858,21 +4858,15 @@
         <v>201</v>
       </c>
       <c r="B166" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="C166" t="s">
         <v>205</v>
       </c>
-      <c r="AL166" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM166" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ166" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA166" t="s">
+      <c r="N166" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD166" t="s">
         <v>67</v>
       </c>
       <c r="BE166" t="s">
@@ -4881,44 +4875,70 @@
     </row>
     <row r="167" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="B167" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="C167" t="s">
         <v>205</v>
       </c>
+      <c r="AL167" t="s">
+        <v>66</v>
+      </c>
       <c r="AM167" t="s">
         <v>67</v>
       </c>
       <c r="AZ167" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA167" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE167" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="168" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
+        <v>244</v>
+      </c>
+      <c r="B168" t="s">
+        <v>245</v>
+      </c>
+      <c r="C168" t="s">
+        <v>205</v>
+      </c>
+      <c r="AM168" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ168" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="169" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>203</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B169" t="s">
         <v>204</v>
       </c>
-      <c r="C168" t="s">
-        <v>205</v>
-      </c>
-      <c r="V168" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB168" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL168" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM168" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ168" t="s">
+      <c r="C169" t="s">
+        <v>205</v>
+      </c>
+      <c r="V169" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB169" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL169" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM169" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ169" t="s">
         <v>67</v>
       </c>
     </row>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25949F24-F037-46C3-AF61-EB75B7DE25B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44D29D1-F3F2-4742-BFAB-EA00BA101E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 01-06-2026'!$A$1:$BK$169</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 02-06-2026'!$A$1:$BK$169</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -154,7 +154,7 @@
     <t>NetForvaltning Sundhed (EG)</t>
   </si>
   <si>
-    <t>OS2korrespondance (OS2)</t>
+    <t>OS2korrespondance (Digital Identity)</t>
   </si>
   <si>
     <t>Phadia (Ukendt)</t>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44D29D1-F3F2-4742-BFAB-EA00BA101E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396D12AA-A26F-41EA-BC17-5B17CC640ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396D12AA-A26F-41EA-BC17-5B17CC640ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61E06B3-97E2-4EFF-9D2B-7D4BB44A51E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 02-06-2026'!$A$1:$BK$169</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 05-06-2026'!$A$1:$BK$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="248">
   <si>
     <t>Standard</t>
   </si>
@@ -678,6 +678,12 @@
   </si>
   <si>
     <t>DIS05 (D0533L)</t>
+  </si>
+  <si>
+    <t>Share Notes</t>
+  </si>
+  <si>
+    <t>ECN (1.0)</t>
   </si>
   <si>
     <t>PDC-DK (2.0)</t>
@@ -1103,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BK169"/>
+  <dimension ref="A1:BK170"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.3">
@@ -3493,22 +3499,16 @@
     </row>
     <row r="103" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C103" t="s">
         <v>205</v>
       </c>
-      <c r="AM103" t="s">
-        <v>66</v>
-      </c>
       <c r="BE103" t="s">
-        <v>67</v>
-      </c>
-      <c r="BF103" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104" spans="1:58" x14ac:dyDescent="0.3">
@@ -3516,30 +3516,36 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="C104" t="s">
         <v>205</v>
       </c>
-      <c r="E104" t="s">
-        <v>67</v>
-      </c>
-      <c r="F104" t="s">
-        <v>67</v>
+      <c r="AM104" t="s">
+        <v>66</v>
       </c>
       <c r="BE104" t="s">
         <v>67</v>
+      </c>
+      <c r="BF104" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="105" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>219</v>
+        <v>100</v>
       </c>
       <c r="B105" t="s">
-        <v>220</v>
+        <v>101</v>
       </c>
       <c r="C105" t="s">
         <v>205</v>
+      </c>
+      <c r="E105" t="s">
+        <v>67</v>
+      </c>
+      <c r="F105" t="s">
+        <v>67</v>
       </c>
       <c r="BE105" t="s">
         <v>67</v>
@@ -3547,19 +3553,13 @@
     </row>
     <row r="106" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="B106" t="s">
-        <v>103</v>
+        <v>222</v>
       </c>
       <c r="C106" t="s">
         <v>205</v>
-      </c>
-      <c r="AM106" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN106" t="s">
-        <v>78</v>
       </c>
       <c r="BE106" t="s">
         <v>67</v>
@@ -3570,41 +3570,41 @@
         <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
         <v>205</v>
       </c>
+      <c r="AM107" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>78</v>
+      </c>
       <c r="BE107" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="108" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C108" t="s">
         <v>205</v>
       </c>
-      <c r="T108" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK108" t="s">
-        <v>67</v>
-      </c>
       <c r="BE108" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C109" t="s">
         <v>205</v>
@@ -3621,50 +3621,56 @@
     </row>
     <row r="110" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C110" t="s">
         <v>205</v>
       </c>
-      <c r="W110" t="s">
-        <v>78</v>
-      </c>
-      <c r="AU110" t="s">
+      <c r="T110" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK110" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE110" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C111" t="s">
         <v>205</v>
       </c>
-      <c r="T111" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK111" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE111" t="s">
+      <c r="W111" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU111" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="C112" t="s">
         <v>205</v>
+      </c>
+      <c r="T112" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK112" t="s">
+        <v>67</v>
       </c>
       <c r="BE112" t="s">
         <v>67</v>
@@ -3675,7 +3681,7 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>114</v>
+        <v>223</v>
       </c>
       <c r="C113" t="s">
         <v>205</v>
@@ -3686,19 +3692,13 @@
     </row>
     <row r="114" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C114" t="s">
         <v>205</v>
-      </c>
-      <c r="AM114" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN114" t="s">
-        <v>78</v>
       </c>
       <c r="BE114" t="s">
         <v>67</v>
@@ -3709,16 +3709,16 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
         <v>205</v>
       </c>
-      <c r="AI115" t="s">
-        <v>67</v>
+      <c r="AM115" t="s">
+        <v>66</v>
       </c>
       <c r="AN115" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="BE115" t="s">
         <v>67</v>
@@ -3726,15 +3726,21 @@
     </row>
     <row r="116" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C116" t="s">
         <v>205</v>
       </c>
-      <c r="AY116" t="s">
+      <c r="AI116" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN116" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE116" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3743,33 +3749,21 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C117" t="s">
         <v>205</v>
       </c>
-      <c r="U117" t="s">
-        <v>67</v>
-      </c>
-      <c r="V117" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM117" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW117" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE117" t="s">
+      <c r="AY117" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="118" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C118" t="s">
         <v>205</v>
@@ -3780,11 +3774,11 @@
       <c r="V118" t="s">
         <v>67</v>
       </c>
-      <c r="AD118" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA118" t="s">
-        <v>66</v>
+      <c r="AM118" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW118" t="s">
+        <v>67</v>
       </c>
       <c r="BE118" t="s">
         <v>67</v>
@@ -3792,10 +3786,10 @@
     </row>
     <row r="119" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C119" t="s">
         <v>205</v>
@@ -3808,6 +3802,9 @@
       </c>
       <c r="AD119" t="s">
         <v>67</v>
+      </c>
+      <c r="BA119" t="s">
+        <v>66</v>
       </c>
       <c r="BE119" t="s">
         <v>67</v>
@@ -3818,7 +3815,7 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C120" t="s">
         <v>205</v>
@@ -3829,19 +3826,19 @@
       <c r="V120" t="s">
         <v>67</v>
       </c>
-      <c r="AB120" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM120" t="s">
+      <c r="AD120" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE120" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
         <v>205</v>
@@ -3849,22 +3846,22 @@
       <c r="U121" t="s">
         <v>67</v>
       </c>
-      <c r="AD121" t="s">
+      <c r="V121" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB121" t="s">
         <v>67</v>
       </c>
       <c r="AM121" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE121" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="122" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C122" t="s">
         <v>205</v>
@@ -3873,6 +3870,9 @@
         <v>67</v>
       </c>
       <c r="AD122" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM122" t="s">
         <v>67</v>
       </c>
       <c r="BE122" t="s">
@@ -3884,7 +3884,7 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C123" t="s">
         <v>205</v>
@@ -3892,8 +3892,11 @@
       <c r="U123" t="s">
         <v>67</v>
       </c>
+      <c r="AD123" t="s">
+        <v>67</v>
+      </c>
       <c r="BE123" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="124" spans="1:57" x14ac:dyDescent="0.3">
@@ -3901,7 +3904,7 @@
         <v>130</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C124" t="s">
         <v>205</v>
@@ -3909,16 +3912,16 @@
       <c r="U124" t="s">
         <v>67</v>
       </c>
-      <c r="AM124" t="s">
-        <v>67</v>
+      <c r="BE124" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="125" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C125" t="s">
         <v>205</v>
@@ -3926,22 +3929,16 @@
       <c r="U125" t="s">
         <v>67</v>
       </c>
-      <c r="AD125" t="s">
-        <v>67</v>
-      </c>
       <c r="AM125" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE125" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B126" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C126" t="s">
         <v>205</v>
@@ -3950,6 +3947,9 @@
         <v>67</v>
       </c>
       <c r="AD126" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM126" t="s">
         <v>67</v>
       </c>
       <c r="BE126" t="s">
@@ -3961,7 +3961,7 @@
         <v>136</v>
       </c>
       <c r="B127" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C127" t="s">
         <v>205</v>
@@ -3970,40 +3970,46 @@
         <v>67</v>
       </c>
       <c r="AD127" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM127" t="s">
         <v>67</v>
       </c>
       <c r="BE127" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C128" t="s">
         <v>205</v>
       </c>
-      <c r="AX128" t="s">
-        <v>67</v>
+      <c r="U128" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD128" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM128" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE128" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="129" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B129" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C129" t="s">
         <v>205</v>
       </c>
-      <c r="AD129" t="s">
+      <c r="AX129" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4012,45 +4018,42 @@
         <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C130" t="s">
         <v>205</v>
       </c>
-      <c r="O130" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>67</v>
-      </c>
-      <c r="V130" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB130" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL130" t="s">
-        <v>78</v>
-      </c>
-      <c r="BA130" t="s">
-        <v>66</v>
+      <c r="AD130" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="131" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="B131" t="s">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="C131" t="s">
         <v>205</v>
       </c>
-      <c r="AZ131" t="s">
-        <v>67</v>
+      <c r="O131" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>67</v>
+      </c>
+      <c r="V131" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB131" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL131" t="s">
+        <v>78</v>
       </c>
       <c r="BA131" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132" spans="1:57" x14ac:dyDescent="0.3">
@@ -4063,7 +4066,10 @@
       <c r="C132" t="s">
         <v>205</v>
       </c>
-      <c r="V132" t="s">
+      <c r="AZ132" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA132" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4077,11 +4083,8 @@
       <c r="C133" t="s">
         <v>205</v>
       </c>
-      <c r="AL133" t="s">
-        <v>78</v>
-      </c>
-      <c r="BA133" t="s">
-        <v>66</v>
+      <c r="V133" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="134" spans="1:57" x14ac:dyDescent="0.3">
@@ -4094,19 +4097,19 @@
       <c r="C134" t="s">
         <v>205</v>
       </c>
-      <c r="V134" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB134" t="s">
-        <v>67</v>
+      <c r="AL134" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA134" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C135" t="s">
         <v>205</v>
@@ -4116,14 +4119,11 @@
       </c>
       <c r="AB135" t="s">
         <v>67</v>
-      </c>
-      <c r="AL135" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="136" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B136" t="s">
         <v>232</v>
@@ -4131,27 +4131,33 @@
       <c r="C136" t="s">
         <v>205</v>
       </c>
+      <c r="V136" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB136" t="s">
+        <v>67</v>
+      </c>
       <c r="AL136" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="137" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>152</v>
+        <v>233</v>
       </c>
       <c r="B137" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C137" t="s">
         <v>205</v>
       </c>
-      <c r="BE137" t="s">
-        <v>66</v>
+      <c r="AL137" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>234</v>
+        <v>152</v>
       </c>
       <c r="B138" t="s">
         <v>235</v>
@@ -4159,40 +4165,22 @@
       <c r="C138" t="s">
         <v>205</v>
       </c>
-      <c r="AZ138" t="s">
-        <v>67</v>
+      <c r="BE138" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="139" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="B139" t="s">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="C139" t="s">
         <v>205</v>
       </c>
-      <c r="L139" t="s">
-        <v>66</v>
-      </c>
-      <c r="U139" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE139" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN139" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR139" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT139" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB139" t="s">
-        <v>66</v>
+      <c r="AZ139" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="140" spans="1:57" x14ac:dyDescent="0.3">
@@ -4200,115 +4188,76 @@
         <v>154</v>
       </c>
       <c r="B140" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C140" t="s">
         <v>205</v>
       </c>
-      <c r="P140" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC140" t="s">
+      <c r="L140" t="s">
+        <v>66</v>
+      </c>
+      <c r="U140" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE140" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN140" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR140" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT140" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB140" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="141" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B141" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C141" t="s">
         <v>205</v>
       </c>
-      <c r="H141" t="s">
-        <v>67</v>
-      </c>
-      <c r="N141" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH141" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR141" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB141" t="s">
+      <c r="P141" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC141" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="142" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>236</v>
+        <v>157</v>
       </c>
       <c r="B142" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="C142" t="s">
         <v>205</v>
       </c>
-      <c r="E142" t="s">
-        <v>67</v>
-      </c>
-      <c r="F142" t="s">
-        <v>67</v>
-      </c>
       <c r="H142" t="s">
         <v>67</v>
       </c>
-      <c r="I142" t="s">
-        <v>67</v>
-      </c>
-      <c r="K142" t="s">
-        <v>67</v>
-      </c>
-      <c r="M142" t="s">
-        <v>67</v>
-      </c>
       <c r="N142" t="s">
         <v>67</v>
       </c>
-      <c r="P142" t="s">
-        <v>67</v>
-      </c>
-      <c r="R142" t="s">
-        <v>67</v>
-      </c>
-      <c r="U142" t="s">
-        <v>67</v>
-      </c>
-      <c r="V142" t="s">
-        <v>67</v>
-      </c>
       <c r="Y142" t="s">
         <v>67</v>
       </c>
-      <c r="AC142" t="s">
-        <v>66</v>
-      </c>
       <c r="AE142" t="s">
         <v>67</v>
       </c>
       <c r="AH142" t="s">
         <v>67</v>
       </c>
-      <c r="AN142" t="s">
-        <v>78</v>
-      </c>
       <c r="AR142" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT142" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW142" t="s">
         <v>67</v>
       </c>
       <c r="BB142" t="s">
@@ -4317,10 +4266,10 @@
     </row>
     <row r="143" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="C143" t="s">
         <v>205</v>
@@ -4359,9 +4308,6 @@
         <v>67</v>
       </c>
       <c r="Y143" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA143" t="s">
         <v>67</v>
       </c>
       <c r="AC143" t="s">
@@ -4391,10 +4337,10 @@
     </row>
     <row r="144" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C144" t="s">
         <v>205</v>
@@ -4411,6 +4357,9 @@
       <c r="I144" t="s">
         <v>67</v>
       </c>
+      <c r="K144" t="s">
+        <v>67</v>
+      </c>
       <c r="M144" t="s">
         <v>67</v>
       </c>
@@ -4430,6 +4379,9 @@
         <v>67</v>
       </c>
       <c r="Y144" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA144" t="s">
         <v>67</v>
       </c>
       <c r="AC144" t="s">
@@ -4459,16 +4411,70 @@
     </row>
     <row r="145" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B145" t="s">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="C145" t="s">
         <v>205</v>
       </c>
-      <c r="AD145" t="s">
-        <v>67</v>
+      <c r="E145" t="s">
+        <v>67</v>
+      </c>
+      <c r="F145" t="s">
+        <v>67</v>
+      </c>
+      <c r="H145" t="s">
+        <v>67</v>
+      </c>
+      <c r="I145" t="s">
+        <v>67</v>
+      </c>
+      <c r="M145" t="s">
+        <v>67</v>
+      </c>
+      <c r="N145" t="s">
+        <v>67</v>
+      </c>
+      <c r="P145" t="s">
+        <v>67</v>
+      </c>
+      <c r="R145" t="s">
+        <v>67</v>
+      </c>
+      <c r="U145" t="s">
+        <v>67</v>
+      </c>
+      <c r="V145" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC145" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE145" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH145" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN145" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR145" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT145" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW145" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB145" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="146" spans="1:57" x14ac:dyDescent="0.3">
@@ -4476,36 +4482,33 @@
         <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="C146" t="s">
         <v>205</v>
       </c>
-      <c r="Y146" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC146" t="s">
-        <v>66</v>
-      </c>
       <c r="AD146" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="147" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B147" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C147" t="s">
         <v>205</v>
       </c>
-      <c r="N147" t="s">
-        <v>67</v>
+      <c r="Y147" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC147" t="s">
+        <v>66</v>
       </c>
       <c r="AD147" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="148" spans="1:57" x14ac:dyDescent="0.3">
@@ -4513,44 +4516,44 @@
         <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C148" t="s">
         <v>205</v>
       </c>
-      <c r="AC148" t="s">
-        <v>66</v>
+      <c r="N148" t="s">
+        <v>67</v>
       </c>
       <c r="AD148" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="149" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B149" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C149" t="s">
         <v>205</v>
       </c>
       <c r="AC149" t="s">
         <v>66</v>
+      </c>
+      <c r="AD149" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="150" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
       <c r="B150" t="s">
-        <v>240</v>
+        <v>169</v>
       </c>
       <c r="C150" t="s">
         <v>205</v>
-      </c>
-      <c r="Y150" t="s">
-        <v>67</v>
       </c>
       <c r="AC150" t="s">
         <v>66</v>
@@ -4558,19 +4561,19 @@
     </row>
     <row r="151" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="B151" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="C151" t="s">
         <v>205</v>
       </c>
-      <c r="N151" t="s">
-        <v>67</v>
-      </c>
       <c r="Y151" t="s">
         <v>67</v>
+      </c>
+      <c r="AC151" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="152" spans="1:57" x14ac:dyDescent="0.3">
@@ -4578,46 +4581,49 @@
         <v>172</v>
       </c>
       <c r="B152" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="C152" t="s">
         <v>205</v>
       </c>
-      <c r="AC152" t="s">
-        <v>66</v>
+      <c r="N152" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y152" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B153" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="C153" t="s">
         <v>205</v>
       </c>
-      <c r="N153" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y153" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD153" t="s">
-        <v>67</v>
+      <c r="AC153" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="154" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B154" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C154" t="s">
         <v>205</v>
       </c>
-      <c r="V154" t="s">
+      <c r="N154" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD154" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4626,103 +4632,82 @@
         <v>176</v>
       </c>
       <c r="B155" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C155" t="s">
         <v>205</v>
       </c>
-      <c r="AB155" t="s">
+      <c r="V155" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="156" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B156" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C156" t="s">
         <v>205</v>
       </c>
-      <c r="V156" t="s">
+      <c r="AB156" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="157" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B157" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C157" t="s">
         <v>205</v>
       </c>
-      <c r="H157" t="s">
-        <v>67</v>
-      </c>
-      <c r="P157" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y157" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC157" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD157" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE157" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH157" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR157" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT157" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB157" t="s">
-        <v>66</v>
+      <c r="V157" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="158" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B158" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C158" t="s">
         <v>205</v>
       </c>
-      <c r="E158" t="s">
-        <v>67</v>
-      </c>
-      <c r="F158" t="s">
-        <v>67</v>
-      </c>
-      <c r="T158" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI158" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK158" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ158" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA158" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE158" t="s">
-        <v>67</v>
+      <c r="H158" t="s">
+        <v>67</v>
+      </c>
+      <c r="P158" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y158" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC158" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD158" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE158" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH158" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR158" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT158" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB158" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="159" spans="1:57" x14ac:dyDescent="0.3">
@@ -4730,30 +4715,51 @@
         <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C159" t="s">
         <v>205</v>
       </c>
+      <c r="E159" t="s">
+        <v>67</v>
+      </c>
+      <c r="F159" t="s">
+        <v>67</v>
+      </c>
+      <c r="T159" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI159" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK159" t="s">
+        <v>67</v>
+      </c>
       <c r="AZ159" t="s">
         <v>67</v>
       </c>
+      <c r="BA159" t="s">
+        <v>67</v>
+      </c>
       <c r="BE159" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="160" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B160" t="s">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="C160" t="s">
         <v>205</v>
       </c>
-      <c r="AW160" t="s">
-        <v>67</v>
+      <c r="AZ160" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE160" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="161" spans="1:57" x14ac:dyDescent="0.3">
@@ -4761,33 +4767,33 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="C161" t="s">
         <v>205</v>
       </c>
-      <c r="N161" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y161" t="s">
-        <v>67</v>
-      </c>
       <c r="AW161" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="162" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B162" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C162" t="s">
         <v>205</v>
       </c>
       <c r="N162" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="Y162" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW162" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="163" spans="1:57" x14ac:dyDescent="0.3">
@@ -4795,50 +4801,38 @@
         <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C163" t="s">
         <v>205</v>
       </c>
       <c r="N163" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW163" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="164" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B164" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C164" t="s">
         <v>205</v>
       </c>
-      <c r="U164" t="s">
-        <v>67</v>
-      </c>
-      <c r="V164" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB164" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM164" t="s">
-        <v>67</v>
-      </c>
-      <c r="BE164" t="s">
+      <c r="N164" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW164" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="165" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B165" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C165" t="s">
         <v>205</v>
@@ -4849,28 +4843,34 @@
       <c r="V165" t="s">
         <v>67</v>
       </c>
+      <c r="AB165" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM165" t="s">
+        <v>67</v>
+      </c>
       <c r="BE165" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="166" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B166" t="s">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="C166" t="s">
         <v>205</v>
       </c>
-      <c r="N166" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD166" t="s">
+      <c r="U166" t="s">
+        <v>67</v>
+      </c>
+      <c r="V166" t="s">
         <v>67</v>
       </c>
       <c r="BE166" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="167" spans="1:57" x14ac:dyDescent="0.3">
@@ -4878,21 +4878,15 @@
         <v>201</v>
       </c>
       <c r="B167" t="s">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="C167" t="s">
         <v>205</v>
       </c>
-      <c r="AL167" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM167" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ167" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA167" t="s">
+      <c r="N167" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD167" t="s">
         <v>67</v>
       </c>
       <c r="BE167" t="s">
@@ -4901,44 +4895,70 @@
     </row>
     <row r="168" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="B168" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="C168" t="s">
         <v>205</v>
       </c>
+      <c r="AL168" t="s">
+        <v>66</v>
+      </c>
       <c r="AM168" t="s">
         <v>67</v>
       </c>
       <c r="AZ168" t="s">
+        <v>67</v>
+      </c>
+      <c r="BA168" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE168" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="169" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
+        <v>246</v>
+      </c>
+      <c r="B169" t="s">
+        <v>247</v>
+      </c>
+      <c r="C169" t="s">
+        <v>205</v>
+      </c>
+      <c r="AM169" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ169" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="170" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>203</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B170" t="s">
         <v>204</v>
       </c>
-      <c r="C169" t="s">
-        <v>205</v>
-      </c>
-      <c r="V169" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB169" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL169" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM169" t="s">
-        <v>67</v>
-      </c>
-      <c r="AZ169" t="s">
+      <c r="C170" t="s">
+        <v>205</v>
+      </c>
+      <c r="V170" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB170" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL170" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM170" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ170" t="s">
         <v>67</v>
       </c>
     </row>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A237ABE-4100-40A4-A557-6B3CF6E31E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04553CA-3A81-45F0-87C5-2A606CFA30C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A021F2-1C3E-46DB-9A33-2B104FCEACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA85781-71F1-4ADF-AA4B-30A5360E4703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA85781-71F1-4ADF-AA4B-30A5360E4703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7487EDBF-51A9-48A0-837F-DE2279F62CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7487EDBF-51A9-48A0-837F-DE2279F62CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED50F1D-0F3D-46C1-A13E-A3A2EDA8C340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 09-06-2026'!$A$1:$BK$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 15-06-2026'!$A$1:$BK$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1110,9 +1110,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BK170"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>105</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>107</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>115</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>118</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>122</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>122</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>125</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>128</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>130</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>130</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>130</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>134</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>136</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>136</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>139</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>139</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>142</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>147</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>147</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -2248,10 +2248,10 @@
         <v>67</v>
       </c>
       <c r="BJ49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>152</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>154</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>154</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>157</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>165</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>168</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>170</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>172</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>174</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>176</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>176</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>179</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>181</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>183</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>183</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>186</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>188</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>192</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>192</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>195</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>197</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>199</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>201</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>203</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>68</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>70</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>72</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>76</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>206</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>208</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>208</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>211</v>
       </c>
@@ -3118,10 +3118,10 @@
         <v>66</v>
       </c>
       <c r="BJ88" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="89" spans="1:62" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="89" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>79</v>
       </c>
@@ -3192,10 +3192,10 @@
         <v>66</v>
       </c>
       <c r="BJ89" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="90" spans="1:62" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="90" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -3263,10 +3263,10 @@
         <v>66</v>
       </c>
       <c r="BJ90" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="91" spans="1:62" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="91" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>85</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>87</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>87</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>89</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>89</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="97" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>214</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>216</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>92</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>94</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>96</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="102" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>98</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>218</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>100</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>100</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>221</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="107" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>102</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="108" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>102</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="112" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="113" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="114" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="115" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="116" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="117" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="118" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="119" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>122</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="120" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="121" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>125</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="122" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>130</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>130</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="126" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>134</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="127" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>136</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="128" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>136</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="129" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="130" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="131" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>142</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>224</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="133" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>226</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="134" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>228</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>230</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>230</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="137" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>233</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="138" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>236</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="140" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>154</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="142" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>238</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>159</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>161</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>163</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>165</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>165</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>168</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>241</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>172</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>174</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>176</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>176</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>179</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>183</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="162" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="163" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>192</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="164" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="165" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>195</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="166" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="167" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>201</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="168" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>201</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="169" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>246</v>
       </c>
@@ -4936,7 +4936,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>203</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED50F1D-0F3D-46C1-A13E-A3A2EDA8C340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4E1CD5-71F7-48B6-A5DE-37DF7249143F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 15-06-2026'!$A$1:$BK$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 22-06-2026'!$A$1:$BK$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4E1CD5-71F7-48B6-A5DE-37DF7249143F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A9EF0B-EDCE-46A6-AF54-128CCAB0DEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 22-06-2026'!$A$1:$BK$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 23-06-2026'!$A$1:$BK$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1110,9 +1110,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BK170"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>68</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>83</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>105</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>107</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>115</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>118</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>122</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>122</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>125</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>128</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>130</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>130</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>130</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>134</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>136</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>136</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>139</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>139</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>142</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>147</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>147</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>152</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>154</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>154</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>157</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>165</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>168</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>170</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>172</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>174</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>176</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>176</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>179</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>181</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>183</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>183</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>186</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>188</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>192</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>192</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>195</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>197</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>199</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>201</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>203</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:63" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>68</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>70</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>72</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>76</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>206</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>208</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>208</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>211</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>79</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>85</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>87</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>87</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>89</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:62" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>89</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="97" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>214</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>216</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>92</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>94</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>96</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="102" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>98</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>218</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>100</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>100</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>221</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="107" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>102</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="108" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>102</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="112" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="113" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="114" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="115" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="116" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="117" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="118" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="119" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>122</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="120" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="121" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>125</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="122" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>130</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>130</v>
       </c>
@@ -3933,7 +3933,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="126" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>134</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="127" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>136</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="128" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>136</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="129" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="130" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="131" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>142</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>224</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="133" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>226</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="134" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>228</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>230</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>230</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="137" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>233</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="138" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>236</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="140" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>154</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="142" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>238</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>159</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>161</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>163</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>165</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>165</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>168</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>241</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>172</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>174</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>176</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>176</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>179</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>183</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="162" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="163" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>192</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="164" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="165" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>195</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="166" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="167" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>201</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="168" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>201</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="169" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>246</v>
       </c>
@@ -4936,7 +4936,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>203</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A9EF0B-EDCE-46A6-AF54-128CCAB0DEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE73D7AC-1BEE-454E-8CBD-2F6BD494C063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61477B5D-77DB-44C3-87EC-3FCE4D514BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4D299C-744A-4B38-951F-E0E96DA2A6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 23-06-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 25-06-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4D299C-744A-4B38-951F-E0E96DA2A6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F509AB-54BC-4F1B-BA3E-16C64C8C3716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 25-06-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 30-06-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F509AB-54BC-4F1B-BA3E-16C64C8C3716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4632FCE3-01AF-48EE-8964-F44ABE64C8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4632FCE3-01AF-48EE-8964-F44ABE64C8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6DCB23-CB47-444F-A5D6-A737F8E99C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 30-06-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 01-07-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1116,9 +1116,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM170"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>178</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>185</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>194</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>70</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>74</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>78</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>208</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>210</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>210</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>213</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>81</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>85</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>87</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>89</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>91</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>91</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>216</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>218</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>94</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>96</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>98</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>220</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>223</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>104</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>104</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>113</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>120</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>127</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>127</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>130</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>136</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>138</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>141</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>226</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>232</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>154</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>238</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>156</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>156</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>240</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>161</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>163</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>165</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="148" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>167</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="149" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="151" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>243</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="152" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>174</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="153" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>174</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="154" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>176</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>178</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="156" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>183</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="159" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>185</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>190</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>194</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>194</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>203</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>248</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>205</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6DCB23-CB47-444F-A5D6-A737F8E99C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF620C80-916A-46CB-B2A2-CE8E28D0EDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 01-07-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 02-07-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6DCB23-CB47-444F-A5D6-A737F8E99C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEBEDF9-A502-4A38-A34A-0ED1F0E2AEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 01-07-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 03-07-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1116,9 +1116,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM170"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>178</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>185</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>194</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>70</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>74</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>78</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>208</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>210</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>210</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>213</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>81</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>85</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>87</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>89</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>91</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>91</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>216</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>218</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>94</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>96</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>98</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>220</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>223</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>104</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>104</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>113</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>120</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>127</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>127</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>130</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>136</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>138</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>141</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>226</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>232</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>154</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>238</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>156</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>156</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>240</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>161</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>163</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>165</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="148" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>167</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="149" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="151" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>243</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="152" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>174</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="153" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>174</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="154" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>176</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>178</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="156" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>183</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="159" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>185</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>190</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>194</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>194</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>203</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>248</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>205</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF620C80-916A-46CB-B2A2-CE8E28D0EDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC5736E-9A3B-4C98-A068-A9F426347705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 02-07-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 03-07-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1116,9 +1116,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM170"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>178</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>185</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>194</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>70</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>74</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>78</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>208</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>210</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>210</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>213</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>81</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>83</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>85</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>87</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>89</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>91</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>91</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>216</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>218</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>94</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>96</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>98</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>220</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>223</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>104</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>104</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>113</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>120</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>127</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>127</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>130</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>136</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>138</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>141</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>226</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>232</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>154</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>238</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>156</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>156</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>159</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>240</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>161</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>163</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>165</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -4535,7 +4535,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="148" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>167</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="149" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="151" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>243</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="152" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>174</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="153" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>174</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="154" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>176</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>178</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="156" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4679,7 +4679,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>183</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="159" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>185</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>190</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>194</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>194</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>203</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>248</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>205</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC5736E-9A3B-4C98-A068-A9F426347705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2410A798-78E5-4116-BB52-3802AB0EBF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 03-07-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 09-07-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2410A798-78E5-4116-BB52-3802AB0EBF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D039FD-25F2-458C-BF76-E6BCA6D1DC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 09-07-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 19-08-2026'!$A$1:$BM$170</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D039FD-25F2-458C-BF76-E6BCA6D1DC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CCED1F-C640-4F3F-B785-5B2EBAE49C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 19-08-2026'!$A$1:$BM$170</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 21-08-2026'!$A$1:$BM$171</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="252">
   <si>
     <t>Standard</t>
   </si>
@@ -615,6 +615,12 @@
   </si>
   <si>
     <t>XREF06 (XH0631R)</t>
+  </si>
+  <si>
+    <t>Physiotherapistreferral</t>
+  </si>
+  <si>
+    <t>XREF07 (XH0732R)</t>
   </si>
   <si>
     <t>MunicipalityReferral</t>
@@ -1115,10 +1121,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BM170"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BM171"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1321,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1335,7 +1341,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1355,7 +1361,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1387,7 +1393,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1401,7 +1407,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1421,7 +1427,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1438,7 +1444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1503,7 +1509,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1553,7 +1559,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1567,7 +1573,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1581,7 +1587,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1595,7 +1601,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1609,7 +1615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1623,7 +1629,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1637,7 +1643,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1651,7 +1657,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1665,7 +1671,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1721,7 +1727,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1735,7 +1741,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1758,7 +1764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1772,7 +1778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1786,7 +1792,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1800,7 +1806,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1817,7 +1823,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1831,7 +1837,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1848,7 +1854,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1877,7 +1883,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1903,7 +1909,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1920,7 +1926,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1939,11 +1945,14 @@
       <c r="AB30" t="s">
         <v>69</v>
       </c>
+      <c r="AC30" t="s">
+        <v>68</v>
+      </c>
       <c r="AD30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1957,7 +1966,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -1980,7 +1989,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2000,7 +2009,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2016,8 +2025,11 @@
       <c r="V34" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="AC34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2030,11 +2042,14 @@
       <c r="U35" t="s">
         <v>69</v>
       </c>
+      <c r="AC35" t="s">
+        <v>68</v>
+      </c>
       <c r="AD35" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2051,7 +2066,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2065,7 +2080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2079,7 +2094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2092,11 +2107,14 @@
       <c r="U39" t="s">
         <v>69</v>
       </c>
+      <c r="AC39" t="s">
+        <v>68</v>
+      </c>
       <c r="AD39" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2113,7 +2131,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2130,7 +2148,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2144,7 +2162,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2158,7 +2176,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2178,7 +2196,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2201,7 +2219,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2218,7 +2236,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2232,7 +2250,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2246,7 +2264,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2263,7 +2281,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2286,7 +2304,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2318,7 +2336,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2338,7 +2356,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2373,7 +2391,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2423,7 +2441,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2473,7 +2491,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2487,7 +2505,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2501,7 +2519,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -2515,7 +2533,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2529,7 +2547,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2552,7 +2570,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2566,7 +2584,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2580,7 +2598,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2594,7 +2612,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>178</v>
       </c>
@@ -2608,7 +2626,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2622,7 +2640,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2681,7 +2699,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2710,7 +2728,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>185</v>
       </c>
@@ -2733,7 +2751,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2747,7 +2765,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2763,8 +2781,11 @@
       <c r="Y70" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="AC70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2778,7 +2799,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2792,7 +2813,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>194</v>
       </c>
@@ -2808,8 +2829,11 @@
       <c r="Y73" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="AC73" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2819,17 +2843,11 @@
       <c r="C74" t="s">
         <v>67</v>
       </c>
-      <c r="U74" t="s">
-        <v>69</v>
-      </c>
-      <c r="V74" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB74" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="AC74" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2845,8 +2863,11 @@
       <c r="V75" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="AB75" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2856,11 +2877,14 @@
       <c r="C76" t="s">
         <v>67</v>
       </c>
-      <c r="O76" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="U76" t="s">
+        <v>69</v>
+      </c>
+      <c r="V76" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2870,11 +2894,11 @@
       <c r="C77" t="s">
         <v>67</v>
       </c>
-      <c r="AA77" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="O77" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2884,157 +2908,154 @@
       <c r="C78" t="s">
         <v>67</v>
       </c>
-      <c r="O78" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="AA78" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>207</v>
+      </c>
+      <c r="B79" t="s">
+        <v>208</v>
+      </c>
+      <c r="C79" t="s">
+        <v>67</v>
+      </c>
+      <c r="O79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>65</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>66</v>
       </c>
-      <c r="C79" t="s">
-        <v>207</v>
-      </c>
-      <c r="L79" t="s">
-        <v>68</v>
-      </c>
-      <c r="V79" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE79" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="C80" t="s">
+        <v>209</v>
+      </c>
+      <c r="L80" t="s">
+        <v>68</v>
+      </c>
+      <c r="V80" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE80" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>70</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>71</v>
       </c>
-      <c r="C80" t="s">
-        <v>207</v>
-      </c>
-      <c r="M80" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL80" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM80" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW80" t="s">
-        <v>68</v>
-      </c>
-      <c r="BB80" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC80" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG80" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="C81" t="s">
+        <v>209</v>
+      </c>
+      <c r="M81" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM81" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW81" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB81" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC81" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG81" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>72</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>73</v>
       </c>
-      <c r="C81" t="s">
-        <v>207</v>
-      </c>
-      <c r="U81" t="s">
-        <v>69</v>
-      </c>
-      <c r="V81" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS81" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT81" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="C82" t="s">
+        <v>209</v>
+      </c>
+      <c r="U82" t="s">
+        <v>69</v>
+      </c>
+      <c r="V82" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS82" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT82" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="83" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>74</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B83" t="s">
         <v>75</v>
       </c>
-      <c r="C82" t="s">
-        <v>207</v>
-      </c>
-      <c r="U82" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="C83" t="s">
+        <v>209</v>
+      </c>
+      <c r="U83" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>76</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B84" t="s">
         <v>77</v>
       </c>
-      <c r="C83" t="s">
-        <v>207</v>
-      </c>
-      <c r="L83" t="s">
-        <v>68</v>
-      </c>
-      <c r="V83" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE83" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="C84" t="s">
+        <v>209</v>
+      </c>
+      <c r="L84" t="s">
+        <v>68</v>
+      </c>
+      <c r="V84" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE84" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>78</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>79</v>
       </c>
-      <c r="C84" t="s">
-        <v>207</v>
-      </c>
-      <c r="W84" t="s">
+      <c r="C85" t="s">
+        <v>209</v>
+      </c>
+      <c r="W85" t="s">
         <v>80</v>
       </c>
-      <c r="AW84" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>208</v>
-      </c>
-      <c r="B85" t="s">
-        <v>209</v>
-      </c>
-      <c r="C85" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB85" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG85" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="AW85" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>210</v>
       </c>
@@ -3042,118 +3063,64 @@
         <v>211</v>
       </c>
       <c r="C86" t="s">
-        <v>207</v>
-      </c>
-      <c r="BC86" t="s">
+        <v>209</v>
+      </c>
+      <c r="BB86" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG86" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>212</v>
+      </c>
+      <c r="B87" t="s">
+        <v>213</v>
+      </c>
+      <c r="C87" t="s">
+        <v>209</v>
+      </c>
+      <c r="BC87" t="s">
         <v>80</v>
       </c>
-      <c r="BG86" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>210</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="BG87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>212</v>
-      </c>
-      <c r="C87" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL87" t="s">
-        <v>68</v>
-      </c>
-      <c r="BB87" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC87" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG87" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>213</v>
       </c>
       <c r="B88" t="s">
         <v>214</v>
       </c>
       <c r="C88" t="s">
-        <v>207</v>
-      </c>
-      <c r="G88" t="s">
-        <v>69</v>
-      </c>
-      <c r="J88" t="s">
-        <v>80</v>
-      </c>
-      <c r="O88" t="s">
-        <v>69</v>
-      </c>
-      <c r="U88" t="s">
-        <v>69</v>
-      </c>
-      <c r="V88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AX88" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY88" t="s">
-        <v>69</v>
-      </c>
-      <c r="BA88" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB88" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC88" t="s">
         <v>69</v>
       </c>
       <c r="BG88" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK88" t="s">
-        <v>68</v>
-      </c>
-      <c r="BL88" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="C89" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G89" t="s">
         <v>69</v>
@@ -3206,9 +3173,6 @@
       <c r="BA89" t="s">
         <v>69</v>
       </c>
-      <c r="BF89" t="s">
-        <v>69</v>
-      </c>
       <c r="BG89" t="s">
         <v>68</v>
       </c>
@@ -3219,15 +3183,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G90" t="s">
         <v>69</v>
@@ -3280,6 +3244,9 @@
       <c r="BA90" t="s">
         <v>69</v>
       </c>
+      <c r="BF90" t="s">
+        <v>69</v>
+      </c>
       <c r="BG90" t="s">
         <v>68</v>
       </c>
@@ -3290,126 +3257,180 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>83</v>
+      </c>
+      <c r="B91" t="s">
+        <v>84</v>
+      </c>
+      <c r="C91" t="s">
+        <v>209</v>
+      </c>
+      <c r="G91" t="s">
+        <v>69</v>
+      </c>
+      <c r="J91" t="s">
+        <v>80</v>
+      </c>
+      <c r="O91" t="s">
+        <v>69</v>
+      </c>
+      <c r="U91" t="s">
+        <v>69</v>
+      </c>
+      <c r="V91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AX91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY91" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA91" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG91" t="s">
+        <v>68</v>
+      </c>
+      <c r="BK91" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL91" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>85</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B92" t="s">
         <v>86</v>
       </c>
-      <c r="C91" t="s">
-        <v>207</v>
-      </c>
-      <c r="AS91" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="C92" t="s">
+        <v>209</v>
+      </c>
+      <c r="AS92" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>87</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B93" t="s">
         <v>88</v>
       </c>
-      <c r="C92" t="s">
-        <v>207</v>
-      </c>
-      <c r="AS92" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>89</v>
-      </c>
-      <c r="B93" t="s">
-        <v>215</v>
-      </c>
       <c r="C93" t="s">
-        <v>207</v>
-      </c>
-      <c r="V93" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD93" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="AS93" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>89</v>
       </c>
       <c r="B94" t="s">
+        <v>217</v>
+      </c>
+      <c r="C94" t="s">
+        <v>209</v>
+      </c>
+      <c r="V94" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD94" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="95" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>89</v>
+      </c>
+      <c r="B95" t="s">
         <v>90</v>
       </c>
-      <c r="C94" t="s">
-        <v>207</v>
-      </c>
-      <c r="V94" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC94" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>91</v>
-      </c>
-      <c r="B95" t="s">
-        <v>92</v>
-      </c>
       <c r="C95" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD95" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="V95" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="96" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>91</v>
       </c>
       <c r="B96" t="s">
+        <v>92</v>
+      </c>
+      <c r="C96" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD96" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>91</v>
+      </c>
+      <c r="B97" t="s">
         <v>93</v>
       </c>
-      <c r="C96" t="s">
-        <v>207</v>
-      </c>
-      <c r="V96" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y96" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB96" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC96" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD96" t="s">
+      <c r="C97" t="s">
+        <v>209</v>
+      </c>
+      <c r="V97" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB97" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD97" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>216</v>
-      </c>
-      <c r="B97" t="s">
-        <v>217</v>
-      </c>
-      <c r="C97" t="s">
-        <v>207</v>
-      </c>
-      <c r="V97" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC97" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>218</v>
       </c>
@@ -3417,432 +3438,423 @@
         <v>219</v>
       </c>
       <c r="C98" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="V98" t="s">
         <v>69</v>
       </c>
-      <c r="AB98" t="s">
-        <v>69</v>
-      </c>
       <c r="AC98" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" t="s">
+        <v>221</v>
+      </c>
+      <c r="C99" t="s">
+        <v>209</v>
+      </c>
+      <c r="V99" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB99" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>94</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B100" t="s">
         <v>95</v>
       </c>
-      <c r="C99" t="s">
-        <v>207</v>
-      </c>
-      <c r="V99" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC99" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="C100" t="s">
+        <v>209</v>
+      </c>
+      <c r="V100" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>96</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B101" t="s">
         <v>97</v>
       </c>
-      <c r="C100" t="s">
-        <v>207</v>
-      </c>
-      <c r="V100" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD100" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="C101" t="s">
+        <v>209</v>
+      </c>
+      <c r="V101" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>98</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B102" t="s">
         <v>99</v>
       </c>
-      <c r="C101" t="s">
-        <v>207</v>
-      </c>
-      <c r="V101" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="C102" t="s">
+        <v>209</v>
+      </c>
+      <c r="V102" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>100</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B103" t="s">
         <v>101</v>
       </c>
-      <c r="C102" t="s">
-        <v>207</v>
-      </c>
-      <c r="H102" t="s">
-        <v>69</v>
-      </c>
-      <c r="V102" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y102" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB102" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC102" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD102" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG102" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS102" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT102" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV102" t="s">
-        <v>69</v>
-      </c>
-      <c r="BA102" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>220</v>
-      </c>
-      <c r="B103" t="s">
-        <v>221</v>
-      </c>
       <c r="C103" t="s">
-        <v>207</v>
-      </c>
-      <c r="BG103" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="H103" t="s">
+        <v>69</v>
+      </c>
+      <c r="V103" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB103" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD103" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG103" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS103" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT103" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV103" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA103" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>222</v>
       </c>
       <c r="B104" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C104" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM104" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="BG104" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH104" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>102</v>
       </c>
       <c r="B105" t="s">
+        <v>224</v>
+      </c>
+      <c r="C105" t="s">
+        <v>209</v>
+      </c>
+      <c r="AM105" t="s">
+        <v>68</v>
+      </c>
+      <c r="BG105" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH105" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>102</v>
+      </c>
+      <c r="B106" t="s">
         <v>103</v>
       </c>
-      <c r="C105" t="s">
-        <v>207</v>
-      </c>
-      <c r="E105" t="s">
-        <v>69</v>
-      </c>
-      <c r="F105" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG105" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>223</v>
-      </c>
-      <c r="B106" t="s">
-        <v>224</v>
-      </c>
       <c r="C106" t="s">
-        <v>207</v>
+        <v>209</v>
+      </c>
+      <c r="E106" t="s">
+        <v>69</v>
+      </c>
+      <c r="F106" t="s">
+        <v>69</v>
       </c>
       <c r="BG106" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="C107" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM107" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN107" t="s">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="BG107" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>104</v>
       </c>
       <c r="B108" t="s">
+        <v>105</v>
+      </c>
+      <c r="C108" t="s">
+        <v>209</v>
+      </c>
+      <c r="AM108" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>80</v>
+      </c>
+      <c r="BG108" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>104</v>
+      </c>
+      <c r="B109" t="s">
         <v>106</v>
       </c>
-      <c r="C108" t="s">
-        <v>207</v>
-      </c>
-      <c r="BG108" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="C109" t="s">
+        <v>209</v>
+      </c>
+      <c r="BG109" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>107</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B110" t="s">
         <v>108</v>
       </c>
-      <c r="C109" t="s">
-        <v>207</v>
-      </c>
-      <c r="T109" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK109" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG109" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="C110" t="s">
+        <v>209</v>
+      </c>
+      <c r="T110" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK110" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG110" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="111" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B111" t="s">
         <v>110</v>
       </c>
-      <c r="C110" t="s">
-        <v>207</v>
-      </c>
-      <c r="T110" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK110" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG110" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="C111" t="s">
+        <v>209</v>
+      </c>
+      <c r="T111" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK111" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG111" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>111</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B112" t="s">
         <v>112</v>
       </c>
-      <c r="C111" t="s">
-        <v>207</v>
-      </c>
-      <c r="W111" t="s">
+      <c r="C112" t="s">
+        <v>209</v>
+      </c>
+      <c r="W112" t="s">
         <v>80</v>
       </c>
-      <c r="AW111" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="AW112" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="113" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>113</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B113" t="s">
         <v>114</v>
       </c>
-      <c r="C112" t="s">
-        <v>207</v>
-      </c>
-      <c r="T112" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK112" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG112" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>115</v>
-      </c>
-      <c r="B113" t="s">
-        <v>225</v>
-      </c>
       <c r="C113" t="s">
-        <v>207</v>
+        <v>209</v>
+      </c>
+      <c r="T113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK113" t="s">
+        <v>69</v>
       </c>
       <c r="BG113" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>115</v>
       </c>
       <c r="B114" t="s">
+        <v>227</v>
+      </c>
+      <c r="C114" t="s">
+        <v>209</v>
+      </c>
+      <c r="BG114" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="115" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" t="s">
         <v>116</v>
       </c>
-      <c r="C114" t="s">
-        <v>207</v>
-      </c>
-      <c r="BG114" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>117</v>
-      </c>
-      <c r="B115" t="s">
-        <v>118</v>
-      </c>
       <c r="C115" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM115" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN115" t="s">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="BG115" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>117</v>
       </c>
       <c r="B116" t="s">
+        <v>118</v>
+      </c>
+      <c r="C116" t="s">
+        <v>209</v>
+      </c>
+      <c r="AM116" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN116" t="s">
+        <v>80</v>
+      </c>
+      <c r="BG116" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="117" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+      <c r="B117" t="s">
         <v>119</v>
       </c>
-      <c r="C116" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI116" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN116" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG116" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>120</v>
-      </c>
-      <c r="B117" t="s">
-        <v>121</v>
-      </c>
       <c r="C117" t="s">
-        <v>207</v>
-      </c>
-      <c r="BA117" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="AI117" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN117" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG117" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="118" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>120</v>
       </c>
       <c r="B118" t="s">
+        <v>121</v>
+      </c>
+      <c r="C118" t="s">
+        <v>209</v>
+      </c>
+      <c r="BA118" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="119" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" t="s">
         <v>122</v>
       </c>
-      <c r="C118" t="s">
-        <v>207</v>
-      </c>
-      <c r="U118" t="s">
-        <v>69</v>
-      </c>
-      <c r="V118" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM118" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY118" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG118" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="C119" t="s">
+        <v>209</v>
+      </c>
+      <c r="U119" t="s">
+        <v>69</v>
+      </c>
+      <c r="V119" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM119" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY119" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG119" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="120" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>124</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B120" t="s">
         <v>126</v>
       </c>
-      <c r="C119" t="s">
-        <v>207</v>
-      </c>
-      <c r="U119" t="s">
-        <v>69</v>
-      </c>
-      <c r="V119" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD119" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC119" t="s">
-        <v>68</v>
-      </c>
-      <c r="BG119" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>127</v>
-      </c>
-      <c r="B120" t="s">
-        <v>128</v>
-      </c>
       <c r="C120" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="U120" t="s">
         <v>69</v>
@@ -3853,65 +3865,68 @@
       <c r="AD120" t="s">
         <v>69</v>
       </c>
+      <c r="BC120" t="s">
+        <v>68</v>
+      </c>
       <c r="BG120" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>127</v>
       </c>
       <c r="B121" t="s">
+        <v>128</v>
+      </c>
+      <c r="C121" t="s">
+        <v>209</v>
+      </c>
+      <c r="U121" t="s">
+        <v>69</v>
+      </c>
+      <c r="V121" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD121" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG121" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="122" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" t="s">
         <v>129</v>
       </c>
-      <c r="C121" t="s">
-        <v>207</v>
-      </c>
-      <c r="U121" t="s">
-        <v>69</v>
-      </c>
-      <c r="V121" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB121" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM121" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="C122" t="s">
+        <v>209</v>
+      </c>
+      <c r="U122" t="s">
+        <v>69</v>
+      </c>
+      <c r="V122" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB122" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM122" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="123" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>130</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B123" t="s">
         <v>131</v>
       </c>
-      <c r="C122" t="s">
-        <v>207</v>
-      </c>
-      <c r="U122" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD122" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM122" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG122" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>132</v>
-      </c>
-      <c r="B123" t="s">
-        <v>133</v>
-      </c>
       <c r="C123" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="U123" t="s">
         <v>69</v>
@@ -3919,76 +3934,76 @@
       <c r="AD123" t="s">
         <v>69</v>
       </c>
+      <c r="AM123" t="s">
+        <v>69</v>
+      </c>
       <c r="BG123" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>132</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C124" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="U124" t="s">
         <v>69</v>
       </c>
+      <c r="AD124" t="s">
+        <v>69</v>
+      </c>
       <c r="BG124" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="125" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>132</v>
       </c>
       <c r="B125" t="s">
+        <v>134</v>
+      </c>
+      <c r="C125" t="s">
+        <v>209</v>
+      </c>
+      <c r="U125" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG125" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="126" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" t="s">
         <v>135</v>
       </c>
-      <c r="C125" t="s">
-        <v>207</v>
-      </c>
-      <c r="U125" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM125" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="C126" t="s">
+        <v>209</v>
+      </c>
+      <c r="U126" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM126" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="127" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>136</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B127" t="s">
         <v>137</v>
       </c>
-      <c r="C126" t="s">
-        <v>207</v>
-      </c>
-      <c r="U126" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD126" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM126" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG126" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>138</v>
-      </c>
-      <c r="B127" t="s">
-        <v>139</v>
-      </c>
       <c r="C127" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="U127" t="s">
         <v>69</v>
@@ -3996,108 +4011,114 @@
       <c r="AD127" t="s">
         <v>69</v>
       </c>
+      <c r="AM127" t="s">
+        <v>69</v>
+      </c>
       <c r="BG127" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>138</v>
       </c>
       <c r="B128" t="s">
+        <v>139</v>
+      </c>
+      <c r="C128" t="s">
+        <v>209</v>
+      </c>
+      <c r="U128" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD128" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG128" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="129" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" t="s">
         <v>140</v>
       </c>
-      <c r="C128" t="s">
-        <v>207</v>
-      </c>
-      <c r="U128" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD128" t="s">
+      <c r="C129" t="s">
+        <v>209</v>
+      </c>
+      <c r="U129" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD129" t="s">
         <v>123</v>
       </c>
-      <c r="AM128" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG128" t="s">
+      <c r="AM129" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG129" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>141</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B130" t="s">
         <v>142</v>
       </c>
-      <c r="C129" t="s">
-        <v>207</v>
-      </c>
-      <c r="AZ129" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>144</v>
-      </c>
-      <c r="B130" t="s">
-        <v>145</v>
-      </c>
       <c r="C130" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD130" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="AZ130" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="131" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>144</v>
       </c>
       <c r="B131" t="s">
+        <v>145</v>
+      </c>
+      <c r="C131" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD131" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="132" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+      <c r="B132" t="s">
         <v>146</v>
       </c>
-      <c r="C131" t="s">
-        <v>207</v>
-      </c>
-      <c r="O131" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>69</v>
-      </c>
-      <c r="V131" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB131" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL131" t="s">
+      <c r="C132" t="s">
+        <v>209</v>
+      </c>
+      <c r="O132" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>69</v>
+      </c>
+      <c r="V132" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB132" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL132" t="s">
         <v>80</v>
       </c>
-      <c r="BC131" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>226</v>
-      </c>
-      <c r="B132" t="s">
-        <v>227</v>
-      </c>
-      <c r="C132" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB132" t="s">
-        <v>69</v>
-      </c>
       <c r="BC132" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="133" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4105,13 +4126,16 @@
         <v>229</v>
       </c>
       <c r="C133" t="s">
-        <v>207</v>
-      </c>
-      <c r="V133" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="BB133" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC133" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="134" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4119,16 +4143,13 @@
         <v>231</v>
       </c>
       <c r="C134" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL134" t="s">
-        <v>80</v>
-      </c>
-      <c r="BC134" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="V134" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="135" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4136,238 +4157,184 @@
         <v>233</v>
       </c>
       <c r="C135" t="s">
-        <v>207</v>
-      </c>
-      <c r="V135" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB135" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="AL135" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC135" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="136" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
+        <v>235</v>
+      </c>
+      <c r="C136" t="s">
+        <v>209</v>
+      </c>
+      <c r="V136" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB136" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="137" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>234</v>
-      </c>
-      <c r="C136" t="s">
-        <v>207</v>
-      </c>
-      <c r="V136" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB136" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL136" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>235</v>
       </c>
       <c r="B137" t="s">
         <v>236</v>
       </c>
       <c r="C137" t="s">
-        <v>207</v>
+        <v>209</v>
+      </c>
+      <c r="V137" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB137" t="s">
+        <v>69</v>
       </c>
       <c r="AL137" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>237</v>
+      </c>
+      <c r="B138" t="s">
+        <v>238</v>
+      </c>
+      <c r="C138" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL138" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="139" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>154</v>
-      </c>
-      <c r="B138" t="s">
-        <v>237</v>
-      </c>
-      <c r="C138" t="s">
-        <v>207</v>
-      </c>
-      <c r="BG138" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>238</v>
       </c>
       <c r="B139" t="s">
         <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB139" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="BG139" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="140" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="C140" t="s">
-        <v>207</v>
-      </c>
-      <c r="L140" t="s">
-        <v>68</v>
-      </c>
-      <c r="U140" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE140" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN140" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT140" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV140" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD140" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="BB140" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="141" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>156</v>
       </c>
       <c r="B141" t="s">
+        <v>157</v>
+      </c>
+      <c r="C141" t="s">
+        <v>209</v>
+      </c>
+      <c r="L141" t="s">
+        <v>68</v>
+      </c>
+      <c r="U141" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE141" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN141" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT141" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV141" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD141" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="142" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>156</v>
+      </c>
+      <c r="B142" t="s">
         <v>158</v>
       </c>
-      <c r="C141" t="s">
-        <v>207</v>
-      </c>
-      <c r="P141" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC141" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+      <c r="C142" t="s">
+        <v>209</v>
+      </c>
+      <c r="P142" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC142" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="143" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>159</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B143" t="s">
         <v>160</v>
       </c>
-      <c r="C142" t="s">
-        <v>207</v>
-      </c>
-      <c r="H142" t="s">
-        <v>69</v>
-      </c>
-      <c r="N142" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y142" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE142" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH142" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT142" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD142" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>240</v>
-      </c>
-      <c r="B143" t="s">
-        <v>241</v>
-      </c>
       <c r="C143" t="s">
-        <v>207</v>
-      </c>
-      <c r="E143" t="s">
-        <v>69</v>
-      </c>
-      <c r="F143" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="H143" t="s">
         <v>69</v>
       </c>
-      <c r="I143" t="s">
-        <v>69</v>
-      </c>
-      <c r="K143" t="s">
-        <v>69</v>
-      </c>
-      <c r="M143" t="s">
-        <v>69</v>
-      </c>
       <c r="N143" t="s">
         <v>69</v>
       </c>
-      <c r="P143" t="s">
-        <v>69</v>
-      </c>
-      <c r="R143" t="s">
-        <v>69</v>
-      </c>
-      <c r="U143" t="s">
-        <v>69</v>
-      </c>
-      <c r="V143" t="s">
-        <v>69</v>
-      </c>
       <c r="Y143" t="s">
         <v>69</v>
       </c>
-      <c r="AC143" t="s">
-        <v>69</v>
-      </c>
       <c r="AE143" t="s">
         <v>69</v>
       </c>
       <c r="AH143" t="s">
         <v>69</v>
       </c>
-      <c r="AN143" t="s">
-        <v>80</v>
-      </c>
       <c r="AT143" t="s">
         <v>69</v>
       </c>
-      <c r="AV143" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY143" t="s">
-        <v>69</v>
-      </c>
       <c r="BD143" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="B144" t="s">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="C144" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E144" t="s">
         <v>69</v>
@@ -4403,9 +4370,6 @@
         <v>69</v>
       </c>
       <c r="Y144" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA144" t="s">
         <v>69</v>
       </c>
       <c r="AC144" t="s">
@@ -4433,15 +4397,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B145" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C145" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E145" t="s">
         <v>69</v>
@@ -4455,6 +4419,9 @@
       <c r="I145" t="s">
         <v>69</v>
       </c>
+      <c r="K145" t="s">
+        <v>69</v>
+      </c>
       <c r="M145" t="s">
         <v>69</v>
       </c>
@@ -4474,6 +4441,9 @@
         <v>69</v>
       </c>
       <c r="Y145" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA145" t="s">
         <v>69</v>
       </c>
       <c r="AC145" t="s">
@@ -4501,383 +4471,425 @@
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="C146" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD146" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="147" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="E146" t="s">
+        <v>69</v>
+      </c>
+      <c r="F146" t="s">
+        <v>69</v>
+      </c>
+      <c r="H146" t="s">
+        <v>69</v>
+      </c>
+      <c r="I146" t="s">
+        <v>69</v>
+      </c>
+      <c r="M146" t="s">
+        <v>69</v>
+      </c>
+      <c r="N146" t="s">
+        <v>69</v>
+      </c>
+      <c r="P146" t="s">
+        <v>69</v>
+      </c>
+      <c r="R146" t="s">
+        <v>69</v>
+      </c>
+      <c r="U146" t="s">
+        <v>69</v>
+      </c>
+      <c r="V146" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN146" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY146" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD146" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="147" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>165</v>
       </c>
       <c r="B147" t="s">
+        <v>244</v>
+      </c>
+      <c r="C147" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD147" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>165</v>
+      </c>
+      <c r="B148" t="s">
         <v>166</v>
       </c>
-      <c r="C147" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y147" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC147" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD147" t="s">
+      <c r="C148" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y148" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC148" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD148" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="148" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>167</v>
-      </c>
-      <c r="B148" t="s">
-        <v>168</v>
-      </c>
-      <c r="C148" t="s">
-        <v>207</v>
-      </c>
-      <c r="N148" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD148" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="149" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>167</v>
       </c>
       <c r="B149" t="s">
+        <v>168</v>
+      </c>
+      <c r="C149" t="s">
+        <v>209</v>
+      </c>
+      <c r="N149" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD149" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="150" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>167</v>
+      </c>
+      <c r="B150" t="s">
         <v>169</v>
       </c>
-      <c r="C149" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC149" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD149" t="s">
+      <c r="C150" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC150" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD150" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+    <row r="151" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>170</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B151" t="s">
         <v>171</v>
       </c>
-      <c r="C150" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC150" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="151" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>243</v>
-      </c>
-      <c r="B151" t="s">
-        <v>244</v>
-      </c>
       <c r="C151" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y151" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="AC151" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="152" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="B152" t="s">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="C152" t="s">
-        <v>207</v>
-      </c>
-      <c r="N152" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="Y152" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="153" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="AC152" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="153" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>174</v>
       </c>
       <c r="B153" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="C153" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC153" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="154" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="N153" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="154" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>174</v>
+      </c>
+      <c r="B154" t="s">
+        <v>247</v>
+      </c>
+      <c r="C154" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC154" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="155" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>176</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B155" t="s">
         <v>177</v>
       </c>
-      <c r="C154" t="s">
-        <v>207</v>
-      </c>
-      <c r="N154" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y154" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD154" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="155" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>178</v>
-      </c>
-      <c r="B155" t="s">
-        <v>179</v>
-      </c>
       <c r="C155" t="s">
-        <v>207</v>
-      </c>
-      <c r="V155" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="156" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="N155" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD155" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="156" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>178</v>
       </c>
       <c r="B156" t="s">
+        <v>179</v>
+      </c>
+      <c r="C156" t="s">
+        <v>209</v>
+      </c>
+      <c r="V156" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="157" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>178</v>
+      </c>
+      <c r="B157" t="s">
         <v>180</v>
       </c>
-      <c r="C156" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB156" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="157" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="C157" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB157" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="158" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>181</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>182</v>
       </c>
-      <c r="C157" t="s">
-        <v>207</v>
-      </c>
-      <c r="V157" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="158" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+      <c r="C158" t="s">
+        <v>209</v>
+      </c>
+      <c r="V158" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="159" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>183</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B159" t="s">
         <v>184</v>
       </c>
-      <c r="C158" t="s">
-        <v>207</v>
-      </c>
-      <c r="H158" t="s">
-        <v>69</v>
-      </c>
-      <c r="P158" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y158" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC158" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD158" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE158" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH158" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT158" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV158" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD158" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="159" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>185</v>
-      </c>
-      <c r="B159" t="s">
-        <v>186</v>
-      </c>
       <c r="C159" t="s">
-        <v>207</v>
-      </c>
-      <c r="E159" t="s">
-        <v>69</v>
-      </c>
-      <c r="F159" t="s">
-        <v>69</v>
-      </c>
-      <c r="T159" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI159" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK159" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB159" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC159" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG159" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="160" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="H159" t="s">
+        <v>69</v>
+      </c>
+      <c r="P159" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y159" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC159" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD159" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE159" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH159" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT159" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV159" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD159" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="160" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>185</v>
       </c>
       <c r="B160" t="s">
+        <v>186</v>
+      </c>
+      <c r="C160" t="s">
+        <v>209</v>
+      </c>
+      <c r="E160" t="s">
+        <v>69</v>
+      </c>
+      <c r="F160" t="s">
+        <v>69</v>
+      </c>
+      <c r="T160" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK160" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB160" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC160" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG160" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>185</v>
+      </c>
+      <c r="B161" t="s">
         <v>187</v>
       </c>
-      <c r="C160" t="s">
-        <v>207</v>
-      </c>
-      <c r="BB160" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG160" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>190</v>
-      </c>
-      <c r="B161" t="s">
-        <v>246</v>
-      </c>
       <c r="C161" t="s">
-        <v>207</v>
-      </c>
-      <c r="AY161" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="BB161" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG161" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>190</v>
       </c>
       <c r="B162" t="s">
+        <v>248</v>
+      </c>
+      <c r="C162" t="s">
+        <v>209</v>
+      </c>
+      <c r="AY162" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>190</v>
+      </c>
+      <c r="B163" t="s">
         <v>191</v>
       </c>
-      <c r="C162" t="s">
-        <v>207</v>
-      </c>
-      <c r="N162" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y162" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY162" t="s">
+      <c r="C163" t="s">
+        <v>209</v>
+      </c>
+      <c r="N163" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y163" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY163" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>194</v>
-      </c>
-      <c r="B163" t="s">
-        <v>195</v>
-      </c>
-      <c r="C163" t="s">
-        <v>207</v>
-      </c>
-      <c r="N163" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>194</v>
       </c>
       <c r="B164" t="s">
+        <v>195</v>
+      </c>
+      <c r="C164" t="s">
+        <v>209</v>
+      </c>
+      <c r="N164" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>194</v>
+      </c>
+      <c r="B165" t="s">
         <v>196</v>
       </c>
-      <c r="C164" t="s">
-        <v>207</v>
-      </c>
-      <c r="N164" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY164" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>197</v>
-      </c>
-      <c r="B165" t="s">
-        <v>198</v>
-      </c>
       <c r="C165" t="s">
-        <v>207</v>
-      </c>
-      <c r="U165" t="s">
-        <v>69</v>
-      </c>
-      <c r="V165" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB165" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM165" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG165" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="N165" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY165" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4885,104 +4897,130 @@
         <v>200</v>
       </c>
       <c r="C166" t="s">
+        <v>209</v>
+      </c>
+      <c r="U166" t="s">
+        <v>69</v>
+      </c>
+      <c r="V166" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB166" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM166" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG166" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>201</v>
+      </c>
+      <c r="B167" t="s">
+        <v>202</v>
+      </c>
+      <c r="C167" t="s">
+        <v>209</v>
+      </c>
+      <c r="U167" t="s">
+        <v>69</v>
+      </c>
+      <c r="V167" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG167" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>205</v>
+      </c>
+      <c r="B168" t="s">
+        <v>249</v>
+      </c>
+      <c r="C168" t="s">
+        <v>209</v>
+      </c>
+      <c r="N168" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD168" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG168" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>205</v>
+      </c>
+      <c r="B169" t="s">
+        <v>206</v>
+      </c>
+      <c r="C169" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL169" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM169" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB169" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC169" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG169" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>250</v>
+      </c>
+      <c r="B170" t="s">
+        <v>251</v>
+      </c>
+      <c r="C170" t="s">
+        <v>209</v>
+      </c>
+      <c r="AM170" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB170" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="171" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>207</v>
       </c>
-      <c r="U166" t="s">
-        <v>69</v>
-      </c>
-      <c r="V166" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG166" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>203</v>
-      </c>
-      <c r="B167" t="s">
-        <v>247</v>
-      </c>
-      <c r="C167" t="s">
-        <v>207</v>
-      </c>
-      <c r="N167" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD167" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG167" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>203</v>
-      </c>
-      <c r="B168" t="s">
-        <v>204</v>
-      </c>
-      <c r="C168" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL168" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM168" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB168" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC168" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG168" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>248</v>
-      </c>
-      <c r="B169" t="s">
-        <v>249</v>
-      </c>
-      <c r="C169" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM169" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB169" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>205</v>
-      </c>
-      <c r="B170" t="s">
-        <v>206</v>
-      </c>
-      <c r="C170" t="s">
-        <v>207</v>
-      </c>
-      <c r="V170" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB170" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL170" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM170" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB170" t="s">
+      <c r="B171" t="s">
+        <v>208</v>
+      </c>
+      <c r="C171" t="s">
+        <v>209</v>
+      </c>
+      <c r="V171" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB171" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL171" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM171" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB171" t="s">
         <v>69</v>
       </c>
     </row>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CCED1F-C640-4F3F-B785-5B2EBAE49C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4983C4B-9634-4683-89F6-7635532D3E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 21-08-2026'!$A$1:$BM$171</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 27-08-2026'!$A$1:$BM$171</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1122,9 +1122,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM171"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>178</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>185</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>194</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>207</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>65</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>70</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>72</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>76</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>78</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>210</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>212</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>212</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>215</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>83</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>85</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>87</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>89</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>89</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>91</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>91</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>218</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>220</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>94</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>96</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>98</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>100</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>222</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>102</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>225</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>104</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>104</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>120</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>127</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>127</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>132</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>136</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>138</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>141</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>144</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>234</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>234</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>237</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>154</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>240</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>156</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>159</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>242</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>161</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="147" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="148" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>165</v>
       </c>
@@ -4573,7 +4573,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="149" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="150" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>167</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="151" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="152" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>245</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="153" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>174</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="154" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>174</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="155" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>176</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="156" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>178</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="159" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="160" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>185</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>190</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>194</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>194</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>201</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>205</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>205</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>250</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="171" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>207</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4983C4B-9634-4683-89F6-7635532D3E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6C0E29-F4E9-4EB9-84C7-0768BD8622C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 27-08-2026'!$A$1:$BM$171</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 02-09-2026'!$A$1:$BM$171</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6C0E29-F4E9-4EB9-84C7-0768BD8622C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8549F63D-D4B6-4318-8B34-F14883BFCDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 02-09-2026'!$A$1:$BM$171</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 06-09-2026'!$A$1:$BM$171</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8549F63D-D4B6-4318-8B34-F14883BFCDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C80D9BB-2A61-4F1A-A1E3-B10EBCA14722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C80D9BB-2A61-4F1A-A1E3-B10EBCA14722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1B295F-693B-4E9B-8E67-68B762FB0F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 06-09-2026'!$A$1:$BM$171</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 07-09-2026'!$A$1:$BM$171</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -692,12 +692,6 @@
     <t>DIS05 (D0533L)</t>
   </si>
   <si>
-    <t>Share Notes</t>
-  </si>
-  <si>
-    <t>ECN (1.0)</t>
-  </si>
-  <si>
     <t>PDC-DK (2.0)</t>
   </si>
   <si>
@@ -744,6 +738,12 @@
   </si>
   <si>
     <t>Shared EKG Recording (2.0)</t>
+  </si>
+  <si>
+    <t>Shared Notes</t>
+  </si>
+  <si>
+    <t>Shared Notes (1.0)</t>
   </si>
   <si>
     <t>Sundhedsjournal</t>
@@ -3561,16 +3561,22 @@
     </row>
     <row r="104" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>102</v>
+      </c>
+      <c r="B104" t="s">
         <v>222</v>
       </c>
-      <c r="B104" t="s">
-        <v>223</v>
-      </c>
       <c r="C104" t="s">
         <v>209</v>
       </c>
+      <c r="AM104" t="s">
+        <v>68</v>
+      </c>
       <c r="BG104" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="BH104" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:60" x14ac:dyDescent="0.3">
@@ -3578,36 +3584,30 @@
         <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>224</v>
+        <v>103</v>
       </c>
       <c r="C105" t="s">
         <v>209</v>
       </c>
-      <c r="AM105" t="s">
-        <v>68</v>
+      <c r="E105" t="s">
+        <v>69</v>
+      </c>
+      <c r="F105" t="s">
+        <v>69</v>
       </c>
       <c r="BG105" t="s">
         <v>69</v>
-      </c>
-      <c r="BH105" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="106" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>102</v>
+        <v>223</v>
       </c>
       <c r="B106" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="C106" t="s">
         <v>209</v>
-      </c>
-      <c r="E106" t="s">
-        <v>69</v>
-      </c>
-      <c r="F106" t="s">
-        <v>69</v>
       </c>
       <c r="BG106" t="s">
         <v>69</v>
@@ -3615,13 +3615,19 @@
     </row>
     <row r="107" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="C107" t="s">
         <v>209</v>
+      </c>
+      <c r="AM107" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>80</v>
       </c>
       <c r="BG107" t="s">
         <v>69</v>
@@ -3632,41 +3638,41 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C108" t="s">
         <v>209</v>
       </c>
-      <c r="AM108" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN108" t="s">
-        <v>80</v>
-      </c>
       <c r="BG108" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C109" t="s">
         <v>209</v>
       </c>
+      <c r="T109" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK109" t="s">
+        <v>69</v>
+      </c>
       <c r="BG109" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C110" t="s">
         <v>209</v>
@@ -3683,56 +3689,50 @@
     </row>
     <row r="111" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
         <v>209</v>
       </c>
-      <c r="T111" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK111" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG111" t="s">
+      <c r="W111" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW111" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C112" t="s">
         <v>209</v>
       </c>
-      <c r="W112" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW112" t="s">
+      <c r="T112" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK112" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG112" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="113" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B113" t="s">
-        <v>114</v>
+        <v>225</v>
       </c>
       <c r="C113" t="s">
         <v>209</v>
-      </c>
-      <c r="T113" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK113" t="s">
-        <v>69</v>
       </c>
       <c r="BG113" t="s">
         <v>69</v>
@@ -3743,7 +3743,7 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>227</v>
+        <v>116</v>
       </c>
       <c r="C114" t="s">
         <v>209</v>
@@ -3754,13 +3754,19 @@
     </row>
     <row r="115" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C115" t="s">
         <v>209</v>
+      </c>
+      <c r="AM115" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN115" t="s">
+        <v>80</v>
       </c>
       <c r="BG115" t="s">
         <v>69</v>
@@ -3771,16 +3777,16 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C116" t="s">
         <v>209</v>
       </c>
-      <c r="AM116" t="s">
-        <v>68</v>
+      <c r="AI116" t="s">
+        <v>69</v>
       </c>
       <c r="AN116" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="BG116" t="s">
         <v>69</v>
@@ -3788,21 +3794,15 @@
     </row>
     <row r="117" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B117" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
         <v>209</v>
       </c>
-      <c r="AI117" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN117" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG117" t="s">
+      <c r="BA117" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3811,21 +3811,33 @@
         <v>120</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C118" t="s">
         <v>209</v>
       </c>
-      <c r="BA118" t="s">
+      <c r="U118" t="s">
+        <v>69</v>
+      </c>
+      <c r="V118" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM118" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY118" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG118" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C119" t="s">
         <v>209</v>
@@ -3836,11 +3848,11 @@
       <c r="V119" t="s">
         <v>69</v>
       </c>
-      <c r="AM119" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY119" t="s">
-        <v>69</v>
+      <c r="AD119" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC119" t="s">
+        <v>68</v>
       </c>
       <c r="BG119" t="s">
         <v>69</v>
@@ -3848,10 +3860,10 @@
     </row>
     <row r="120" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C120" t="s">
         <v>209</v>
@@ -3864,9 +3876,6 @@
       </c>
       <c r="AD120" t="s">
         <v>69</v>
-      </c>
-      <c r="BC120" t="s">
-        <v>68</v>
       </c>
       <c r="BG120" t="s">
         <v>69</v>
@@ -3877,7 +3886,7 @@
         <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C121" t="s">
         <v>209</v>
@@ -3888,19 +3897,19 @@
       <c r="V121" t="s">
         <v>69</v>
       </c>
-      <c r="AD121" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG121" t="s">
+      <c r="AB121" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM121" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C122" t="s">
         <v>209</v>
@@ -3908,22 +3917,22 @@
       <c r="U122" t="s">
         <v>69</v>
       </c>
-      <c r="V122" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB122" t="s">
+      <c r="AD122" t="s">
         <v>69</v>
       </c>
       <c r="AM122" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG122" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="123" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B123" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C123" t="s">
         <v>209</v>
@@ -3932,9 +3941,6 @@
         <v>69</v>
       </c>
       <c r="AD123" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM123" t="s">
         <v>69</v>
       </c>
       <c r="BG123" t="s">
@@ -3946,7 +3952,7 @@
         <v>132</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C124" t="s">
         <v>209</v>
@@ -3954,11 +3960,8 @@
       <c r="U124" t="s">
         <v>69</v>
       </c>
-      <c r="AD124" t="s">
-        <v>69</v>
-      </c>
       <c r="BG124" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="125" spans="1:59" x14ac:dyDescent="0.3">
@@ -3966,7 +3969,7 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C125" t="s">
         <v>209</v>
@@ -3974,16 +3977,16 @@
       <c r="U125" t="s">
         <v>69</v>
       </c>
-      <c r="BG125" t="s">
-        <v>68</v>
+      <c r="AM125" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="126" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C126" t="s">
         <v>209</v>
@@ -3991,16 +3994,22 @@
       <c r="U126" t="s">
         <v>69</v>
       </c>
+      <c r="AD126" t="s">
+        <v>69</v>
+      </c>
       <c r="AM126" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG126" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="127" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C127" t="s">
         <v>209</v>
@@ -4009,9 +4018,6 @@
         <v>69</v>
       </c>
       <c r="AD127" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM127" t="s">
         <v>69</v>
       </c>
       <c r="BG127" t="s">
@@ -4023,7 +4029,7 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C128" t="s">
         <v>209</v>
@@ -4032,46 +4038,40 @@
         <v>69</v>
       </c>
       <c r="AD128" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM128" t="s">
         <v>69</v>
       </c>
       <c r="BG128" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
     </row>
     <row r="129" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B129" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C129" t="s">
         <v>209</v>
       </c>
-      <c r="U129" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD129" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM129" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG129" t="s">
-        <v>123</v>
+      <c r="AZ129" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="130" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B130" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C130" t="s">
         <v>209</v>
       </c>
-      <c r="AZ130" t="s">
+      <c r="AD130" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4080,42 +4080,45 @@
         <v>144</v>
       </c>
       <c r="B131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C131" t="s">
         <v>209</v>
       </c>
-      <c r="AD131" t="s">
-        <v>69</v>
+      <c r="O131" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>69</v>
+      </c>
+      <c r="V131" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB131" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL131" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC131" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="C132" t="s">
         <v>209</v>
       </c>
-      <c r="O132" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>69</v>
-      </c>
-      <c r="V132" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB132" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL132" t="s">
-        <v>80</v>
+      <c r="BB132" t="s">
+        <v>69</v>
       </c>
       <c r="BC132" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="133" spans="1:59" x14ac:dyDescent="0.3">
@@ -4128,10 +4131,7 @@
       <c r="C133" t="s">
         <v>209</v>
       </c>
-      <c r="BB133" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC133" t="s">
+      <c r="V133" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4145,8 +4145,11 @@
       <c r="C134" t="s">
         <v>209</v>
       </c>
-      <c r="V134" t="s">
-        <v>69</v>
+      <c r="AL134" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC134" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="135" spans="1:59" x14ac:dyDescent="0.3">
@@ -4159,20 +4162,20 @@
       <c r="C135" t="s">
         <v>209</v>
       </c>
-      <c r="AL135" t="s">
-        <v>80</v>
-      </c>
-      <c r="BC135" t="s">
-        <v>68</v>
+      <c r="V135" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB135" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>234</v>
       </c>
-      <c r="B136" t="s">
-        <v>235</v>
-      </c>
       <c r="C136" t="s">
         <v>209</v>
       </c>
@@ -4181,11 +4184,14 @@
       </c>
       <c r="AB136" t="s">
         <v>69</v>
+      </c>
+      <c r="AL136" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="137" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
         <v>236</v>
@@ -4193,33 +4199,27 @@
       <c r="C137" t="s">
         <v>209</v>
       </c>
-      <c r="V137" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB137" t="s">
-        <v>69</v>
-      </c>
       <c r="AL137" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>154</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
       </c>
-      <c r="B138" t="s">
-        <v>238</v>
-      </c>
       <c r="C138" t="s">
         <v>209</v>
       </c>
-      <c r="AL138" t="s">
-        <v>80</v>
+      <c r="BG138" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="139" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
         <v>239</v>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1B295F-693B-4E9B-8E67-68B762FB0F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003204A9-93E6-40E1-B551-2C97A7AC7322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 07-09-2026'!$A$1:$BM$171</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 09-09-2026'!$A$1:$BM$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="256">
   <si>
     <t>Standard</t>
   </si>
@@ -509,6 +509,12 @@
     <t>XBIN01 (XB0131X)</t>
   </si>
   <si>
+    <t>ReferralAttachment</t>
+  </si>
+  <si>
+    <t>XBIN02 (XB0210X)</t>
+  </si>
+  <si>
     <t>NegativeReceipt</t>
   </si>
   <si>
@@ -780,6 +786,12 @@
   </si>
   <si>
     <t>XRPT04 (XR0432P)</t>
+  </si>
+  <si>
+    <t>GeneticsReport</t>
+  </si>
+  <si>
+    <t>XRPT07 (XR0731G)</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BM171"/>
+  <dimension ref="A1:BM173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:65" x14ac:dyDescent="0.3">
@@ -2401,43 +2413,7 @@
       <c r="C54" t="s">
         <v>67</v>
       </c>
-      <c r="H54" t="s">
-        <v>69</v>
-      </c>
-      <c r="N54" t="s">
-        <v>69</v>
-      </c>
-      <c r="P54" t="s">
-        <v>69</v>
-      </c>
-      <c r="U54" t="s">
-        <v>69</v>
-      </c>
-      <c r="V54" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>69</v>
-      </c>
       <c r="AC54" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE54" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH54" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT54" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV54" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY54" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD54" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2501,8 +2477,44 @@
       <c r="C56" t="s">
         <v>67</v>
       </c>
+      <c r="H56" t="s">
+        <v>69</v>
+      </c>
+      <c r="N56" t="s">
+        <v>69</v>
+      </c>
+      <c r="P56" t="s">
+        <v>69</v>
+      </c>
+      <c r="U56" t="s">
+        <v>69</v>
+      </c>
+      <c r="V56" t="s">
+        <v>69</v>
+      </c>
       <c r="Y56" t="s">
         <v>69</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY56" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD56" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:64" x14ac:dyDescent="0.3">
@@ -2515,27 +2527,27 @@
       <c r="C57" t="s">
         <v>67</v>
       </c>
-      <c r="N57" t="s">
+      <c r="Y57" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B58" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s">
         <v>67</v>
       </c>
-      <c r="R58" t="s">
+      <c r="N58" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B59" t="s">
         <v>171</v>
@@ -2543,7 +2555,7 @@
       <c r="C59" t="s">
         <v>67</v>
       </c>
-      <c r="Y59" t="s">
+      <c r="R59" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2557,16 +2569,7 @@
       <c r="C60" t="s">
         <v>67</v>
       </c>
-      <c r="E60" t="s">
-        <v>69</v>
-      </c>
-      <c r="F60" t="s">
-        <v>69</v>
-      </c>
-      <c r="I60" t="s">
-        <v>69</v>
-      </c>
-      <c r="M60" t="s">
+      <c r="Y60" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2580,7 +2583,16 @@
       <c r="C61" t="s">
         <v>67</v>
       </c>
-      <c r="N61" t="s">
+      <c r="E61" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" t="s">
+        <v>69</v>
+      </c>
+      <c r="I61" t="s">
+        <v>69</v>
+      </c>
+      <c r="M61" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2594,7 +2606,7 @@
       <c r="C62" t="s">
         <v>67</v>
       </c>
-      <c r="Y62" t="s">
+      <c r="N62" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2608,27 +2620,27 @@
       <c r="C63" t="s">
         <v>67</v>
       </c>
-      <c r="V63" t="s">
+      <c r="Y63" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C64" t="s">
         <v>67</v>
       </c>
-      <c r="AB64" t="s">
+      <c r="V64" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B65" t="s">
         <v>182</v>
@@ -2636,7 +2648,7 @@
       <c r="C65" t="s">
         <v>67</v>
       </c>
-      <c r="V65" t="s">
+      <c r="AB65" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2650,53 +2662,8 @@
       <c r="C66" t="s">
         <v>67</v>
       </c>
-      <c r="H66" t="s">
-        <v>69</v>
-      </c>
-      <c r="K66" t="s">
-        <v>69</v>
-      </c>
-      <c r="N66" t="s">
-        <v>69</v>
-      </c>
-      <c r="P66" t="s">
-        <v>69</v>
-      </c>
-      <c r="R66" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD66" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE66" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH66" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN66" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT66" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV66" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY66" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD66" t="s">
-        <v>68</v>
+      <c r="V66" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:65" x14ac:dyDescent="0.3">
@@ -2709,51 +2676,87 @@
       <c r="C67" t="s">
         <v>67</v>
       </c>
-      <c r="D67" t="s">
-        <v>69</v>
-      </c>
-      <c r="T67" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI67" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ67" t="s">
-        <v>69</v>
-      </c>
-      <c r="BM67" t="s">
-        <v>69</v>
+      <c r="H67" t="s">
+        <v>69</v>
+      </c>
+      <c r="K67" t="s">
+        <v>69</v>
+      </c>
+      <c r="N67" t="s">
+        <v>69</v>
+      </c>
+      <c r="P67" t="s">
+        <v>69</v>
+      </c>
+      <c r="R67" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY67" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD67" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C68" t="s">
         <v>67</v>
       </c>
-      <c r="X68" t="s">
-        <v>68</v>
-      </c>
-      <c r="AP68" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ68" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR68" t="s">
-        <v>68</v>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="T68" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ68" t="s">
+        <v>69</v>
+      </c>
+      <c r="BM68" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B69" t="s">
         <v>189</v>
@@ -2761,8 +2764,17 @@
       <c r="C69" t="s">
         <v>67</v>
       </c>
-      <c r="Y69" t="s">
-        <v>69</v>
+      <c r="X69" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP69" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ69" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR69" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:65" x14ac:dyDescent="0.3">
@@ -2775,14 +2787,8 @@
       <c r="C70" t="s">
         <v>67</v>
       </c>
-      <c r="N70" t="s">
-        <v>69</v>
-      </c>
       <c r="Y70" t="s">
         <v>69</v>
-      </c>
-      <c r="AC70" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:65" x14ac:dyDescent="0.3">
@@ -2795,8 +2801,14 @@
       <c r="C71" t="s">
         <v>67</v>
       </c>
+      <c r="N71" t="s">
+        <v>69</v>
+      </c>
       <c r="Y71" t="s">
         <v>69</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:65" x14ac:dyDescent="0.3">
@@ -2809,39 +2821,39 @@
       <c r="C72" t="s">
         <v>67</v>
       </c>
-      <c r="N72" t="s">
+      <c r="Y72" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C73" t="s">
         <v>67</v>
       </c>
       <c r="N73" t="s">
         <v>69</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC73" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
         <v>198</v>
       </c>
       <c r="C74" t="s">
         <v>67</v>
+      </c>
+      <c r="N74" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>69</v>
       </c>
       <c r="AC74" t="s">
         <v>68</v>
@@ -2857,14 +2869,8 @@
       <c r="C75" t="s">
         <v>67</v>
       </c>
-      <c r="U75" t="s">
-        <v>69</v>
-      </c>
-      <c r="V75" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB75" t="s">
-        <v>69</v>
+      <c r="AC75" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:65" x14ac:dyDescent="0.3">
@@ -2883,6 +2889,9 @@
       <c r="V76" t="s">
         <v>69</v>
       </c>
+      <c r="AB76" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="77" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -2894,8 +2903,11 @@
       <c r="C77" t="s">
         <v>67</v>
       </c>
-      <c r="O77" t="s">
-        <v>68</v>
+      <c r="U77" t="s">
+        <v>69</v>
+      </c>
+      <c r="V77" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:65" x14ac:dyDescent="0.3">
@@ -2908,8 +2920,8 @@
       <c r="C78" t="s">
         <v>67</v>
       </c>
-      <c r="AA78" t="s">
-        <v>80</v>
+      <c r="O78" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:65" x14ac:dyDescent="0.3">
@@ -2922,153 +2934,150 @@
       <c r="C79" t="s">
         <v>67</v>
       </c>
-      <c r="O79" t="s">
-        <v>69</v>
+      <c r="AA79" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>209</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="C80" t="s">
-        <v>209</v>
-      </c>
-      <c r="L80" t="s">
-        <v>68</v>
-      </c>
-      <c r="V80" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE80" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="O80" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>209</v>
-      </c>
-      <c r="M81" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL81" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM81" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW81" t="s">
-        <v>68</v>
-      </c>
-      <c r="BB81" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC81" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG81" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="L81" t="s">
+        <v>68</v>
+      </c>
+      <c r="V81" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C82" t="s">
-        <v>209</v>
-      </c>
-      <c r="U82" t="s">
-        <v>69</v>
-      </c>
-      <c r="V82" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS82" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT82" t="s">
+        <v>211</v>
+      </c>
+      <c r="M82" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM82" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW82" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB82" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC82" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG82" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B83" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C83" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U83" t="s">
+        <v>69</v>
+      </c>
+      <c r="V83" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS83" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT83" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>209</v>
-      </c>
-      <c r="L84" t="s">
-        <v>68</v>
-      </c>
-      <c r="V84" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE84" t="s">
-        <v>68</v>
+        <v>211</v>
+      </c>
+      <c r="U84" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C85" t="s">
-        <v>209</v>
-      </c>
-      <c r="W85" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW85" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="L85" t="s">
+        <v>68</v>
+      </c>
+      <c r="V85" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE85" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="B86" t="s">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="C86" t="s">
-        <v>209</v>
-      </c>
-      <c r="BB86" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG86" t="s">
+        <v>211</v>
+      </c>
+      <c r="W86" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW86" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3080,10 +3089,10 @@
         <v>213</v>
       </c>
       <c r="C87" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC87" t="s">
-        <v>80</v>
+        <v>211</v>
+      </c>
+      <c r="BB87" t="s">
+        <v>69</v>
       </c>
       <c r="BG87" t="s">
         <v>69</v>
@@ -3091,22 +3100,16 @@
     </row>
     <row r="88" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
-        <v>209</v>
-      </c>
-      <c r="AL88" t="s">
-        <v>68</v>
-      </c>
-      <c r="BB88" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="BC88" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="BG88" t="s">
         <v>69</v>
@@ -3114,84 +3117,36 @@
     </row>
     <row r="89" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B89" t="s">
         <v>216</v>
       </c>
       <c r="C89" t="s">
-        <v>209</v>
-      </c>
-      <c r="G89" t="s">
-        <v>69</v>
-      </c>
-      <c r="J89" t="s">
-        <v>80</v>
-      </c>
-      <c r="O89" t="s">
-        <v>69</v>
-      </c>
-      <c r="U89" t="s">
-        <v>69</v>
-      </c>
-      <c r="V89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AX89" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY89" t="s">
-        <v>69</v>
-      </c>
-      <c r="BA89" t="s">
+        <v>211</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB89" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC89" t="s">
         <v>69</v>
       </c>
       <c r="BG89" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK89" t="s">
-        <v>68</v>
-      </c>
-      <c r="BL89" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="C90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G90" t="s">
         <v>69</v>
@@ -3244,9 +3199,6 @@
       <c r="BA90" t="s">
         <v>69</v>
       </c>
-      <c r="BF90" t="s">
-        <v>69</v>
-      </c>
       <c r="BG90" t="s">
         <v>68</v>
       </c>
@@ -3259,13 +3211,13 @@
     </row>
     <row r="91" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G91" t="s">
         <v>69</v>
@@ -3318,6 +3270,9 @@
       <c r="BA91" t="s">
         <v>69</v>
       </c>
+      <c r="BF91" t="s">
+        <v>69</v>
+      </c>
       <c r="BG91" t="s">
         <v>68</v>
       </c>
@@ -3330,27 +3285,84 @@
     </row>
     <row r="92" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="G92" t="s">
+        <v>69</v>
+      </c>
+      <c r="J92" t="s">
+        <v>80</v>
+      </c>
+      <c r="O92" t="s">
+        <v>69</v>
+      </c>
+      <c r="U92" t="s">
+        <v>69</v>
+      </c>
+      <c r="V92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ92" t="s">
+        <v>69</v>
       </c>
       <c r="AS92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AX92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY92" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA92" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG92" t="s">
+        <v>68</v>
+      </c>
+      <c r="BK92" t="s">
+        <v>68</v>
+      </c>
+      <c r="BL92" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C93" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AS93" t="s">
         <v>69</v>
@@ -3358,18 +3370,15 @@
     </row>
     <row r="94" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B94" t="s">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="C94" t="s">
-        <v>209</v>
-      </c>
-      <c r="V94" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD94" t="s">
+        <v>211</v>
+      </c>
+      <c r="AS94" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3378,30 +3387,33 @@
         <v>89</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="V95" t="s">
         <v>69</v>
       </c>
-      <c r="AC95" t="s">
-        <v>68</v>
+      <c r="AD95" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C96" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD96" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="V96" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:60" x14ac:dyDescent="0.3">
@@ -3409,42 +3421,39 @@
         <v>91</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
-      </c>
-      <c r="V97" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y97" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB97" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC97" t="s">
-        <v>68</v>
+        <v>211</v>
       </c>
       <c r="AD97" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="B98" t="s">
-        <v>219</v>
+        <v>93</v>
       </c>
       <c r="C98" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="V98" t="s">
         <v>69</v>
       </c>
+      <c r="Y98" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB98" t="s">
+        <v>69</v>
+      </c>
       <c r="AC98" t="s">
         <v>68</v>
+      </c>
+      <c r="AD98" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:60" x14ac:dyDescent="0.3">
@@ -3455,12 +3464,9 @@
         <v>221</v>
       </c>
       <c r="C99" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="V99" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB99" t="s">
         <v>69</v>
       </c>
       <c r="AC99" t="s">
@@ -3469,15 +3475,18 @@
     </row>
     <row r="100" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>223</v>
       </c>
       <c r="C100" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="V100" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB100" t="s">
         <v>69</v>
       </c>
       <c r="AC100" t="s">
@@ -3486,97 +3495,94 @@
     </row>
     <row r="101" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B101" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="V101" t="s">
         <v>69</v>
       </c>
-      <c r="AD101" t="s">
-        <v>69</v>
+      <c r="AC101" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="V102" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD102" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
-        <v>209</v>
-      </c>
-      <c r="H103" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="V103" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV103" t="s">
-        <v>69</v>
-      </c>
-      <c r="BA103" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="104" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>222</v>
+        <v>101</v>
       </c>
       <c r="C104" t="s">
-        <v>209</v>
-      </c>
-      <c r="AM104" t="s">
-        <v>68</v>
-      </c>
-      <c r="BG104" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH104" t="s">
-        <v>80</v>
+        <v>211</v>
+      </c>
+      <c r="H104" t="s">
+        <v>69</v>
+      </c>
+      <c r="V104" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV104" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA104" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:60" x14ac:dyDescent="0.3">
@@ -3584,30 +3590,36 @@
         <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="C105" t="s">
-        <v>209</v>
-      </c>
-      <c r="E105" t="s">
-        <v>69</v>
-      </c>
-      <c r="F105" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="AM105" t="s">
+        <v>68</v>
       </c>
       <c r="BG105" t="s">
         <v>69</v>
+      </c>
+      <c r="BH105" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="106" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>224</v>
+        <v>103</v>
       </c>
       <c r="C106" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="E106" t="s">
+        <v>69</v>
+      </c>
+      <c r="F106" t="s">
+        <v>69</v>
       </c>
       <c r="BG106" t="s">
         <v>69</v>
@@ -3615,19 +3627,13 @@
     </row>
     <row r="107" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="C107" t="s">
-        <v>209</v>
-      </c>
-      <c r="AM107" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN107" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="BG107" t="s">
         <v>69</v>
@@ -3638,44 +3644,44 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C108" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="AM108" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>80</v>
       </c>
       <c r="BG108" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="109" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C109" t="s">
-        <v>209</v>
-      </c>
-      <c r="T109" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK109" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="BG109" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T110" t="s">
         <v>68</v>
@@ -3689,50 +3695,56 @@
     </row>
     <row r="111" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C111" t="s">
-        <v>209</v>
-      </c>
-      <c r="W111" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW111" t="s">
+        <v>211</v>
+      </c>
+      <c r="T111" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK111" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG111" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C112" t="s">
-        <v>209</v>
-      </c>
-      <c r="T112" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK112" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG112" t="s">
+        <v>211</v>
+      </c>
+      <c r="W112" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW112" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="113" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>225</v>
+        <v>114</v>
       </c>
       <c r="C113" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="T113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK113" t="s">
+        <v>69</v>
       </c>
       <c r="BG113" t="s">
         <v>69</v>
@@ -3743,10 +3755,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>116</v>
+        <v>227</v>
       </c>
       <c r="C114" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BG114" t="s">
         <v>69</v>
@@ -3754,19 +3766,13 @@
     </row>
     <row r="115" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>209</v>
-      </c>
-      <c r="AM115" t="s">
-        <v>68</v>
-      </c>
-      <c r="AN115" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="BG115" t="s">
         <v>69</v>
@@ -3777,16 +3783,16 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C116" t="s">
-        <v>209</v>
-      </c>
-      <c r="AI116" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="AM116" t="s">
+        <v>68</v>
       </c>
       <c r="AN116" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="BG116" t="s">
         <v>69</v>
@@ -3794,15 +3800,21 @@
     </row>
     <row r="117" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C117" t="s">
-        <v>209</v>
-      </c>
-      <c r="BA117" t="s">
+        <v>211</v>
+      </c>
+      <c r="AI117" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN117" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG117" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3811,36 +3823,24 @@
         <v>120</v>
       </c>
       <c r="B118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>209</v>
-      </c>
-      <c r="U118" t="s">
-        <v>69</v>
-      </c>
-      <c r="V118" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM118" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY118" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG118" t="s">
+        <v>211</v>
+      </c>
+      <c r="BA118" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C119" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U119" t="s">
         <v>69</v>
@@ -3848,11 +3848,11 @@
       <c r="V119" t="s">
         <v>69</v>
       </c>
-      <c r="AD119" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC119" t="s">
-        <v>68</v>
+      <c r="AM119" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY119" t="s">
+        <v>69</v>
       </c>
       <c r="BG119" t="s">
         <v>69</v>
@@ -3860,13 +3860,13 @@
     </row>
     <row r="120" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B120" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U120" t="s">
         <v>69</v>
@@ -3876,6 +3876,9 @@
       </c>
       <c r="AD120" t="s">
         <v>69</v>
+      </c>
+      <c r="BC120" t="s">
+        <v>68</v>
       </c>
       <c r="BG120" t="s">
         <v>69</v>
@@ -3886,10 +3889,10 @@
         <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C121" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U121" t="s">
         <v>69</v>
@@ -3897,50 +3900,53 @@
       <c r="V121" t="s">
         <v>69</v>
       </c>
-      <c r="AB121" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM121" t="s">
+      <c r="AD121" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG121" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C122" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U122" t="s">
         <v>69</v>
       </c>
-      <c r="AD122" t="s">
+      <c r="V122" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB122" t="s">
         <v>69</v>
       </c>
       <c r="AM122" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG122" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="123" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C123" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U123" t="s">
         <v>69</v>
       </c>
       <c r="AD123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM123" t="s">
         <v>69</v>
       </c>
       <c r="BG123" t="s">
@@ -3952,16 +3958,19 @@
         <v>132</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C124" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U124" t="s">
         <v>69</v>
       </c>
+      <c r="AD124" t="s">
+        <v>69</v>
+      </c>
       <c r="BG124" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="125" spans="1:59" x14ac:dyDescent="0.3">
@@ -3969,55 +3978,52 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C125" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U125" t="s">
         <v>69</v>
       </c>
-      <c r="AM125" t="s">
-        <v>69</v>
+      <c r="BG125" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="126" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B126" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C126" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U126" t="s">
         <v>69</v>
       </c>
-      <c r="AD126" t="s">
-        <v>69</v>
-      </c>
       <c r="AM126" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG126" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="127" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B127" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C127" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U127" t="s">
         <v>69</v>
       </c>
       <c r="AD127" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM127" t="s">
         <v>69</v>
       </c>
       <c r="BG127" t="s">
@@ -4029,49 +4035,55 @@
         <v>138</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C128" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U128" t="s">
         <v>69</v>
       </c>
       <c r="AD128" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM128" t="s">
         <v>69</v>
       </c>
       <c r="BG128" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B129" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C129" t="s">
-        <v>209</v>
-      </c>
-      <c r="AZ129" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="U129" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD129" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM129" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG129" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="130" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B130" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C130" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD130" t="s">
+        <v>211</v>
+      </c>
+      <c r="AZ130" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4080,45 +4092,42 @@
         <v>144</v>
       </c>
       <c r="B131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C131" t="s">
-        <v>209</v>
-      </c>
-      <c r="O131" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>69</v>
-      </c>
-      <c r="V131" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB131" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL131" t="s">
-        <v>80</v>
-      </c>
-      <c r="BC131" t="s">
-        <v>68</v>
+        <v>211</v>
+      </c>
+      <c r="AD131" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="132" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>226</v>
+        <v>144</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>146</v>
       </c>
       <c r="C132" t="s">
-        <v>209</v>
-      </c>
-      <c r="BB132" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="O132" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>69</v>
+      </c>
+      <c r="V132" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB132" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL132" t="s">
+        <v>80</v>
       </c>
       <c r="BC132" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="133" spans="1:59" x14ac:dyDescent="0.3">
@@ -4129,9 +4138,12 @@
         <v>229</v>
       </c>
       <c r="C133" t="s">
-        <v>209</v>
-      </c>
-      <c r="V133" t="s">
+        <v>211</v>
+      </c>
+      <c r="BB133" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC133" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4143,13 +4155,10 @@
         <v>231</v>
       </c>
       <c r="C134" t="s">
-        <v>209</v>
-      </c>
-      <c r="AL134" t="s">
-        <v>80</v>
-      </c>
-      <c r="BC134" t="s">
-        <v>68</v>
+        <v>211</v>
+      </c>
+      <c r="V134" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:59" x14ac:dyDescent="0.3">
@@ -4160,44 +4169,47 @@
         <v>233</v>
       </c>
       <c r="C135" t="s">
-        <v>209</v>
-      </c>
-      <c r="V135" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB135" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="AL135" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC135" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C136" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="V136" t="s">
         <v>69</v>
       </c>
       <c r="AB136" t="s">
         <v>69</v>
-      </c>
-      <c r="AL136" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="137" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
         <v>236</v>
       </c>
       <c r="C137" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="V137" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB137" t="s">
+        <v>69</v>
       </c>
       <c r="AL137" t="s">
         <v>80</v>
@@ -4205,27 +4217,27 @@
     </row>
     <row r="138" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C138" t="s">
-        <v>209</v>
-      </c>
-      <c r="BG138" t="s">
-        <v>68</v>
+        <v>211</v>
+      </c>
+      <c r="AL138" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="139" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="B139" t="s">
         <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BG139" t="s">
         <v>68</v>
@@ -4239,42 +4251,24 @@
         <v>241</v>
       </c>
       <c r="C140" t="s">
-        <v>209</v>
-      </c>
-      <c r="BB140" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="BG140" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="141" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>157</v>
+        <v>243</v>
       </c>
       <c r="C141" t="s">
-        <v>209</v>
-      </c>
-      <c r="L141" t="s">
-        <v>68</v>
-      </c>
-      <c r="U141" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE141" t="s">
-        <v>69</v>
-      </c>
-      <c r="AN141" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT141" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV141" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD141" t="s">
-        <v>68</v>
+        <v>211</v>
+      </c>
+      <c r="BB141" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="142" spans="1:59" x14ac:dyDescent="0.3">
@@ -4282,130 +4276,91 @@
         <v>156</v>
       </c>
       <c r="B142" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C142" t="s">
-        <v>209</v>
-      </c>
-      <c r="P142" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC142" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="L142" t="s">
+        <v>68</v>
+      </c>
+      <c r="U142" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE142" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN142" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT142" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV142" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD142" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="143" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C143" t="s">
-        <v>209</v>
-      </c>
-      <c r="H143" t="s">
-        <v>69</v>
-      </c>
-      <c r="N143" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y143" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE143" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH143" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT143" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD143" t="s">
-        <v>68</v>
+        <v>211</v>
+      </c>
+      <c r="P143" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC143" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="144" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>242</v>
+        <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="C144" t="s">
-        <v>209</v>
-      </c>
-      <c r="E144" t="s">
-        <v>69</v>
-      </c>
-      <c r="F144" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="H144" t="s">
         <v>69</v>
       </c>
-      <c r="I144" t="s">
-        <v>69</v>
-      </c>
-      <c r="K144" t="s">
-        <v>69</v>
-      </c>
-      <c r="M144" t="s">
-        <v>69</v>
-      </c>
       <c r="N144" t="s">
         <v>69</v>
       </c>
-      <c r="P144" t="s">
-        <v>69</v>
-      </c>
-      <c r="R144" t="s">
-        <v>69</v>
-      </c>
-      <c r="U144" t="s">
-        <v>69</v>
-      </c>
-      <c r="V144" t="s">
-        <v>69</v>
-      </c>
       <c r="Y144" t="s">
         <v>69</v>
       </c>
-      <c r="AC144" t="s">
-        <v>69</v>
-      </c>
       <c r="AE144" t="s">
         <v>69</v>
       </c>
       <c r="AH144" t="s">
         <v>69</v>
       </c>
-      <c r="AN144" t="s">
-        <v>80</v>
-      </c>
       <c r="AT144" t="s">
         <v>69</v>
       </c>
-      <c r="AV144" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY144" t="s">
-        <v>69</v>
-      </c>
       <c r="BD144" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="B145" t="s">
-        <v>162</v>
+        <v>245</v>
       </c>
       <c r="C145" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E145" t="s">
         <v>69</v>
@@ -4441,9 +4396,6 @@
         <v>69</v>
       </c>
       <c r="Y145" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA145" t="s">
         <v>69</v>
       </c>
       <c r="AC145" t="s">
@@ -4471,7 +4423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -4479,7 +4431,7 @@
         <v>164</v>
       </c>
       <c r="C146" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E146" t="s">
         <v>69</v>
@@ -4493,6 +4445,9 @@
       <c r="I146" t="s">
         <v>69</v>
       </c>
+      <c r="K146" t="s">
+        <v>69</v>
+      </c>
       <c r="M146" t="s">
         <v>69</v>
       </c>
@@ -4512,6 +4467,9 @@
         <v>69</v>
       </c>
       <c r="Y146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA146" t="s">
         <v>69</v>
       </c>
       <c r="AC146" t="s">
@@ -4539,41 +4497,89 @@
         <v>68</v>
       </c>
     </row>
-    <row r="147" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>165</v>
       </c>
       <c r="B147" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="C147" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD147" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="148" spans="1:59" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="E147" t="s">
+        <v>69</v>
+      </c>
+      <c r="F147" t="s">
+        <v>69</v>
+      </c>
+      <c r="H147" t="s">
+        <v>69</v>
+      </c>
+      <c r="I147" t="s">
+        <v>69</v>
+      </c>
+      <c r="M147" t="s">
+        <v>69</v>
+      </c>
+      <c r="N147" t="s">
+        <v>69</v>
+      </c>
+      <c r="P147" t="s">
+        <v>69</v>
+      </c>
+      <c r="R147" t="s">
+        <v>69</v>
+      </c>
+      <c r="U147" t="s">
+        <v>69</v>
+      </c>
+      <c r="V147" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN147" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY147" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD147" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="148" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B148" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="C148" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y148" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC148" t="s">
-        <v>68</v>
+        <v>211</v>
       </c>
       <c r="AD148" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="149" spans="1:59" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="149" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4581,115 +4587,115 @@
         <v>168</v>
       </c>
       <c r="C149" t="s">
-        <v>209</v>
-      </c>
-      <c r="N149" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC149" t="s">
+        <v>68</v>
       </c>
       <c r="AD149" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="150" spans="1:59" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="150" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B150" t="s">
+        <v>170</v>
+      </c>
+      <c r="C150" t="s">
+        <v>211</v>
+      </c>
+      <c r="N150" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD150" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="151" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
         <v>169</v>
-      </c>
-      <c r="C150" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC150" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD150" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="151" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>170</v>
       </c>
       <c r="B151" t="s">
         <v>171</v>
       </c>
       <c r="C151" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AC151" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="152" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="AD151" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="152" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="B152" t="s">
-        <v>246</v>
+        <v>173</v>
       </c>
       <c r="C152" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y152" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="AC152" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="153" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="B153" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="C153" t="s">
-        <v>209</v>
-      </c>
-      <c r="N153" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="Y153" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="154" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="AC153" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="154" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B154" t="s">
-        <v>247</v>
+        <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC154" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="155" spans="1:59" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="N154" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="155" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>176</v>
       </c>
       <c r="B155" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="C155" t="s">
-        <v>209</v>
-      </c>
-      <c r="N155" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y155" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD155" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="156" spans="1:59" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="AC155" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="156" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4697,41 +4703,47 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>209</v>
-      </c>
-      <c r="V156" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="157" spans="1:59" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="N156" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y156" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD156" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="157" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B157" t="s">
+        <v>181</v>
+      </c>
+      <c r="C157" t="s">
+        <v>211</v>
+      </c>
+      <c r="V157" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="158" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>180</v>
-      </c>
-      <c r="C157" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB157" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="158" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>181</v>
       </c>
       <c r="B158" t="s">
         <v>182</v>
       </c>
       <c r="C158" t="s">
-        <v>209</v>
-      </c>
-      <c r="V158" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="159" spans="1:59" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="AB158" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="159" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4739,40 +4751,13 @@
         <v>184</v>
       </c>
       <c r="C159" t="s">
-        <v>209</v>
-      </c>
-      <c r="H159" t="s">
-        <v>69</v>
-      </c>
-      <c r="P159" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y159" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC159" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD159" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE159" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH159" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT159" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV159" t="s">
-        <v>69</v>
-      </c>
-      <c r="BD159" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="160" spans="1:59" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="V159" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="160" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4780,138 +4765,153 @@
         <v>186</v>
       </c>
       <c r="C160" t="s">
-        <v>209</v>
-      </c>
-      <c r="E160" t="s">
-        <v>69</v>
-      </c>
-      <c r="F160" t="s">
-        <v>69</v>
-      </c>
-      <c r="T160" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI160" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK160" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB160" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC160" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG160" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="H160" t="s">
+        <v>69</v>
+      </c>
+      <c r="P160" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV160" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD160" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="161" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B161" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C161" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="E161" t="s">
+        <v>69</v>
+      </c>
+      <c r="F161" t="s">
+        <v>69</v>
+      </c>
+      <c r="T161" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI161" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK161" t="s">
+        <v>69</v>
       </c>
       <c r="BB161" t="s">
         <v>69</v>
       </c>
+      <c r="BC161" t="s">
+        <v>69</v>
+      </c>
       <c r="BG161" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B162" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="C162" t="s">
-        <v>209</v>
-      </c>
-      <c r="AY162" t="s">
-        <v>69</v>
+        <v>211</v>
+      </c>
+      <c r="BB162" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG162" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="163" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B163" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="C163" t="s">
-        <v>209</v>
-      </c>
-      <c r="N163" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y163" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="AY163" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="164" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B164" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C164" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N164" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="Y164" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY164" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="165" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B165" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C165" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N165" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY165" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="166" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B166" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C166" t="s">
-        <v>209</v>
-      </c>
-      <c r="U166" t="s">
-        <v>69</v>
-      </c>
-      <c r="V166" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB166" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM166" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG166" t="s">
+        <v>211</v>
+      </c>
+      <c r="N166" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY166" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
         <v>202</v>
       </c>
       <c r="C167" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U167" t="s">
         <v>69</v>
@@ -4931,50 +4931,50 @@
       <c r="V167" t="s">
         <v>69</v>
       </c>
+      <c r="AB167" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM167" t="s">
+        <v>69</v>
+      </c>
       <c r="BG167" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="168" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B168" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="C168" t="s">
-        <v>209</v>
-      </c>
-      <c r="N168" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD168" t="s">
+        <v>211</v>
+      </c>
+      <c r="U168" t="s">
+        <v>69</v>
+      </c>
+      <c r="V168" t="s">
         <v>69</v>
       </c>
       <c r="BG168" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="169" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B169" t="s">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="C169" t="s">
-        <v>209</v>
-      </c>
-      <c r="AL169" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM169" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB169" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC169" t="s">
+        <v>211</v>
+      </c>
+      <c r="N169" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD169" t="s">
         <v>69</v>
       </c>
       <c r="BG169" t="s">
@@ -4983,45 +4983,85 @@
     </row>
     <row r="170" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="B170" t="s">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="C170" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="AL170" t="s">
+        <v>68</v>
       </c>
       <c r="AM170" t="s">
         <v>69</v>
       </c>
       <c r="BB170" t="s">
+        <v>69</v>
+      </c>
+      <c r="BC170" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG170" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="171" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="B171" t="s">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="C171" t="s">
+        <v>211</v>
+      </c>
+      <c r="AM171" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB171" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="172" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>209</v>
       </c>
-      <c r="V171" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB171" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL171" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM171" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB171" t="s">
-        <v>69</v>
+      <c r="B172" t="s">
+        <v>210</v>
+      </c>
+      <c r="C172" t="s">
+        <v>211</v>
+      </c>
+      <c r="V172" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB172" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL172" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM172" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB172" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="173" spans="1:59" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>254</v>
+      </c>
+      <c r="B173" t="s">
+        <v>255</v>
+      </c>
+      <c r="C173" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG173" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003204A9-93E6-40E1-B551-2C97A7AC7322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481C86E7-C42D-456B-988B-5872EBE3F480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
